--- a/database/event/3454/event_3454_evp_summary.xlsx
+++ b/database/event/3454/event_3454_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5179</v>
+        <v>7.478</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0519</v>
+        <v>2.0411</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6157</v>
+        <v>2.5353</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5179</v>
+        <v>7.478</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6898</v>
+        <v>2.6499</v>
       </c>
       <c r="G2" t="n">
         <v>4.8281</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6898</v>
+        <v>2.6499</v>
       </c>
       <c r="I2" t="n">
         <v>2.7402</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7564</v>
+        <v>5.749</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5712</v>
+        <v>1.5691</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9041</v>
+        <v>1.8465</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7564</v>
+        <v>5.749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="G3" t="n">
         <v>4.7651</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.984</v>
       </c>
       <c r="I3" t="n">
         <v>1.0006</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6662</v>
+        <v>4.6312</v>
       </c>
       <c r="C4" t="n">
-        <v>1.2736</v>
+        <v>1.264</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4637</v>
+        <v>1.4012</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6662</v>
+        <v>4.6312</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3579</v>
+        <v>2.3229</v>
       </c>
       <c r="G4" t="n">
         <v>2.3083</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3579</v>
+        <v>2.3229</v>
       </c>
       <c r="I4" t="n">
         <v>2.4021</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9792</v>
+        <v>3.9704</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0861</v>
+        <v>1.0837</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1861</v>
+        <v>1.1379</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9792</v>
+        <v>3.9704</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1779</v>
+        <v>1.1691</v>
       </c>
       <c r="G5" t="n">
         <v>2.8013</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1779</v>
+        <v>1.1691</v>
       </c>
       <c r="I5" t="n">
         <v>1.1889</v>
@@ -686,7 +686,7 @@
         <v>1.0485</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1305</v>
+        <v>1.0865</v>
       </c>
       <c r="E6" t="n">
         <v>3.8414</v>
@@ -732,7 +732,7 @@
         <v>1.0466</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1278</v>
+        <v>1.0838</v>
       </c>
       <c r="E7" t="n">
         <v>3.8347</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7617</v>
+        <v>3.753</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0267</v>
+        <v>1.0243</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0983</v>
+        <v>1.0513</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7617</v>
+        <v>3.753</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1697</v>
+        <v>1.161</v>
       </c>
       <c r="G8" t="n">
         <v>2.592</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1697</v>
+        <v>1.161</v>
       </c>
       <c r="I8" t="n">
         <v>1.1806</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6935</v>
+        <v>3.6566</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0081</v>
+        <v>0.998</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0707</v>
+        <v>1.0129</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6935</v>
+        <v>3.6566</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4887</v>
+        <v>2.4518</v>
       </c>
       <c r="G9" t="n">
         <v>1.2048</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4887</v>
+        <v>2.4518</v>
       </c>
       <c r="I9" t="n">
         <v>2.5354</v>
@@ -870,7 +870,7 @@
         <v>0.9653</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0074</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>3.5368</v>
@@ -916,7 +916,7 @@
         <v>0.7127</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6335</v>
+        <v>0.5964</v>
       </c>
       <c r="E11" t="n">
         <v>2.6111</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.394</v>
+        <v>2.3572</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6534</v>
+        <v>0.6434</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5458</v>
+        <v>0.4952</v>
       </c>
       <c r="E12" t="n">
-        <v>2.394</v>
+        <v>2.3572</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4776</v>
+        <v>2.4408</v>
       </c>
       <c r="G12" t="n">
         <v>-0.08359999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4776</v>
+        <v>2.4408</v>
       </c>
       <c r="I12" t="n">
         <v>2.524</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9822</v>
+        <v>1.9788</v>
       </c>
       <c r="C13" t="n">
-        <v>0.541</v>
+        <v>0.5401</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3794</v>
+        <v>0.3444</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9822</v>
+        <v>1.9788</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4549</v>
+        <v>0.4515</v>
       </c>
       <c r="G13" t="n">
         <v>1.5273</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4549</v>
+        <v>0.4515</v>
       </c>
       <c r="I13" t="n">
         <v>0.4591</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9478</v>
+        <v>1.9447</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5316</v>
+        <v>0.5308</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3655</v>
+        <v>0.3309</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9478</v>
+        <v>1.9447</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8171</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>1.1307</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8171</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0.8209</v>
@@ -1100,7 +1100,7 @@
         <v>0.5104</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3341</v>
+        <v>0.3011</v>
       </c>
       <c r="E15" t="n">
         <v>1.8701</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8077</v>
+        <v>1.815</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4934</v>
+        <v>0.4954</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3089</v>
+        <v>0.2792</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8077</v>
+        <v>1.815</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9809</v>
+        <v>-0.9736</v>
       </c>
       <c r="G16" t="n">
         <v>2.7886</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9809</v>
+        <v>-0.9736</v>
       </c>
       <c r="I16" t="n">
         <v>-0.9901</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6613</v>
+        <v>1.6486</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4534</v>
+        <v>0.45</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2498</v>
+        <v>0.2129</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6613</v>
+        <v>1.6486</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7082</v>
+        <v>1.6955</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0469</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7082</v>
+        <v>1.6955</v>
       </c>
       <c r="I17" t="n">
         <v>1.7241</v>
@@ -1238,7 +1238,7 @@
         <v>0.3961</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1649</v>
+        <v>0.1342</v>
       </c>
       <c r="E18" t="n">
         <v>1.4512</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1808</v>
+        <v>1.1344</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3223</v>
+        <v>0.3096</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0557</v>
+        <v>0.008</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1808</v>
+        <v>1.1344</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0958</v>
+        <v>2.0494</v>
       </c>
       <c r="G19" t="n">
         <v>-0.915</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0958</v>
+        <v>2.0494</v>
       </c>
       <c r="I19" t="n">
         <v>2.1551</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9615</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2624</v>
+        <v>0.2626</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0329</v>
+        <v>-0.0606</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9615</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1001</v>
+        <v>-0.0993</v>
       </c>
       <c r="G20" t="n">
         <v>1.0616</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1001</v>
+        <v>-0.0993</v>
       </c>
       <c r="I20" t="n">
         <v>-0.101</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6908</v>
+        <v>0.6883</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1885</v>
+        <v>0.1879</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1423</v>
+        <v>-0.1697</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6908</v>
+        <v>0.6883</v>
       </c>
       <c r="F21" t="n">
-        <v>0.662</v>
+        <v>0.6595</v>
       </c>
       <c r="G21" t="n">
         <v>0.0288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.662</v>
+        <v>0.6595</v>
       </c>
       <c r="I21" t="n">
         <v>0.6651</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.644</v>
+        <v>0.6444</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1758</v>
+        <v>0.1759</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1612</v>
+        <v>-0.1872</v>
       </c>
       <c r="E22" t="n">
-        <v>0.644</v>
+        <v>0.6444</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1106</v>
+        <v>-0.1102</v>
       </c>
       <c r="G22" t="n">
         <v>0.7546</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1106</v>
+        <v>-0.1102</v>
       </c>
       <c r="I22" t="n">
         <v>-0.1111</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5659</v>
+        <v>0.5662</v>
       </c>
       <c r="C23" t="n">
         <v>0.1545</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1928</v>
+        <v>-0.2183</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5659</v>
+        <v>0.5662</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0422</v>
+        <v>-0.0419</v>
       </c>
       <c r="G23" t="n">
         <v>0.6081</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0422</v>
+        <v>-0.0419</v>
       </c>
       <c r="I23" t="n">
         <v>-0.0426</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5617</v>
+        <v>0.5522</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1533</v>
+        <v>0.1507</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1944</v>
+        <v>-0.2239</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5617</v>
+        <v>0.5522</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2829</v>
+        <v>1.2734</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7212</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2829</v>
+        <v>1.2734</v>
       </c>
       <c r="I24" t="n">
         <v>1.2949</v>
@@ -1560,7 +1560,7 @@
         <v>0.0844</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2964</v>
+        <v>-0.3206</v>
       </c>
       <c r="E25" t="n">
         <v>0.3094</v>
@@ -1606,7 +1606,7 @@
         <v>0.0616</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3302</v>
+        <v>-0.354</v>
       </c>
       <c r="E26" t="n">
         <v>0.2256</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1738</v>
+        <v>0.1752</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0474</v>
+        <v>0.0478</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3512</v>
+        <v>-0.3741</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1738</v>
+        <v>0.1752</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3707</v>
+        <v>-0.3693</v>
       </c>
       <c r="G27" t="n">
         <v>0.5445</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3707</v>
+        <v>-0.3693</v>
       </c>
       <c r="I27" t="n">
         <v>-0.3724</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3013</v>
+        <v>-0.3027</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0822</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5431</v>
+        <v>-0.5645</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3013</v>
+        <v>-0.3027</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3754</v>
+        <v>0.374</v>
       </c>
       <c r="G28" t="n">
         <v>-0.6767</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3754</v>
+        <v>0.374</v>
       </c>
       <c r="I28" t="n">
         <v>0.3771</v>
@@ -1744,7 +1744,7 @@
         <v>-0.08649999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5494</v>
+        <v>-0.5702</v>
       </c>
       <c r="E29" t="n">
         <v>-0.3169</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4193</v>
+        <v>-0.4138</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1144</v>
+        <v>-0.1129</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5908</v>
+        <v>-0.6088</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4193</v>
+        <v>-0.4138</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7323</v>
+        <v>-0.7268</v>
       </c>
       <c r="G30" t="n">
         <v>0.313</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7323</v>
+        <v>-0.7268</v>
       </c>
       <c r="I30" t="n">
         <v>-0.7391</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2019</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7202</v>
+        <v>-0.7386</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7397</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.977</v>
+        <v>-0.981</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2667</v>
+        <v>-0.2678</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-0.8347</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.977</v>
+        <v>-0.981</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5434</v>
+        <v>0.5394</v>
       </c>
       <c r="G32" t="n">
         <v>-1.5204</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5434</v>
+        <v>0.5394</v>
       </c>
       <c r="I32" t="n">
         <v>0.5485</v>
@@ -1928,7 +1928,7 @@
         <v>-0.27</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.8381</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9893999999999999</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2787</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8338</v>
+        <v>-0.8507</v>
       </c>
       <c r="E34" t="n">
         <v>-1.021</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2841</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8419</v>
+        <v>-0.8586</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0409</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3055</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8736</v>
+        <v>-0.8899</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1194</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2454</v>
+        <v>-1.2453</v>
       </c>
       <c r="C37" t="n">
         <v>-0.3399</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9245</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2454</v>
+        <v>-1.2453</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.0164</v>
+        <v>-0.0163</v>
       </c>
       <c r="G37" t="n">
         <v>-1.229</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0164</v>
+        <v>-0.0163</v>
       </c>
       <c r="I37" t="n">
         <v>-0.0166</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2546</v>
+        <v>-1.249</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3424</v>
+        <v>-0.3409</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9282</v>
+        <v>-0.9415</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2546</v>
+        <v>-1.249</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.756</v>
+        <v>-0.7504</v>
       </c>
       <c r="G38" t="n">
         <v>-0.4986</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.756</v>
+        <v>-0.7504</v>
       </c>
       <c r="I38" t="n">
         <v>-0.7631</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2899</v>
+        <v>-1.2878</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3521</v>
+        <v>-0.3515</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9425</v>
+        <v>-0.957</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2899</v>
+        <v>-1.2878</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.288</v>
+        <v>-0.2859</v>
       </c>
       <c r="G39" t="n">
         <v>-1.0019</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.288</v>
+        <v>-0.2859</v>
       </c>
       <c r="I39" t="n">
         <v>-0.2907</v>
@@ -2250,7 +2250,7 @@
         <v>-0.4995</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1606</v>
+        <v>-1.173</v>
       </c>
       <c r="E40" t="n">
         <v>-1.83</v>

--- a/database/event/3454/event_3454_evp_summary.xlsx
+++ b/database/event/3454/event_3454_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.478</v>
+        <v>6.8793</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0411</v>
+        <v>1.8776</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5353</v>
+        <v>2.4676</v>
       </c>
       <c r="E2" t="n">
-        <v>7.478</v>
+        <v>6.8793</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6499</v>
+        <v>2.552</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8281</v>
+        <v>4.3273</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6499</v>
+        <v>2.552</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7402</v>
+        <v>2.9984</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8281</v>
+        <v>4.3273</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>263</v>
       </c>
       <c r="M2" t="n">
-        <v>7.568300000000001</v>
+        <v>7.3257</v>
       </c>
       <c r="N2" t="n">
         <v>368</v>
@@ -538,185 +538,185 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.749</v>
+        <v>4.9498</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5691</v>
+        <v>1.351</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8465</v>
+        <v>1.5966</v>
       </c>
       <c r="E3" t="n">
-        <v>5.749</v>
+        <v>4.9498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.984</v>
+        <v>2.7356</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7651</v>
+        <v>2.2142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.984</v>
+        <v>2.7356</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0006</v>
+        <v>3.2141</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7651</v>
+        <v>2.2142</v>
       </c>
       <c r="K3" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="L3" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="M3" t="n">
-        <v>5.765700000000001</v>
+        <v>5.4283</v>
       </c>
       <c r="N3" t="n">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6312</v>
+        <v>4.8998</v>
       </c>
       <c r="C4" t="n">
-        <v>1.264</v>
+        <v>1.3374</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4012</v>
+        <v>1.574</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6312</v>
+        <v>4.8998</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3229</v>
+        <v>0.9828</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3083</v>
+        <v>3.917</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3229</v>
+        <v>0.9828</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4021</v>
+        <v>1.0653</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3083</v>
+        <v>3.917</v>
       </c>
       <c r="K4" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7104</v>
+        <v>4.9823</v>
       </c>
       <c r="N4" t="n">
-        <v>368</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9704</v>
+        <v>3.6263</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0837</v>
+        <v>0.9898</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1379</v>
+        <v>0.9991</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9704</v>
+        <v>3.6263</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1691</v>
+        <v>0.7836</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8013</v>
+        <v>2.8427</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1691</v>
+        <v>0.7836</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1889</v>
+        <v>0.7836</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8013</v>
+        <v>2.8427</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="L5" t="n">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9902</v>
+        <v>3.6263</v>
       </c>
       <c r="N5" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8414</v>
+        <v>3.5632</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0485</v>
+        <v>0.9725</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0865</v>
+        <v>0.9706</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8414</v>
+        <v>3.5632</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3882</v>
+        <v>1.1213</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4532</v>
+        <v>2.4419</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3882</v>
+        <v>1.1213</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3882</v>
+        <v>1.2154</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4532</v>
+        <v>2.4419</v>
       </c>
       <c r="K6" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>112</v>
+        <v>181</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8414</v>
+        <v>3.6573</v>
       </c>
       <c r="N6" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8347</v>
+        <v>3.3555</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0466</v>
+        <v>0.9159</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0838</v>
+        <v>0.8768</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8347</v>
+        <v>3.3555</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8347</v>
+        <v>3.3555</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8347</v>
+        <v>3.3555</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8347</v>
+        <v>3.3555</v>
       </c>
       <c r="N7" t="n">
         <v>162</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.753</v>
+        <v>3.3334</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0243</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0513</v>
+        <v>0.8668</v>
       </c>
       <c r="E8" t="n">
-        <v>3.753</v>
+        <v>3.3334</v>
       </c>
       <c r="F8" t="n">
-        <v>1.161</v>
+        <v>2.1427</v>
       </c>
       <c r="G8" t="n">
-        <v>2.592</v>
+        <v>1.1907</v>
       </c>
       <c r="H8" t="n">
-        <v>1.161</v>
+        <v>2.1427</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1806</v>
+        <v>2.5175</v>
       </c>
       <c r="J8" t="n">
-        <v>2.592</v>
+        <v>1.1907</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="L8" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7726</v>
+        <v>3.7082</v>
       </c>
       <c r="N8" t="n">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6566</v>
+        <v>3.2851</v>
       </c>
       <c r="C9" t="n">
-        <v>0.998</v>
+        <v>0.8966</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0129</v>
+        <v>0.845</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6566</v>
+        <v>3.2851</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4518</v>
+        <v>1.0984</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2048</v>
+        <v>2.1867</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4518</v>
+        <v>1.0984</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5354</v>
+        <v>1.1906</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2048</v>
+        <v>2.1867</v>
       </c>
       <c r="K9" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="L9" t="n">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7402</v>
+        <v>3.3773</v>
       </c>
       <c r="N9" t="n">
-        <v>368</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5368</v>
+        <v>2.9307</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9653</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9651999999999999</v>
+        <v>0.6851</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5368</v>
+        <v>2.9307</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.5603</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4163</v>
+        <v>3.491</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.5603</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.5603</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4163</v>
+        <v>3.491</v>
       </c>
       <c r="K10" t="n">
         <v>113</v>
@@ -897,7 +897,7 @@
         <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>3.536799999999999</v>
+        <v>2.9307</v>
       </c>
       <c r="N10" t="n">
         <v>225</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6111</v>
+        <v>2.6231</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7127</v>
+        <v>0.716</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5964</v>
+        <v>0.5462</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6111</v>
+        <v>2.6231</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1427</v>
+        <v>2.469</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4684</v>
+        <v>0.1541</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1427</v>
+        <v>2.469</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1427</v>
+        <v>2.9009</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4684</v>
+        <v>0.1541</v>
       </c>
       <c r="K11" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="L11" t="n">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6111</v>
+        <v>3.055</v>
       </c>
       <c r="N11" t="n">
-        <v>225</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3572</v>
+        <v>2.5268</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6434</v>
+        <v>0.6897</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4952</v>
+        <v>0.5027</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3572</v>
+        <v>2.5268</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4408</v>
+        <v>0.5609</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.08359999999999999</v>
+        <v>1.9659</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4408</v>
+        <v>0.5609</v>
       </c>
       <c r="I12" t="n">
-        <v>2.524</v>
+        <v>0.5609</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.08359999999999999</v>
+        <v>1.9659</v>
       </c>
       <c r="K12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="L12" t="n">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4404</v>
+        <v>2.5268</v>
       </c>
       <c r="N12" t="n">
-        <v>368</v>
+        <v>225</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9788</v>
+        <v>1.9465</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5401</v>
+        <v>0.5313</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3444</v>
+        <v>0.2407</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9788</v>
+        <v>1.9465</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4515</v>
+        <v>0.5736</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5273</v>
+        <v>1.3729</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4515</v>
+        <v>0.5736</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4591</v>
+        <v>0.6217</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5273</v>
+        <v>1.3729</v>
       </c>
       <c r="K13" t="n">
         <v>122</v>
@@ -1035,7 +1035,7 @@
         <v>98</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9864</v>
+        <v>1.9946</v>
       </c>
       <c r="N13" t="n">
         <v>220</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9447</v>
+        <v>1.852</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5308</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3309</v>
+        <v>0.1981</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9447</v>
+        <v>1.852</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.3726</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1307</v>
+        <v>-0.5206</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8139999999999999</v>
+        <v>2.3726</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8209</v>
+        <v>3.0216</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1307</v>
+        <v>-0.5206</v>
       </c>
       <c r="K14" t="n">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="L14" t="n">
-        <v>73</v>
+        <v>359</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9516</v>
+        <v>2.501</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15">
@@ -1094,22 +1094,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8701</v>
+        <v>1.7787</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5104</v>
+        <v>0.4855</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3011</v>
+        <v>0.165</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8701</v>
+        <v>1.7787</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8701</v>
+        <v>1.7787</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8701</v>
+        <v>1.7787</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>162</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8701</v>
+        <v>1.7787</v>
       </c>
       <c r="N15" t="n">
         <v>162</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.815</v>
+        <v>1.7468</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4954</v>
+        <v>0.4768</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2792</v>
+        <v>0.1506</v>
       </c>
       <c r="E16" t="n">
-        <v>1.815</v>
+        <v>1.7468</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9736</v>
+        <v>-0.784</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7886</v>
+        <v>2.5308</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9736</v>
+        <v>-0.784</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9901</v>
+        <v>-0.8498</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7886</v>
+        <v>2.5308</v>
       </c>
       <c r="K16" t="n">
         <v>50</v>
@@ -1173,7 +1173,7 @@
         <v>181</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7985</v>
+        <v>1.681</v>
       </c>
       <c r="N16" t="n">
         <v>231</v>
@@ -1182,139 +1182,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6486</v>
+        <v>1.7106</v>
       </c>
       <c r="C17" t="n">
-        <v>0.45</v>
+        <v>0.4669</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2129</v>
+        <v>0.1342</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6486</v>
+        <v>1.7106</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6955</v>
+        <v>0.7821</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0469</v>
+        <v>0.9285</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6955</v>
+        <v>0.7821</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7241</v>
+        <v>0.8143</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0469</v>
+        <v>0.9285</v>
       </c>
       <c r="K17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L17" t="n">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6772</v>
+        <v>1.7428</v>
       </c>
       <c r="N17" t="n">
-        <v>231</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4512</v>
+        <v>1.4894</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3961</v>
+        <v>0.4065</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1342</v>
+        <v>0.0344</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4512</v>
+        <v>1.4894</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.8065</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4512</v>
+        <v>-0.3171</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.8065</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1.9582</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4512</v>
+        <v>-0.3171</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L18" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4512</v>
+        <v>1.6411</v>
       </c>
       <c r="N18" t="n">
-        <v>162</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1344</v>
+        <v>1.2795</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3096</v>
+        <v>0.3492</v>
       </c>
       <c r="D19" t="n">
-        <v>0.008</v>
+        <v>-0.0604</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1344</v>
+        <v>1.2795</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0494</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.915</v>
+        <v>1.2795</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0494</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1551</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.915</v>
+        <v>1.2795</v>
       </c>
       <c r="K19" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>359</v>
+        <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2401</v>
+        <v>1.2795</v>
       </c>
       <c r="N19" t="n">
-        <v>523</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9754</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2626</v>
+        <v>0.2662</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0606</v>
+        <v>-0.1977</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9754</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0993</v>
+        <v>0.3681</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0616</v>
+        <v>0.6073</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0993</v>
+        <v>0.3681</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.101</v>
+        <v>0.399</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0616</v>
+        <v>0.6073</v>
       </c>
       <c r="K20" t="n">
         <v>122</v>
@@ -1357,7 +1357,7 @@
         <v>98</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9606000000000001</v>
+        <v>1.0063</v>
       </c>
       <c r="N20" t="n">
         <v>220</v>
@@ -1366,81 +1366,81 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6883</v>
+        <v>0.821</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1879</v>
+        <v>0.2241</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1697</v>
+        <v>-0.2674</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6883</v>
+        <v>0.821</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6595</v>
+        <v>1.1959</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0288</v>
+        <v>-0.3749</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6595</v>
+        <v>1.1959</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6651</v>
+        <v>1.2963</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0288</v>
+        <v>-0.3749</v>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="L21" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6939000000000001</v>
+        <v>0.9214</v>
       </c>
       <c r="N21" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6444</v>
+        <v>0.8021</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1759</v>
+        <v>0.2189</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1872</v>
+        <v>-0.2759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6444</v>
+        <v>0.8021</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1102</v>
+        <v>0.6048</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7546</v>
+        <v>0.1973</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1102</v>
+        <v>0.6048</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1111</v>
+        <v>0.6297</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7546</v>
+        <v>0.1973</v>
       </c>
       <c r="K22" t="n">
         <v>80</v>
@@ -1449,7 +1449,7 @@
         <v>73</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6435000000000001</v>
+        <v>0.8270000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>153</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5662</v>
+        <v>0.8015</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1545</v>
+        <v>0.2188</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2183</v>
+        <v>-0.2762</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5662</v>
+        <v>0.8015</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0419</v>
+        <v>0.1955</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6081</v>
+        <v>0.606</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0419</v>
+        <v>0.1955</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0426</v>
+        <v>0.2119</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6081</v>
+        <v>0.606</v>
       </c>
       <c r="K23" t="n">
         <v>122</v>
@@ -1495,7 +1495,7 @@
         <v>98</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5655</v>
+        <v>0.8179</v>
       </c>
       <c r="N23" t="n">
         <v>220</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5522</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1507</v>
+        <v>0.1677</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2239</v>
+        <v>-0.3606</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5522</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2734</v>
+        <v>0.0282</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7212</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2734</v>
+        <v>0.0282</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2949</v>
+        <v>0.0294</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7212</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L24" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5737</v>
+        <v>0.6156</v>
       </c>
       <c r="N24" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3094</v>
+        <v>0.494</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0844</v>
+        <v>0.1348</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3206</v>
+        <v>-0.415</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3094</v>
+        <v>0.494</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3094</v>
+        <v>0.494</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3094</v>
+        <v>0.494</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3094</v>
+        <v>0.494</v>
       </c>
       <c r="N25" t="n">
         <v>162</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2256</v>
+        <v>0.3935</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0616</v>
+        <v>0.1074</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.354</v>
+        <v>-0.4604</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2256</v>
+        <v>0.3935</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3248</v>
+        <v>-0.1244</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5504</v>
+        <v>0.5179</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3248</v>
+        <v>-0.1244</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3248</v>
+        <v>-0.1244</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5504</v>
+        <v>0.5179</v>
       </c>
       <c r="K26" t="n">
         <v>113</v>
@@ -1633,7 +1633,7 @@
         <v>112</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2256</v>
+        <v>0.3935</v>
       </c>
       <c r="N26" t="n">
         <v>225</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1752</v>
+        <v>0.2921</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0478</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3741</v>
+        <v>-0.5061</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1752</v>
+        <v>0.2921</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3693</v>
+        <v>-0.0926</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5445</v>
+        <v>0.3847</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3693</v>
+        <v>-0.0926</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3724</v>
+        <v>-0.0964</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5445</v>
+        <v>0.3847</v>
       </c>
       <c r="K27" t="n">
         <v>80</v>
@@ -1679,7 +1679,7 @@
         <v>73</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1721</v>
+        <v>0.2883</v>
       </c>
       <c r="N27" t="n">
         <v>153</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3027</v>
+        <v>0.2349</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5645</v>
+        <v>-0.532</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3027</v>
+        <v>0.2349</v>
       </c>
       <c r="F28" t="n">
-        <v>0.374</v>
+        <v>0.6514</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6767</v>
+        <v>-0.4165</v>
       </c>
       <c r="H28" t="n">
-        <v>0.374</v>
+        <v>0.6514</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3771</v>
+        <v>0.6782</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6767</v>
+        <v>-0.4165</v>
       </c>
       <c r="K28" t="n">
         <v>80</v>
@@ -1725,7 +1725,7 @@
         <v>73</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2996</v>
+        <v>0.2617</v>
       </c>
       <c r="N28" t="n">
         <v>153</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3169</v>
+        <v>0.1829</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.0499</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5702</v>
+        <v>-0.5554</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3169</v>
+        <v>0.1829</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4589</v>
+        <v>-0.283</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7758</v>
+        <v>0.4659</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4589</v>
+        <v>-0.283</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4589</v>
+        <v>-0.3068</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7758</v>
+        <v>0.4659</v>
       </c>
       <c r="K29" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="L29" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3169000000000001</v>
+        <v>0.1591</v>
       </c>
       <c r="N29" t="n">
-        <v>98</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4138</v>
+        <v>0.0606</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1129</v>
+        <v>0.0165</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6088</v>
+        <v>-0.6107</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4138</v>
+        <v>0.0606</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7268</v>
+        <v>0.6595</v>
       </c>
       <c r="G30" t="n">
-        <v>0.313</v>
+        <v>-0.5989</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7268</v>
+        <v>0.6595</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7391</v>
+        <v>0.6595</v>
       </c>
       <c r="J30" t="n">
-        <v>0.313</v>
+        <v>-0.5989</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="L30" t="n">
+        <v>39</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="N30" t="n">
         <v>98</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-0.4261</v>
-      </c>
-      <c r="N30" t="n">
-        <v>220</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7397</v>
+        <v>-0.148</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2019</v>
+        <v>-0.0404</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7386</v>
+        <v>-0.7048</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7397</v>
+        <v>-0.148</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0981</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3584</v>
+        <v>0.4654</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0981</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0981</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3584</v>
+        <v>0.4654</v>
       </c>
       <c r="K31" t="n">
         <v>113</v>
@@ -1863,7 +1863,7 @@
         <v>112</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7397</v>
+        <v>-0.148</v>
       </c>
       <c r="N31" t="n">
         <v>225</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.981</v>
+        <v>-0.4773</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2678</v>
+        <v>-0.1303</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8347</v>
+        <v>-0.8535</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.981</v>
+        <v>-0.4773</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5394</v>
+        <v>0.6158</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.5204</v>
+        <v>-1.0931</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5394</v>
+        <v>0.6158</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5485</v>
+        <v>0.6675</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.5204</v>
+        <v>-1.0931</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -1909,7 +1909,7 @@
         <v>96</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.9719</v>
+        <v>-0.4256</v>
       </c>
       <c r="N32" t="n">
         <v>155</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.539</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.27</v>
+        <v>-0.1471</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8381</v>
+        <v>-0.8813</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.539</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9314</v>
+        <v>-0.5964</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.058</v>
+        <v>0.0574</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9314</v>
+        <v>-0.5964</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9314</v>
+        <v>-0.5964</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.058</v>
+        <v>0.0574</v>
       </c>
       <c r="K33" t="n">
         <v>59</v>
@@ -1955,7 +1955,7 @@
         <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9894000000000001</v>
+        <v>-0.539</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.021</v>
+        <v>-0.7585</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2787</v>
+        <v>-0.207</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8507</v>
+        <v>-0.9804</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.021</v>
+        <v>-0.7585</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.021</v>
+        <v>0.117</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.021</v>
+        <v>0.117</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.021</v>
+        <v>0.117</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="K34" t="n">
         <v>59</v>
@@ -2001,7 +2001,7 @@
         <v>39</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.021</v>
+        <v>-0.7585</v>
       </c>
       <c r="N34" t="n">
         <v>98</v>
@@ -2010,35 +2010,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>jR</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0409</v>
+        <v>-0.7677</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2841</v>
+        <v>-0.2095</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8586</v>
+        <v>-0.9846</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0409</v>
+        <v>-0.7677</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.0409</v>
+        <v>0.013</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0409</v>
+        <v>0.013</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0409</v>
+        <v>0.013</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="K35" t="n">
         <v>59</v>
@@ -2047,7 +2047,7 @@
         <v>39</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0409</v>
+        <v>-0.7676999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>98</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1194</v>
+        <v>-0.7684</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3055</v>
+        <v>-0.2097</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8899</v>
+        <v>-0.9849</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1194</v>
+        <v>-0.7684</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1194</v>
+        <v>0.0926</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>-0.861</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1194</v>
+        <v>0.0926</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1194</v>
+        <v>0.1004</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>-0.861</v>
       </c>
       <c r="K36" t="n">
         <v>59</v>
       </c>
       <c r="L36" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1194</v>
+        <v>-0.7605999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2453</v>
+        <v>-0.7692</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3399</v>
+        <v>-0.2099</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9853</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2453</v>
+        <v>-0.7692</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.0163</v>
+        <v>-0.4516</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.229</v>
+        <v>-0.3176</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0163</v>
+        <v>-0.4516</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0166</v>
+        <v>-0.4895</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.229</v>
+        <v>-0.3176</v>
       </c>
       <c r="K37" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="L37" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2456</v>
+        <v>-0.8070999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>155</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>jR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.249</v>
+        <v>-0.7945</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3409</v>
+        <v>-0.2169</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9415</v>
+        <v>-0.9967</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.249</v>
+        <v>-0.7945</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7504</v>
+        <v>0.0611</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4986</v>
+        <v>-0.8556</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7504</v>
+        <v>0.0611</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7631</v>
+        <v>0.0611</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4986</v>
+        <v>-0.8556</v>
       </c>
       <c r="K38" t="n">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="L38" t="n">
+        <v>39</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.7945</v>
+      </c>
+      <c r="N38" t="n">
         <v>98</v>
-      </c>
-      <c r="M38" t="n">
-        <v>-1.2617</v>
-      </c>
-      <c r="N38" t="n">
-        <v>220</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2878</v>
+        <v>-0.9216</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3515</v>
+        <v>-0.2515</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.957</v>
+        <v>-1.0541</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2878</v>
+        <v>-0.9216</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2859</v>
+        <v>-0.1404</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.0019</v>
+        <v>-0.7812</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2859</v>
+        <v>-0.1404</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2907</v>
+        <v>-0.1522</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.0019</v>
+        <v>-0.7812</v>
       </c>
       <c r="K39" t="n">
         <v>59</v>
@@ -2231,7 +2231,7 @@
         <v>96</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2926</v>
+        <v>-0.9334</v>
       </c>
       <c r="N39" t="n">
         <v>155</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.83</v>
+        <v>-1.3028</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4995</v>
+        <v>-0.3556</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.173</v>
+        <v>-1.2262</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.83</v>
+        <v>-1.3028</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.83</v>
+        <v>-1.3028</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.83</v>
+        <v>-1.3028</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.83</v>
+        <v>-1.3028</v>
       </c>
       <c r="N40" t="n">
         <v>162</v>
@@ -2383,10 +2383,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2484</v>
+        <v>0.1981</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2484</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2316</v>
+        <v>0.1841</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2316</v>
+        <v>0.1841</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1593</v>
+        <v>0.1259</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1593</v>
+        <v>0.1259</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0954</v>
+        <v>0.0789</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0954</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3476</v>
+        <v>-0.2125</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3476</v>
+        <v>-0.2125</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4547</v>
+        <v>0.5394</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4547</v>
+        <v>0.5394</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3267</v>
+        <v>0.3809</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3267</v>
+        <v>0.3809</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0442</v>
+        <v>0.081</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0442</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0389</v>
+        <v>-0.0066</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0389</v>
+        <v>-0.0066</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2326</v>
+        <v>-0.1316</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2326</v>
+        <v>-0.1316</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3115</v>
+        <v>0.33</v>
       </c>
       <c r="J12" t="n">
-        <v>11.214</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>0.87</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1485</v>
+        <v>-0.1349</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.346</v>
+        <v>-4.8564</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4936</v>
+        <v>-0.3313</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.7696</v>
+        <v>-11.9268</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5793</v>
+        <v>-0.3876</v>
       </c>
       <c r="J15" t="n">
-        <v>-20.8548</v>
+        <v>-13.9536</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7238</v>
+        <v>-0.4902</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.0568</v>
+        <v>-17.6472</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.879</v>
+        <v>0.8018</v>
       </c>
       <c r="J17" t="n">
-        <v>31.644</v>
+        <v>28.8648</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>1.4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5324</v>
+        <v>0.4911</v>
       </c>
       <c r="J18" t="n">
-        <v>19.1664</v>
+        <v>17.6796</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.471</v>
+        <v>0.4492</v>
       </c>
       <c r="J19" t="n">
-        <v>16.956</v>
+        <v>16.1712</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3298</v>
+        <v>0.3379</v>
       </c>
       <c r="J20" t="n">
-        <v>11.8728</v>
+        <v>12.1644</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0843</v>
+        <v>0.1188</v>
       </c>
       <c r="J21" t="n">
-        <v>3.0348</v>
+        <v>4.2768</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4649</v>
+        <v>0.5537</v>
       </c>
       <c r="J22" t="n">
-        <v>11.1576</v>
+        <v>13.2888</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1889</v>
+        <v>0.2294</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5336</v>
+        <v>5.5056</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0404</v>
+        <v>0.0794</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9696</v>
+        <v>1.9056</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0404</v>
+        <v>0.0794</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9696</v>
+        <v>1.9056</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0421</v>
+        <v>-0.0076</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.0104</v>
+        <v>-0.1824</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4639</v>
+        <v>0.39</v>
       </c>
       <c r="J27" t="n">
-        <v>11.1336</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2251</v>
+        <v>0.1817</v>
       </c>
       <c r="J28" t="n">
-        <v>5.4024</v>
+        <v>4.3608</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0066</v>
+        <v>0.0222</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1584</v>
+        <v>0.5328000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0639</v>
+        <v>-0.0249</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.5336</v>
+        <v>-0.5976</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2906</v>
+        <v>-0.1725</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.9744</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>1.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.179</v>
+        <v>0.1254</v>
       </c>
       <c r="J32" t="n">
-        <v>4.833</v>
+        <v>3.3858</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.179</v>
+        <v>0.1254</v>
       </c>
       <c r="J33" t="n">
-        <v>4.833</v>
+        <v>3.3858</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0511</v>
+        <v>-0.0456</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.3797</v>
+        <v>-1.2312</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2242</v>
+        <v>-0.1388</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.0534</v>
+        <v>-3.7476</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4683</v>
+        <v>-0.3007</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.6441</v>
+        <v>-8.1189</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9062</v>
+        <v>1.0912</v>
       </c>
       <c r="J37" t="n">
-        <v>24.4674</v>
+        <v>29.4624</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4067</v>
+        <v>0.4985</v>
       </c>
       <c r="J38" t="n">
-        <v>10.9809</v>
+        <v>13.4595</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.225</v>
+        <v>0.3115</v>
       </c>
       <c r="J39" t="n">
-        <v>6.075</v>
+        <v>8.410500000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2376</v>
+        <v>-0.1306</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.4152</v>
+        <v>-3.5262</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.286</v>
+        <v>-0.1644</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.722</v>
+        <v>-4.4388</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.391</v>
+        <v>0.4507</v>
       </c>
       <c r="J42" t="n">
-        <v>14.076</v>
+        <v>16.2252</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1043</v>
+        <v>0.1126</v>
       </c>
       <c r="J43" t="n">
-        <v>3.7548</v>
+        <v>4.0536</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0218</v>
+        <v>0.0356</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.2816</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1812</v>
+        <v>-0.1022</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.5232</v>
+        <v>-3.6792</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2169</v>
+        <v>-0.1252</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.8084</v>
+        <v>-4.5072</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6933</v>
       </c>
       <c r="J47" t="n">
-        <v>26.0748</v>
+        <v>24.9588</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6504</v>
+        <v>0.6183</v>
       </c>
       <c r="J48" t="n">
-        <v>23.4144</v>
+        <v>22.2588</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0825</v>
+        <v>0.1166</v>
       </c>
       <c r="J49" t="n">
-        <v>2.97</v>
+        <v>4.1976</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.167</v>
+        <v>-0.1108</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.012</v>
+        <v>-3.9888</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4586</v>
+        <v>-0.3976</v>
       </c>
       <c r="J51" t="n">
-        <v>-16.5096</v>
+        <v>-14.3136</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4607</v>
+        <v>0.5313</v>
       </c>
       <c r="J52" t="n">
-        <v>12.4389</v>
+        <v>14.3451</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1269</v>
+        <v>0.1008</v>
       </c>
       <c r="J53" t="n">
-        <v>3.4263</v>
+        <v>2.7216</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2129</v>
+        <v>-0.1529</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.7483</v>
+        <v>-4.1283</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5448</v>
+        <v>-0.3576</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.7096</v>
+        <v>-9.655200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.673</v>
+        <v>-0.4507</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.171</v>
+        <v>-12.1689</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>1.58</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3484</v>
+        <v>1.2269</v>
       </c>
       <c r="J57" t="n">
-        <v>36.4068</v>
+        <v>33.1263</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>1.51</v>
       </c>
       <c r="I58" t="n">
-        <v>1.211</v>
+        <v>1.1396</v>
       </c>
       <c r="J58" t="n">
-        <v>32.697</v>
+        <v>30.7692</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3441</v>
+        <v>0.4231</v>
       </c>
       <c r="J59" t="n">
-        <v>9.290699999999999</v>
+        <v>11.4237</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.059</v>
+        <v>0.1368</v>
       </c>
       <c r="J60" t="n">
-        <v>1.593</v>
+        <v>3.6936</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>1.03</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0688</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.2268</v>
+        <v>1.8576</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2242</v>
+        <v>1.1424</v>
       </c>
       <c r="J62" t="n">
-        <v>30.605</v>
+        <v>28.56</v>
       </c>
     </row>
     <row r="63">
@@ -4863,10 +4863,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6313</v>
       </c>
       <c r="J64" t="n">
-        <v>15.5125</v>
+        <v>15.7825</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2957</v>
+        <v>0.3587</v>
       </c>
       <c r="J65" t="n">
-        <v>7.3925</v>
+        <v>8.967499999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.681</v>
+        <v>-0.6221</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.025</v>
+        <v>-15.5525</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2599</v>
+        <v>0.2715</v>
       </c>
       <c r="J67" t="n">
-        <v>6.4975</v>
+        <v>6.7875</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.1026</v>
+        <v>-0.081</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.565</v>
+        <v>-2.025</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>0.91</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.172</v>
+        <v>-0.1147</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.3</v>
+        <v>-2.8675</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1928</v>
+        <v>-0.1255</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.82</v>
+        <v>-3.1375</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4621</v>
+        <v>-0.2975</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.5525</v>
+        <v>-7.4375</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.82</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6301</v>
+        <v>1.4395</v>
       </c>
       <c r="J72" t="n">
-        <v>27.7117</v>
+        <v>24.4715</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.77</v>
       </c>
       <c r="I73" t="n">
-        <v>1.5391</v>
+        <v>1.3846</v>
       </c>
       <c r="J73" t="n">
-        <v>26.1647</v>
+        <v>23.5382</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.72</v>
       </c>
       <c r="I74" t="n">
-        <v>1.4447</v>
+        <v>1.3295</v>
       </c>
       <c r="J74" t="n">
-        <v>24.5599</v>
+        <v>22.6015</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1004</v>
+        <v>1.152</v>
       </c>
       <c r="J75" t="n">
-        <v>18.7068</v>
+        <v>19.584</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>1.34</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6562</v>
+        <v>0.7988</v>
       </c>
       <c r="J76" t="n">
-        <v>11.1554</v>
+        <v>13.5796</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>0.64</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3811</v>
+        <v>-0.3143</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.4787</v>
+        <v>-5.3431</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.62</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4119</v>
+        <v>-0.3352</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.0023</v>
+        <v>-5.6984</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.53</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5604</v>
+        <v>-0.4229</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.5268</v>
+        <v>-7.1893</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.742</v>
+        <v>-0.5139</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.614</v>
+        <v>-8.7363</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8417</v>
+        <v>-0.582</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.3089</v>
+        <v>-9.894</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3861</v>
+        <v>0.4333</v>
       </c>
       <c r="J82" t="n">
-        <v>9.6525</v>
+        <v>10.8325</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2444</v>
+        <v>0.2516</v>
       </c>
       <c r="J83" t="n">
-        <v>6.11</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1717</v>
+        <v>0.162</v>
       </c>
       <c r="J84" t="n">
-        <v>4.2925</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.75</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.433</v>
+        <v>-0.2776</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.825</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.49</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7645</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.1125</v>
+        <v>-12.9925</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3706</v>
+        <v>1.2365</v>
       </c>
       <c r="J87" t="n">
-        <v>34.265</v>
+        <v>30.9125</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6842</v>
+        <v>0.6828</v>
       </c>
       <c r="J88" t="n">
-        <v>17.105</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5524</v>
+        <v>0.5634</v>
       </c>
       <c r="J89" t="n">
-        <v>13.81</v>
+        <v>14.085</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.024</v>
+        <v>0.09</v>
       </c>
       <c r="J90" t="n">
-        <v>0.6</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.627</v>
+        <v>-0.5646</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.675</v>
+        <v>-14.115</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5183</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>12.9575</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.301</v>
+        <v>0.3213</v>
       </c>
       <c r="J93" t="n">
-        <v>7.525</v>
+        <v>8.032500000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2554</v>
+        <v>-0.1654</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.385</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4422</v>
+        <v>-0.285</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.055</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7738</v>
+        <v>-0.5269</v>
       </c>
       <c r="J96" t="n">
-        <v>-19.345</v>
+        <v>-13.1725</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1566</v>
+        <v>1.1006</v>
       </c>
       <c r="J97" t="n">
-        <v>28.915</v>
+        <v>27.515</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7134</v>
+        <v>0.7217</v>
       </c>
       <c r="J98" t="n">
-        <v>17.835</v>
+        <v>18.0425</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6365</v>
+        <v>0.652</v>
       </c>
       <c r="J99" t="n">
-        <v>15.9125</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3164</v>
+        <v>0.3825</v>
       </c>
       <c r="J100" t="n">
-        <v>7.91</v>
+        <v>9.5625</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3631</v>
+        <v>-0.2852</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.077500000000001</v>
+        <v>-7.13</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3215</v>
+        <v>0.3402</v>
       </c>
       <c r="J102" t="n">
-        <v>8.0375</v>
+        <v>8.505000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2387</v>
+        <v>0.2408</v>
       </c>
       <c r="J103" t="n">
-        <v>5.9675</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3336</v>
+        <v>-0.2147</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.34</v>
+        <v>-5.3675</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.75</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4244</v>
+        <v>-0.2737</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.61</v>
+        <v>-6.8425</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5748</v>
+        <v>-0.3785</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.37</v>
+        <v>-9.4625</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.6176</v>
       </c>
       <c r="J107" t="n">
-        <v>20.325</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.29</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7658</v>
+        <v>0.5905</v>
       </c>
       <c r="J108" t="n">
-        <v>19.145</v>
+        <v>14.7625</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4313</v>
+        <v>0.4242</v>
       </c>
       <c r="J109" t="n">
-        <v>10.7825</v>
+        <v>10.605</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3196</v>
+        <v>0.3634</v>
       </c>
       <c r="J110" t="n">
-        <v>7.99</v>
+        <v>9.085000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2914</v>
+        <v>0.3471</v>
       </c>
       <c r="J111" t="n">
-        <v>7.285</v>
+        <v>8.6775</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>0.99</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0299</v>
+        <v>-0.0055</v>
       </c>
       <c r="J112" t="n">
-        <v>0.8073</v>
+        <v>-0.1485</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>0.0046</v>
+        <v>-0.0217</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1242</v>
+        <v>-0.5859</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0603</v>
+        <v>-0.0631</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.6281</v>
+        <v>-1.7037</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1571</v>
+        <v>-0.1219</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.2417</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6987</v>
+        <v>-0.4698</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.8649</v>
+        <v>-12.6846</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.7703</v>
+        <v>1.2602</v>
       </c>
       <c r="J117" t="n">
-        <v>47.7981</v>
+        <v>34.0254</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>1.27</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.5574</v>
       </c>
       <c r="J118" t="n">
-        <v>18.441</v>
+        <v>15.0498</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4815</v>
+        <v>0.4622</v>
       </c>
       <c r="J119" t="n">
-        <v>13.0005</v>
+        <v>12.4794</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>1.08</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1553</v>
+        <v>0.2324</v>
       </c>
       <c r="J120" t="n">
-        <v>4.1931</v>
+        <v>6.2748</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5443</v>
+        <v>-0.473</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.6961</v>
+        <v>-12.771</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2494</v>
+        <v>0.8783</v>
       </c>
       <c r="J122" t="n">
-        <v>37.482</v>
+        <v>26.349</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.5342</v>
       </c>
       <c r="J123" t="n">
-        <v>21.546</v>
+        <v>16.026</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1588</v>
+        <v>-0.1295</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.764</v>
+        <v>-3.885</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.8588</v>
+        <v>-0.8237</v>
       </c>
       <c r="J125" t="n">
-        <v>-25.764</v>
+        <v>-24.711</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0807</v>
+        <v>-1.0672</v>
       </c>
       <c r="J126" t="n">
-        <v>-32.421</v>
+        <v>-32.016</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6146</v>
       </c>
       <c r="J127" t="n">
-        <v>19.764</v>
+        <v>18.438</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3147</v>
+        <v>0.3577</v>
       </c>
       <c r="J128" t="n">
-        <v>9.441000000000001</v>
+        <v>10.731</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.083</v>
+        <v>-0.0309</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.49</v>
+        <v>-0.927</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>0.97</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1296</v>
+        <v>-0.061</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.888</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1296</v>
+        <v>-0.061</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.888</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9271</v>
+        <v>0.6905</v>
       </c>
       <c r="J132" t="n">
-        <v>23.1775</v>
+        <v>17.2625</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>1.37</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9271</v>
+        <v>0.6905</v>
       </c>
       <c r="J133" t="n">
-        <v>23.1775</v>
+        <v>17.2625</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>1.29</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7405</v>
+        <v>0.5849</v>
       </c>
       <c r="J134" t="n">
-        <v>18.5125</v>
+        <v>14.6225</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4069</v>
+        <v>0.4194</v>
       </c>
       <c r="J135" t="n">
-        <v>10.1725</v>
+        <v>10.485</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.0388</v>
+        <v>0.0365</v>
       </c>
       <c r="J136" t="n">
-        <v>-0.97</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1892</v>
+        <v>0.184</v>
       </c>
       <c r="J137" t="n">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.01</v>
       </c>
       <c r="I138" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="J138" t="n">
-        <v>2.0275</v>
+        <v>1.3875</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2304</v>
+        <v>-0.1468</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.76</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2821</v>
+        <v>-0.1781</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.0525</v>
+        <v>-4.4525</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3908</v>
+        <v>-0.2487</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.77</v>
+        <v>-6.2175</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1686</v>
+        <v>0.1521</v>
       </c>
       <c r="J142" t="n">
-        <v>4.5522</v>
+        <v>4.1067</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1252</v>
+        <v>0.0994</v>
       </c>
       <c r="J143" t="n">
-        <v>3.3804</v>
+        <v>2.6838</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2784</v>
+        <v>-0.1832</v>
       </c>
       <c r="J144" t="n">
-        <v>-7.5168</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4351</v>
+        <v>-0.2818</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.7477</v>
+        <v>-7.6086</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.71</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4777</v>
+        <v>-0.3107</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.8979</v>
+        <v>-8.3889</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0618</v>
+        <v>1.043</v>
       </c>
       <c r="J147" t="n">
-        <v>28.6686</v>
+        <v>28.161</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8878</v>
+        <v>0.8973</v>
       </c>
       <c r="J148" t="n">
-        <v>23.9706</v>
+        <v>24.2271</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J149" t="n">
-        <v>14.8122</v>
+        <v>16.2675</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3043</v>
+        <v>0.377</v>
       </c>
       <c r="J150" t="n">
-        <v>8.216100000000001</v>
+        <v>10.179</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.0368</v>
+        <v>0.1109</v>
       </c>
       <c r="J151" t="n">
-        <v>0.9936</v>
+        <v>2.9943</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.67</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.7773</v>
       </c>
       <c r="J152" t="n">
-        <v>19.6719</v>
+        <v>17.8779</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.33</v>
       </c>
       <c r="I153" t="n">
-        <v>0.443</v>
+        <v>0.4193</v>
       </c>
       <c r="J153" t="n">
-        <v>10.189</v>
+        <v>9.6439</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4099</v>
+        <v>0.3977</v>
       </c>
       <c r="J154" t="n">
-        <v>9.4277</v>
+        <v>9.1471</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2687</v>
+        <v>0.2814</v>
       </c>
       <c r="J155" t="n">
-        <v>6.1801</v>
+        <v>6.4722</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>1.13</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1524</v>
+        <v>0.1786</v>
       </c>
       <c r="J156" t="n">
-        <v>3.5052</v>
+        <v>4.1078</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3359</v>
+        <v>0.2772</v>
       </c>
       <c r="J157" t="n">
-        <v>7.7257</v>
+        <v>6.3756</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1417</v>
+        <v>-0.1236</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.2591</v>
+        <v>-2.8428</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>0.76</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3806</v>
+        <v>-0.2541</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.7538</v>
+        <v>-5.8443</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3965</v>
+        <v>-0.2637</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.1195</v>
+        <v>-6.0651</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.51</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7234</v>
+        <v>-0.489</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.6382</v>
+        <v>-11.247</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5861</v>
+        <v>0.7075</v>
       </c>
       <c r="J162" t="n">
-        <v>17.583</v>
+        <v>21.225</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.04</v>
       </c>
       <c r="I163" t="n">
-        <v>0.0969</v>
+        <v>0.111</v>
       </c>
       <c r="J163" t="n">
-        <v>2.907</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0149</v>
+        <v>0.034</v>
       </c>
       <c r="J164" t="n">
-        <v>0.447</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.203</v>
+        <v>-0.1151</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.09</v>
+        <v>-3.453</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3472</v>
+        <v>-0.2123</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.416</v>
+        <v>-6.369</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.0864</v>
+        <v>1.045</v>
       </c>
       <c r="J167" t="n">
-        <v>32.592</v>
+        <v>31.35</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3164</v>
+        <v>0.3012</v>
       </c>
       <c r="J168" t="n">
-        <v>9.492000000000001</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>1.03</v>
       </c>
       <c r="I169" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1175</v>
       </c>
       <c r="J169" t="n">
-        <v>2.565</v>
+        <v>3.525</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2401</v>
+        <v>-0.1817</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.203</v>
+        <v>-5.451</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.85</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5653</v>
+        <v>-0.5077</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.959</v>
+        <v>-15.231</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2181</v>
+        <v>1.1367</v>
       </c>
       <c r="J172" t="n">
-        <v>35.3249</v>
+        <v>32.9643</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4012</v>
+        <v>0.4433</v>
       </c>
       <c r="J173" t="n">
-        <v>11.6348</v>
+        <v>12.8557</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.09</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2233</v>
+        <v>0.2815</v>
       </c>
       <c r="J174" t="n">
-        <v>6.4757</v>
+        <v>8.163500000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1303</v>
+        <v>0.192</v>
       </c>
       <c r="J175" t="n">
-        <v>3.7787</v>
+        <v>5.568</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0977</v>
+        <v>0.1602</v>
       </c>
       <c r="J176" t="n">
-        <v>2.8333</v>
+        <v>4.6458</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>1.38</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6302</v>
+        <v>0.7658</v>
       </c>
       <c r="J177" t="n">
-        <v>18.2758</v>
+        <v>22.2082</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2031</v>
+        <v>0.2114</v>
       </c>
       <c r="J178" t="n">
-        <v>5.8899</v>
+        <v>6.1306</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3017</v>
+        <v>-0.1849</v>
       </c>
       <c r="J179" t="n">
-        <v>-8.7493</v>
+        <v>-5.3621</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3326</v>
+        <v>-0.2056</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.6454</v>
+        <v>-5.9624</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.73</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4754</v>
+        <v>-0.3046</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.7866</v>
+        <v>-8.833399999999999</v>
       </c>
     </row>
     <row r="182">
@@ -9583,10 +9583,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.265</v>
+        <v>1.1685</v>
       </c>
       <c r="J182" t="n">
-        <v>37.95</v>
+        <v>35.055</v>
       </c>
     </row>
     <row r="183">
@@ -9623,10 +9623,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1646</v>
+        <v>1.1043</v>
       </c>
       <c r="J183" t="n">
-        <v>34.938</v>
+        <v>33.129</v>
       </c>
     </row>
     <row r="184">
@@ -9663,10 +9663,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3252</v>
+        <v>0.386</v>
       </c>
       <c r="J184" t="n">
-        <v>9.756</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="185">
@@ -9703,10 +9703,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3884</v>
+        <v>-0.3124</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.652</v>
+        <v>-9.372</v>
       </c>
     </row>
     <row r="186">
@@ -9743,10 +9743,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4178</v>
+        <v>-0.3429</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.534</v>
+        <v>-10.287</v>
       </c>
     </row>
     <row r="187">
@@ -9783,10 +9783,10 @@
         <v>1.12</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2807</v>
+        <v>0.3019</v>
       </c>
       <c r="J187" t="n">
-        <v>8.420999999999999</v>
+        <v>9.057</v>
       </c>
     </row>
     <row r="188">
@@ -9823,10 +9823,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2132</v>
+        <v>0.2186</v>
       </c>
       <c r="J188" t="n">
-        <v>6.396</v>
+        <v>6.558</v>
       </c>
     </row>
     <row r="189">
@@ -9863,10 +9863,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1713</v>
+        <v>-0.1063</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.139</v>
+        <v>-3.189</v>
       </c>
     </row>
     <row r="190">
@@ -9903,10 +9903,10 @@
         <v>0.88</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.244</v>
+        <v>-0.1503</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.32</v>
+        <v>-4.509</v>
       </c>
     </row>
     <row r="191">
@@ -9943,10 +9943,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.456</v>
+        <v>-0.2918</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.68</v>
+        <v>-8.754</v>
       </c>
     </row>
     <row r="192">
@@ -9983,10 +9983,10 @@
         <v>0.84</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1778</v>
+        <v>-0.1586</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.556</v>
+        <v>-3.172</v>
       </c>
     </row>
     <row r="193">
@@ -10023,10 +10023,10 @@
         <v>0.73</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.3578</v>
+        <v>-0.271</v>
       </c>
       <c r="J193" t="n">
-        <v>-7.156</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="194">
@@ -10063,10 +10063,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.4204</v>
+        <v>-0.2979</v>
       </c>
       <c r="J194" t="n">
-        <v>-8.407999999999999</v>
+        <v>-5.958</v>
       </c>
     </row>
     <row r="195">
@@ -10103,10 +10103,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4394</v>
+        <v>-0.3069</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.788</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="196">
@@ -10143,10 +10143,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6204</v>
+        <v>-0.4183</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.408</v>
+        <v>-8.366</v>
       </c>
     </row>
     <row r="197">
@@ -10183,10 +10183,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>1.2942</v>
+        <v>0.9346</v>
       </c>
       <c r="J197" t="n">
-        <v>25.884</v>
+        <v>18.692</v>
       </c>
     </row>
     <row r="198">
@@ -10223,10 +10223,10 @@
         <v>1.57</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2547</v>
+        <v>0.9109</v>
       </c>
       <c r="J198" t="n">
-        <v>25.094</v>
+        <v>18.218</v>
       </c>
     </row>
     <row r="199">
@@ -10263,10 +10263,10 @@
         <v>1.46</v>
       </c>
       <c r="I199" t="n">
-        <v>1.024</v>
+        <v>0.7793</v>
       </c>
       <c r="J199" t="n">
-        <v>20.48</v>
+        <v>15.586</v>
       </c>
     </row>
     <row r="200">
@@ -10303,10 +10303,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.893</v>
+        <v>0.7199</v>
       </c>
       <c r="J200" t="n">
-        <v>17.86</v>
+        <v>14.398</v>
       </c>
     </row>
     <row r="201">
@@ -10343,10 +10343,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1295</v>
+        <v>0.2229</v>
       </c>
       <c r="J201" t="n">
-        <v>2.59</v>
+        <v>4.458</v>
       </c>
     </row>
     <row r="202">
@@ -10383,10 +10383,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4282</v>
+        <v>0.4291</v>
       </c>
       <c r="J202" t="n">
-        <v>11.5614</v>
+        <v>11.5857</v>
       </c>
     </row>
     <row r="203">
@@ -10423,10 +10423,10 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3416</v>
+        <v>0.364</v>
       </c>
       <c r="J203" t="n">
-        <v>9.2232</v>
+        <v>9.827999999999999</v>
       </c>
     </row>
     <row r="204">
@@ -10463,10 +10463,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1118</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>-3.0186</v>
+        <v>-1.6929</v>
       </c>
     </row>
     <row r="205">
@@ -10503,10 +10503,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1906</v>
+        <v>-0.111</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.1462</v>
+        <v>-2.997</v>
       </c>
     </row>
     <row r="206">
@@ -10543,10 +10543,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5322</v>
+        <v>-0.345</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.3694</v>
+        <v>-9.315</v>
       </c>
     </row>
     <row r="207">
@@ -10583,10 +10583,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1141</v>
+        <v>0.7968</v>
       </c>
       <c r="J207" t="n">
-        <v>30.0807</v>
+        <v>21.5136</v>
       </c>
     </row>
     <row r="208">
@@ -10623,10 +10623,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.4982</v>
       </c>
       <c r="J208" t="n">
-        <v>16.5078</v>
+        <v>13.4514</v>
       </c>
     </row>
     <row r="209">
@@ -10663,10 +10663,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5847</v>
+        <v>0.4841</v>
       </c>
       <c r="J209" t="n">
-        <v>15.7869</v>
+        <v>13.0707</v>
       </c>
     </row>
     <row r="210">
@@ -10703,10 +10703,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5574</v>
+        <v>0.4698</v>
       </c>
       <c r="J210" t="n">
-        <v>15.0498</v>
+        <v>12.6846</v>
       </c>
     </row>
     <row r="211">
@@ -10743,10 +10743,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7466</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.1582</v>
+        <v>-18.7407</v>
       </c>
     </row>
     <row r="212">
@@ -10783,10 +10783,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6334</v>
+        <v>0.4959</v>
       </c>
       <c r="J212" t="n">
-        <v>18.3686</v>
+        <v>14.3811</v>
       </c>
     </row>
     <row r="213">
@@ -10823,10 +10823,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5819</v>
+        <v>0.4663</v>
       </c>
       <c r="J213" t="n">
-        <v>16.8751</v>
+        <v>13.5227</v>
       </c>
     </row>
     <row r="214">
@@ -10863,10 +10863,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4445</v>
+        <v>0.3905</v>
       </c>
       <c r="J214" t="n">
-        <v>12.8905</v>
+        <v>11.3245</v>
       </c>
     </row>
     <row r="215">
@@ -10903,10 +10903,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1712</v>
+        <v>0.2084</v>
       </c>
       <c r="J215" t="n">
-        <v>4.9648</v>
+        <v>6.0436</v>
       </c>
     </row>
     <row r="216">
@@ -10943,10 +10943,10 @@
         <v>0.89</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4697</v>
+        <v>-0.4055</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.6213</v>
+        <v>-11.7595</v>
       </c>
     </row>
     <row r="217">
@@ -10983,10 +10983,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8099</v>
+        <v>0.7378</v>
       </c>
       <c r="J217" t="n">
-        <v>23.4871</v>
+        <v>21.3962</v>
       </c>
     </row>
     <row r="218">
@@ -11023,10 +11023,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.2099</v>
+        <v>-0.1228</v>
       </c>
       <c r="J218" t="n">
-        <v>-6.0871</v>
+        <v>-3.5612</v>
       </c>
     </row>
     <row r="219">
@@ -11063,10 +11063,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2607</v>
+        <v>-0.1559</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.5603</v>
+        <v>-4.5211</v>
       </c>
     </row>
     <row r="220">
@@ -11103,10 +11103,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2929</v>
+        <v>-0.1772</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.4941</v>
+        <v>-5.1388</v>
       </c>
     </row>
     <row r="221">
@@ -11143,10 +11143,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3831</v>
+        <v>-0.2388</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.1099</v>
+        <v>-6.9252</v>
       </c>
     </row>
     <row r="222">
@@ -11183,10 +11183,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2355</v>
+        <v>0.8723</v>
       </c>
       <c r="J222" t="n">
-        <v>51.891</v>
+        <v>36.6366</v>
       </c>
     </row>
     <row r="223">
@@ -11223,10 +11223,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.9198</v>
+        <v>0.672</v>
       </c>
       <c r="J223" t="n">
-        <v>38.6316</v>
+        <v>28.224</v>
       </c>
     </row>
     <row r="224">
@@ -11263,10 +11263,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3384</v>
+        <v>0.3561</v>
       </c>
       <c r="J224" t="n">
-        <v>14.2128</v>
+        <v>14.9562</v>
       </c>
     </row>
     <row r="225">
@@ -11303,10 +11303,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3047</v>
+        <v>-0.2333</v>
       </c>
       <c r="J225" t="n">
-        <v>-12.7974</v>
+        <v>-9.7986</v>
       </c>
     </row>
     <row r="226">
@@ -11343,10 +11343,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7835</v>
+        <v>-0.7356</v>
       </c>
       <c r="J226" t="n">
-        <v>-32.907</v>
+        <v>-30.8952</v>
       </c>
     </row>
     <row r="227">
@@ -11383,10 +11383,10 @@
         <v>1.17</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3574</v>
+        <v>0.3726</v>
       </c>
       <c r="J227" t="n">
-        <v>15.0108</v>
+        <v>15.6492</v>
       </c>
     </row>
     <row r="228">
@@ -11423,10 +11423,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0794</v>
+        <v>-0.0594</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.3348</v>
+        <v>-2.4948</v>
       </c>
     </row>
     <row r="229">
@@ -11463,10 +11463,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1914</v>
+        <v>-0.1177</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.0388</v>
+        <v>-4.9434</v>
       </c>
     </row>
     <row r="230">
@@ -11503,10 +11503,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2781</v>
+        <v>-0.1717</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.6802</v>
+        <v>-7.2114</v>
       </c>
     </row>
     <row r="231">
@@ -11543,10 +11543,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2943</v>
+        <v>-0.1821</v>
       </c>
       <c r="J231" t="n">
-        <v>-12.3606</v>
+        <v>-7.6482</v>
       </c>
     </row>
     <row r="232">
@@ -11583,10 +11583,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7722</v>
+        <v>1.2751</v>
       </c>
       <c r="J232" t="n">
-        <v>35.444</v>
+        <v>25.502</v>
       </c>
     </row>
     <row r="233">
@@ -11623,10 +11623,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>1.321</v>
+        <v>0.9734</v>
       </c>
       <c r="J233" t="n">
-        <v>26.42</v>
+        <v>19.468</v>
       </c>
     </row>
     <row r="234">
@@ -11663,10 +11663,10 @@
         <v>1.55</v>
       </c>
       <c r="I234" t="n">
-        <v>1.1145</v>
+        <v>0.8726</v>
       </c>
       <c r="J234" t="n">
-        <v>22.29</v>
+        <v>17.452</v>
       </c>
     </row>
     <row r="235">
@@ -11703,10 +11703,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.6796</v>
       </c>
       <c r="J235" t="n">
-        <v>15.594</v>
+        <v>13.592</v>
       </c>
     </row>
     <row r="236">
@@ -11743,10 +11743,10 @@
         <v>1.38</v>
       </c>
       <c r="I236" t="n">
-        <v>0.7589</v>
+        <v>0.6669</v>
       </c>
       <c r="J236" t="n">
-        <v>15.178</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="237">
@@ -11783,10 +11783,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1783</v>
+        <v>-0.1664</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.566</v>
+        <v>-3.328</v>
       </c>
     </row>
     <row r="238">
@@ -11823,10 +11823,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2553</v>
+        <v>-0.2237</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.106</v>
+        <v>-4.474</v>
       </c>
     </row>
     <row r="239">
@@ -11863,10 +11863,10 @@
         <v>0.58</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4881</v>
+        <v>-0.3803</v>
       </c>
       <c r="J239" t="n">
-        <v>-9.762</v>
+        <v>-7.606</v>
       </c>
     </row>
     <row r="240">
@@ -11903,10 +11903,10 @@
         <v>0.33</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.6153</v>
       </c>
       <c r="J240" t="n">
-        <v>-17.752</v>
+        <v>-12.306</v>
       </c>
     </row>
     <row r="241">
@@ -11943,10 +11943,10 @@
         <v>0.25</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.9901</v>
+        <v>-0.6947</v>
       </c>
       <c r="J241" t="n">
-        <v>-19.802</v>
+        <v>-13.894</v>
       </c>
     </row>
     <row r="242">
@@ -11983,10 +11983,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4462</v>
+        <v>1.0119</v>
       </c>
       <c r="J242" t="n">
-        <v>37.6012</v>
+        <v>26.3094</v>
       </c>
     </row>
     <row r="243">
@@ -12023,10 +12023,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.6817</v>
+        <v>0.5312</v>
       </c>
       <c r="J243" t="n">
-        <v>17.7242</v>
+        <v>13.8112</v>
       </c>
     </row>
     <row r="244">
@@ -12063,10 +12063,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.525</v>
+        <v>0.4447</v>
       </c>
       <c r="J244" t="n">
-        <v>13.65</v>
+        <v>11.5622</v>
       </c>
     </row>
     <row r="245">
@@ -12103,10 +12103,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.176</v>
+        <v>0.2288</v>
       </c>
       <c r="J245" t="n">
-        <v>4.576</v>
+        <v>5.9488</v>
       </c>
     </row>
     <row r="246">
@@ -12143,10 +12143,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-1.1129</v>
+        <v>-1.1026</v>
       </c>
       <c r="J246" t="n">
-        <v>-28.9354</v>
+        <v>-28.6676</v>
       </c>
     </row>
     <row r="247">
@@ -12183,10 +12183,10 @@
         <v>1.36</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5913</v>
+        <v>0.5577</v>
       </c>
       <c r="J247" t="n">
-        <v>15.3738</v>
+        <v>14.5002</v>
       </c>
     </row>
     <row r="248">
@@ -12223,10 +12223,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1675</v>
+        <v>0.1802</v>
       </c>
       <c r="J248" t="n">
-        <v>4.355</v>
+        <v>4.6852</v>
       </c>
     </row>
     <row r="249">
@@ -12263,10 +12263,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1279</v>
+        <v>0.1363</v>
       </c>
       <c r="J249" t="n">
-        <v>3.3254</v>
+        <v>3.5438</v>
       </c>
     </row>
     <row r="250">
@@ -12303,10 +12303,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2328</v>
+        <v>-0.136</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.0528</v>
+        <v>-3.536</v>
       </c>
     </row>
     <row r="251">
@@ -12343,10 +12343,10 @@
         <v>0.7</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5231</v>
+        <v>-0.338</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.6006</v>
+        <v>-8.788</v>
       </c>
     </row>
     <row r="252">
@@ -12383,10 +12383,10 @@
         <v>1.85</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0051</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>19.0969</v>
+        <v>13.015</v>
       </c>
     </row>
     <row r="253">
@@ -12423,10 +12423,10 @@
         <v>1.67</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8186</v>
+        <v>0.5814</v>
       </c>
       <c r="J253" t="n">
-        <v>15.5534</v>
+        <v>11.0466</v>
       </c>
     </row>
     <row r="254">
@@ -12463,10 +12463,10 @@
         <v>1.62</v>
       </c>
       <c r="I254" t="n">
-        <v>0.7637</v>
+        <v>0.5522</v>
       </c>
       <c r="J254" t="n">
-        <v>14.5103</v>
+        <v>10.4918</v>
       </c>
     </row>
     <row r="255">
@@ -12503,10 +12503,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2921</v>
+        <v>0.3137</v>
       </c>
       <c r="J255" t="n">
-        <v>5.5499</v>
+        <v>5.9603</v>
       </c>
     </row>
     <row r="256">
@@ -12543,10 +12543,10 @@
         <v>0.99</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1467</v>
+        <v>-0.0635</v>
       </c>
       <c r="J256" t="n">
-        <v>-2.7873</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="257">
@@ -12583,10 +12583,10 @@
         <v>0.82</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1534</v>
+        <v>-0.1477</v>
       </c>
       <c r="J257" t="n">
-        <v>-2.9146</v>
+        <v>-2.8063</v>
       </c>
     </row>
     <row r="258">
@@ -12623,10 +12623,10 @@
         <v>0.76</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2473</v>
+        <v>-0.215</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.6987</v>
+        <v>-4.085</v>
       </c>
     </row>
     <row r="259">
@@ -12663,10 +12663,10 @@
         <v>0.6</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.5085</v>
+        <v>-0.3736</v>
       </c>
       <c r="J259" t="n">
-        <v>-9.6615</v>
+        <v>-7.0984</v>
       </c>
     </row>
     <row r="260">
@@ -12703,10 +12703,10 @@
         <v>0.43</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.7744</v>
+        <v>-0.5309</v>
       </c>
       <c r="J260" t="n">
-        <v>-14.7136</v>
+        <v>-10.0871</v>
       </c>
     </row>
     <row r="261">
@@ -12743,10 +12743,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8399</v>
+        <v>-0.5788</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.9581</v>
+        <v>-10.9972</v>
       </c>
     </row>
     <row r="262">
@@ -12783,10 +12783,10 @@
         <v>0.91</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1328</v>
+        <v>-0.1095</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.1872</v>
+        <v>-2.628</v>
       </c>
     </row>
     <row r="263">
@@ -12823,10 +12823,10 @@
         <v>0.89</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1704</v>
+        <v>-0.1316</v>
       </c>
       <c r="J263" t="n">
-        <v>-4.0896</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="264">
@@ -12863,10 +12863,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2094</v>
+        <v>-0.1526</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.0256</v>
+        <v>-3.6624</v>
       </c>
     </row>
     <row r="265">
@@ -12903,10 +12903,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2094</v>
+        <v>-0.1526</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.0256</v>
+        <v>-3.6624</v>
       </c>
     </row>
     <row r="266">
@@ -12943,10 +12943,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3882</v>
+        <v>-0.2516</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.316800000000001</v>
+        <v>-6.0384</v>
       </c>
     </row>
     <row r="267">
@@ -12983,10 +12983,10 @@
         <v>1.64</v>
       </c>
       <c r="I267" t="n">
-        <v>1.4577</v>
+        <v>1.0245</v>
       </c>
       <c r="J267" t="n">
-        <v>34.9848</v>
+        <v>24.588</v>
       </c>
     </row>
     <row r="268">
@@ -13023,10 +13023,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>1.1043</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J268" t="n">
-        <v>26.5032</v>
+        <v>19.2216</v>
       </c>
     </row>
     <row r="269">
@@ -13063,10 +13063,10 @@
         <v>1.31</v>
       </c>
       <c r="I269" t="n">
-        <v>0.7695</v>
+        <v>0.6078</v>
       </c>
       <c r="J269" t="n">
-        <v>18.468</v>
+        <v>14.5872</v>
       </c>
     </row>
     <row r="270">
@@ -13103,10 +13103,10 @@
         <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1481</v>
+        <v>-0.0667</v>
       </c>
       <c r="J270" t="n">
-        <v>-3.5544</v>
+        <v>-1.6008</v>
       </c>
     </row>
     <row r="271">
@@ -13143,10 +13143,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3185</v>
+        <v>-0.2351</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.644</v>
+        <v>-5.6424</v>
       </c>
     </row>
     <row r="272">
@@ -13183,10 +13183,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4998</v>
+        <v>0.4858</v>
       </c>
       <c r="J272" t="n">
-        <v>14.994</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="273">
@@ -13223,10 +13223,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1454</v>
+        <v>0.1574</v>
       </c>
       <c r="J273" t="n">
-        <v>4.362</v>
+        <v>4.722</v>
       </c>
     </row>
     <row r="274">
@@ -13263,10 +13263,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1249</v>
+        <v>0.1352</v>
       </c>
       <c r="J274" t="n">
-        <v>3.747</v>
+        <v>4.056</v>
       </c>
     </row>
     <row r="275">
@@ -13303,10 +13303,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2512</v>
+        <v>-0.1477</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.536</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="276">
@@ -13343,10 +13343,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3596</v>
+        <v>-0.2214</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.788</v>
+        <v>-6.642</v>
       </c>
     </row>
     <row r="277">
@@ -13383,10 +13383,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8733</v>
+        <v>0.6395</v>
       </c>
       <c r="J277" t="n">
-        <v>26.199</v>
+        <v>19.185</v>
       </c>
     </row>
     <row r="278">
@@ -13423,10 +13423,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.4963</v>
       </c>
       <c r="J278" t="n">
-        <v>19.038</v>
+        <v>14.889</v>
       </c>
     </row>
     <row r="279">
@@ -13463,10 +13463,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.1727</v>
+        <v>0.2089</v>
       </c>
       <c r="J279" t="n">
-        <v>5.181</v>
+        <v>6.267</v>
       </c>
     </row>
     <row r="280">
@@ -13503,10 +13503,10 @@
         <v>1.05</v>
       </c>
       <c r="I280" t="n">
-        <v>0.138</v>
+        <v>0.1775</v>
       </c>
       <c r="J280" t="n">
-        <v>4.14</v>
+        <v>5.325</v>
       </c>
     </row>
     <row r="281">
@@ -13543,10 +13543,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5762</v>
+        <v>-0.5161</v>
       </c>
       <c r="J281" t="n">
-        <v>-17.286</v>
+        <v>-15.483</v>
       </c>
     </row>
     <row r="282">
@@ -13583,10 +13583,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5409</v>
+        <v>1.0881</v>
       </c>
       <c r="J282" t="n">
-        <v>32.3589</v>
+        <v>22.8501</v>
       </c>
     </row>
     <row r="283">
@@ -13623,10 +13623,10 @@
         <v>1.67</v>
       </c>
       <c r="I283" t="n">
-        <v>1.4487</v>
+        <v>1.0297</v>
       </c>
       <c r="J283" t="n">
-        <v>30.4227</v>
+        <v>21.6237</v>
       </c>
     </row>
     <row r="284">
@@ -13663,10 +13663,10 @@
         <v>1.47</v>
       </c>
       <c r="I284" t="n">
-        <v>1.0489</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="J284" t="n">
-        <v>22.0269</v>
+        <v>16.6278</v>
       </c>
     </row>
     <row r="285">
@@ -13703,10 +13703,10 @@
         <v>1.15</v>
       </c>
       <c r="I285" t="n">
-        <v>0.2878</v>
+        <v>0.3662</v>
       </c>
       <c r="J285" t="n">
-        <v>6.0438</v>
+        <v>7.6902</v>
       </c>
     </row>
     <row r="286">
@@ -13743,10 +13743,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1305</v>
+        <v>0.2237</v>
       </c>
       <c r="J286" t="n">
-        <v>2.7405</v>
+        <v>4.6977</v>
       </c>
     </row>
     <row r="287">
@@ -13783,10 +13783,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3792</v>
+        <v>0.3902</v>
       </c>
       <c r="J287" t="n">
-        <v>7.9632</v>
+        <v>8.1942</v>
       </c>
     </row>
     <row r="288">
@@ -13823,10 +13823,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.3386</v>
+        <v>-0.2661</v>
       </c>
       <c r="J288" t="n">
-        <v>-7.1106</v>
+        <v>-5.5881</v>
       </c>
     </row>
     <row r="289">
@@ -13863,10 +13863,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.4039</v>
       </c>
       <c r="J289" t="n">
-        <v>-12.5013</v>
+        <v>-8.4819</v>
       </c>
     </row>
     <row r="290">
@@ -13903,10 +13903,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.7052</v>
+        <v>-0.4788</v>
       </c>
       <c r="J290" t="n">
-        <v>-14.8092</v>
+        <v>-10.0548</v>
       </c>
     </row>
     <row r="291">
@@ -13943,10 +13943,10 @@
         <v>0.46</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7573</v>
+        <v>-0.5163</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.9033</v>
+        <v>-10.8423</v>
       </c>
     </row>
     <row r="292">
@@ -13983,10 +13983,10 @@
         <v>2.23</v>
       </c>
       <c r="I292" t="n">
-        <v>2.0683</v>
+        <v>1.6345</v>
       </c>
       <c r="J292" t="n">
-        <v>37.2294</v>
+        <v>29.421</v>
       </c>
     </row>
     <row r="293">
@@ -14023,10 +14023,10 @@
         <v>2.23</v>
       </c>
       <c r="I293" t="n">
-        <v>2.0683</v>
+        <v>1.6345</v>
       </c>
       <c r="J293" t="n">
-        <v>37.2294</v>
+        <v>29.421</v>
       </c>
     </row>
     <row r="294">
@@ -14063,10 +14063,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2353</v>
+        <v>0.3356</v>
       </c>
       <c r="J294" t="n">
-        <v>4.2354</v>
+        <v>6.0408</v>
       </c>
     </row>
     <row r="295">
@@ -14103,10 +14103,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2102</v>
+        <v>0.3131</v>
       </c>
       <c r="J295" t="n">
-        <v>3.7836</v>
+        <v>5.6358</v>
       </c>
     </row>
     <row r="296">
@@ -14143,10 +14143,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5468</v>
+        <v>-0.4718</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.8424</v>
+        <v>-8.4924</v>
       </c>
     </row>
     <row r="297">
@@ -14183,10 +14183,10 @@
         <v>0.65</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.4372</v>
+        <v>-0.3328</v>
       </c>
       <c r="J297" t="n">
-        <v>-7.8696</v>
+        <v>-5.9904</v>
       </c>
     </row>
     <row r="298">
@@ -14223,10 +14223,10 @@
         <v>0.65</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.4372</v>
+        <v>-0.3328</v>
       </c>
       <c r="J298" t="n">
-        <v>-7.8696</v>
+        <v>-5.9904</v>
       </c>
     </row>
     <row r="299">
@@ -14263,10 +14263,10 @@
         <v>0.62</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.5</v>
+        <v>-0.3592</v>
       </c>
       <c r="J299" t="n">
-        <v>-9</v>
+        <v>-6.4656</v>
       </c>
     </row>
     <row r="300">
@@ -14303,10 +14303,10 @@
         <v>0.6</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5375</v>
+        <v>-0.3768</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.675000000000001</v>
+        <v>-6.7824</v>
       </c>
     </row>
     <row r="301">
@@ -14343,10 +14343,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5375</v>
+        <v>-0.3768</v>
       </c>
       <c r="J301" t="n">
-        <v>-9.675000000000001</v>
+        <v>-6.7824</v>
       </c>
     </row>
     <row r="302">
@@ -14383,10 +14383,10 @@
         <v>1.82</v>
       </c>
       <c r="I302" t="n">
-        <v>1.694</v>
+        <v>1.1943</v>
       </c>
       <c r="J302" t="n">
-        <v>33.88</v>
+        <v>23.886</v>
       </c>
     </row>
     <row r="303">
@@ -14423,10 +14423,10 @@
         <v>1.73</v>
       </c>
       <c r="I303" t="n">
-        <v>1.5398</v>
+        <v>1.0913</v>
       </c>
       <c r="J303" t="n">
-        <v>30.796</v>
+        <v>21.826</v>
       </c>
     </row>
     <row r="304">
@@ -14463,10 +14463,10 @@
         <v>1.5</v>
       </c>
       <c r="I304" t="n">
-        <v>1.087</v>
+        <v>0.8228</v>
       </c>
       <c r="J304" t="n">
-        <v>21.74</v>
+        <v>16.456</v>
       </c>
     </row>
     <row r="305">
@@ -14503,10 +14503,10 @@
         <v>1.14</v>
       </c>
       <c r="I305" t="n">
-        <v>0.25</v>
+        <v>0.3442</v>
       </c>
       <c r="J305" t="n">
-        <v>5</v>
+        <v>6.884</v>
       </c>
     </row>
     <row r="306">
@@ -14543,10 +14543,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.25</v>
+        <v>0.3442</v>
       </c>
       <c r="J306" t="n">
-        <v>5</v>
+        <v>6.884</v>
       </c>
     </row>
     <row r="307">
@@ -14583,10 +14583,10 @@
         <v>0.85</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1269</v>
+        <v>-0.1275</v>
       </c>
       <c r="J307" t="n">
-        <v>-2.538</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="308">
@@ -14623,10 +14623,10 @@
         <v>0.72</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3322</v>
+        <v>-0.268</v>
       </c>
       <c r="J308" t="n">
-        <v>-6.644</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="309">
@@ -14663,10 +14663,10 @@
         <v>0.66</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4304</v>
+        <v>-0.3259</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.608000000000001</v>
+        <v>-6.518</v>
       </c>
     </row>
     <row r="310">
@@ -14703,10 +14703,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.578</v>
+        <v>-0.3974</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.56</v>
+        <v>-7.948</v>
       </c>
     </row>
     <row r="311">
@@ -14743,10 +14743,10 @@
         <v>0.38</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.8496</v>
+        <v>-0.5856</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.992</v>
+        <v>-11.712</v>
       </c>
     </row>
     <row r="312">
@@ -14783,10 +14783,10 @@
         <v>1.99</v>
       </c>
       <c r="I312" t="n">
-        <v>1.873</v>
+        <v>1.3899</v>
       </c>
       <c r="J312" t="n">
-        <v>39.333</v>
+        <v>29.1879</v>
       </c>
     </row>
     <row r="313">
@@ -14823,10 +14823,10 @@
         <v>1.51</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1184</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J313" t="n">
-        <v>23.4864</v>
+        <v>17.5602</v>
       </c>
     </row>
     <row r="314">
@@ -14863,10 +14863,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0748</v>
+        <v>0.8125</v>
       </c>
       <c r="J314" t="n">
-        <v>22.5708</v>
+        <v>17.0625</v>
       </c>
     </row>
     <row r="315">
@@ -14903,10 +14903,10 @@
         <v>1.22</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4474</v>
+        <v>0.4663</v>
       </c>
       <c r="J315" t="n">
-        <v>9.3954</v>
+        <v>9.792299999999999</v>
       </c>
     </row>
     <row r="316">
@@ -14943,10 +14943,10 @@
         <v>1.04</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0253</v>
+        <v>0.0624</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.5313</v>
+        <v>1.3104</v>
       </c>
     </row>
     <row r="317">
@@ -14983,10 +14983,10 @@
         <v>0.79</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.2279</v>
+        <v>-0.1978</v>
       </c>
       <c r="J317" t="n">
-        <v>-4.7859</v>
+        <v>-4.1538</v>
       </c>
     </row>
     <row r="318">
@@ -15023,10 +15023,10 @@
         <v>0.67</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.4205</v>
+        <v>-0.3182</v>
       </c>
       <c r="J318" t="n">
-        <v>-8.830500000000001</v>
+        <v>-6.6822</v>
       </c>
     </row>
     <row r="319">
@@ -15063,10 +15063,10 @@
         <v>0.66</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.4386</v>
+        <v>-0.3273</v>
       </c>
       <c r="J319" t="n">
-        <v>-9.210599999999999</v>
+        <v>-6.8733</v>
       </c>
     </row>
     <row r="320">
@@ -15103,10 +15103,10 @@
         <v>0.57</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5978</v>
+        <v>-0.4084</v>
       </c>
       <c r="J320" t="n">
-        <v>-12.5538</v>
+        <v>-8.5764</v>
       </c>
     </row>
     <row r="321">
@@ -15143,10 +15143,10 @@
         <v>0.55</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6269</v>
+        <v>-0.427</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.1649</v>
+        <v>-8.967000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3454/event_3454_evp_summary.xlsx
+++ b/database/event/3454/event_3454_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8793</v>
+        <v>6.9847</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8776</v>
+        <v>1.9064</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4676</v>
+        <v>2.5554</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8793</v>
+        <v>6.9847</v>
       </c>
       <c r="F2" t="n">
-        <v>2.552</v>
+        <v>2.4402</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3273</v>
+        <v>4.5445</v>
       </c>
       <c r="H2" t="n">
-        <v>2.552</v>
+        <v>2.616</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9984</v>
+        <v>2.8962</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3273</v>
+        <v>4.5445</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>263</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3257</v>
+        <v>7.4407</v>
       </c>
       <c r="N2" t="n">
         <v>368</v>
@@ -538,185 +538,185 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.9498</v>
+        <v>5.2511</v>
       </c>
       <c r="C3" t="n">
-        <v>1.351</v>
+        <v>1.4332</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5966</v>
+        <v>1.7662</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9498</v>
+        <v>5.2511</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7356</v>
+        <v>0.9868</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2142</v>
+        <v>4.2643</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7356</v>
+        <v>0.9868</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2141</v>
+        <v>1.0383</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2142</v>
+        <v>4.2643</v>
       </c>
       <c r="K3" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="L3" t="n">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4283</v>
+        <v>5.3026</v>
       </c>
       <c r="N3" t="n">
-        <v>368</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8998</v>
+        <v>4.953</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3374</v>
+        <v>1.3519</v>
       </c>
       <c r="D4" t="n">
-        <v>1.574</v>
+        <v>1.6305</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8998</v>
+        <v>4.953</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9828</v>
+        <v>2.5521</v>
       </c>
       <c r="G4" t="n">
-        <v>3.917</v>
+        <v>2.4009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9828</v>
+        <v>2.8609</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0653</v>
+        <v>3.1674</v>
       </c>
       <c r="J4" t="n">
-        <v>3.917</v>
+        <v>2.4009</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="L4" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9823</v>
+        <v>5.568300000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6263</v>
+        <v>3.8718</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9898</v>
+        <v>1.0568</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9991</v>
+        <v>1.1383</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6263</v>
+        <v>3.8718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7836</v>
+        <v>1.1173</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8427</v>
+        <v>2.7545</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7836</v>
+        <v>1.1173</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7836</v>
+        <v>1.1756</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8427</v>
+        <v>2.7545</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="L5" t="n">
-        <v>112</v>
+        <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6263</v>
+        <v>3.9301</v>
       </c>
       <c r="N5" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5632</v>
+        <v>3.8564</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9725</v>
+        <v>1.0526</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9706</v>
+        <v>1.1313</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5632</v>
+        <v>3.8564</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1213</v>
+        <v>0.7466</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4419</v>
+        <v>3.1098</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1213</v>
+        <v>0.7466</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2154</v>
+        <v>0.7466</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4419</v>
+        <v>3.1098</v>
       </c>
       <c r="K6" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="L6" t="n">
-        <v>181</v>
+        <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6573</v>
+        <v>3.8564</v>
       </c>
       <c r="N6" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3555</v>
+        <v>3.7468</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9159</v>
+        <v>1.0227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8768</v>
+        <v>1.0814</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3555</v>
+        <v>3.7468</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3555</v>
+        <v>3.7468</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3555</v>
+        <v>3.7468</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>162</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3555</v>
+        <v>3.7468</v>
       </c>
       <c r="N7" t="n">
         <v>162</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3334</v>
+        <v>3.5493</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.9688</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8668</v>
+        <v>0.9915</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3334</v>
+        <v>3.5493</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1427</v>
+        <v>1.1102</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1907</v>
+        <v>2.4391</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1427</v>
+        <v>1.1102</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5175</v>
+        <v>1.1682</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1907</v>
+        <v>2.4391</v>
       </c>
       <c r="K8" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7082</v>
+        <v>3.6073</v>
       </c>
       <c r="N8" t="n">
-        <v>368</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2851</v>
+        <v>3.5368</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8966</v>
+        <v>0.9653</v>
       </c>
       <c r="D9" t="n">
-        <v>0.845</v>
+        <v>0.9858</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2851</v>
+        <v>3.5368</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0984</v>
+        <v>2.2564</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1867</v>
+        <v>1.2804</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0984</v>
+        <v>2.2564</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1906</v>
+        <v>2.4981</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1867</v>
+        <v>1.2804</v>
       </c>
       <c r="K9" t="n">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="L9" t="n">
-        <v>181</v>
+        <v>263</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3773</v>
+        <v>3.7785</v>
       </c>
       <c r="N9" t="n">
-        <v>231</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9307</v>
+        <v>3.2757</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8941</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6851</v>
+        <v>0.867</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9307</v>
+        <v>3.2757</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5603</v>
+        <v>-0.6018</v>
       </c>
       <c r="G10" t="n">
-        <v>3.491</v>
+        <v>3.8775</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5603</v>
+        <v>-0.6018</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5603</v>
+        <v>-0.6018</v>
       </c>
       <c r="J10" t="n">
-        <v>3.491</v>
+        <v>3.8775</v>
       </c>
       <c r="K10" t="n">
         <v>113</v>
@@ -897,7 +897,7 @@
         <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9307</v>
+        <v>3.2757</v>
       </c>
       <c r="N10" t="n">
         <v>225</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6231</v>
+        <v>2.8142</v>
       </c>
       <c r="C11" t="n">
-        <v>0.716</v>
+        <v>0.7681</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5462</v>
+        <v>0.6569</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6231</v>
+        <v>2.8142</v>
       </c>
       <c r="F11" t="n">
-        <v>2.469</v>
+        <v>2.4259</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1541</v>
+        <v>0.3883</v>
       </c>
       <c r="H11" t="n">
-        <v>2.469</v>
+        <v>2.5847</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9009</v>
+        <v>2.8616</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1541</v>
+        <v>0.3883</v>
       </c>
       <c r="K11" t="n">
         <v>105</v>
@@ -943,7 +943,7 @@
         <v>263</v>
       </c>
       <c r="M11" t="n">
-        <v>3.055</v>
+        <v>3.2499</v>
       </c>
       <c r="N11" t="n">
         <v>368</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5268</v>
+        <v>2.6882</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6897</v>
+        <v>0.7337</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5027</v>
+        <v>0.5995</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5268</v>
+        <v>2.6882</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5609</v>
+        <v>0.4974</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9659</v>
+        <v>2.1908</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5609</v>
+        <v>0.4974</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5609</v>
+        <v>0.4974</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9659</v>
+        <v>2.1908</v>
       </c>
       <c r="K12" t="n">
         <v>113</v>
@@ -989,7 +989,7 @@
         <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5268</v>
+        <v>2.6882</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9465</v>
+        <v>2.076</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5313</v>
+        <v>0.5666</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2407</v>
+        <v>0.3208</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9465</v>
+        <v>2.076</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5736</v>
+        <v>2.4123</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3729</v>
+        <v>-0.3363</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5736</v>
+        <v>2.5548</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6217</v>
+        <v>2.9762</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3729</v>
+        <v>-0.3363</v>
       </c>
       <c r="K13" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="L13" t="n">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9946</v>
+        <v>2.6399</v>
       </c>
       <c r="N13" t="n">
-        <v>220</v>
+        <v>523</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.852</v>
+        <v>2.0323</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.5547</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1981</v>
+        <v>0.3009</v>
       </c>
       <c r="E14" t="n">
-        <v>1.852</v>
+        <v>2.0323</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3726</v>
+        <v>0.5222</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5206</v>
+        <v>1.5101</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3726</v>
+        <v>0.5222</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0216</v>
+        <v>0.5495</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5206</v>
+        <v>1.5101</v>
       </c>
       <c r="K14" t="n">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="L14" t="n">
-        <v>359</v>
+        <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>2.501</v>
+        <v>2.0596</v>
       </c>
       <c r="N14" t="n">
-        <v>523</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7787</v>
+        <v>1.9777</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4855</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.165</v>
+        <v>0.2761</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7787</v>
+        <v>1.9777</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7787</v>
+        <v>2.7353</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.7971</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7787</v>
+        <v>2.7353</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L15" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7787</v>
+        <v>1.9382</v>
       </c>
       <c r="N15" t="n">
-        <v>162</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7468</v>
+        <v>1.9043</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4768</v>
+        <v>0.5198</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1506</v>
+        <v>0.2427</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7468</v>
+        <v>1.9043</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.784</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5308</v>
+        <v>1.9043</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.784</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8498</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5308</v>
+        <v>1.9043</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="M16" t="n">
-        <v>1.681</v>
+        <v>1.9043</v>
       </c>
       <c r="N16" t="n">
-        <v>231</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7106</v>
+        <v>1.8288</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4669</v>
+        <v>0.4992</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1342</v>
+        <v>0.2083</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7106</v>
+        <v>1.8288</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7821</v>
+        <v>0.7762</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9285</v>
+        <v>1.0526</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7821</v>
+        <v>0.7762</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8143</v>
+        <v>0.7962</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9285</v>
+        <v>1.0526</v>
       </c>
       <c r="K17" t="n">
         <v>80</v>
@@ -1219,7 +1219,7 @@
         <v>73</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7428</v>
+        <v>1.8488</v>
       </c>
       <c r="N17" t="n">
         <v>153</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4894</v>
+        <v>1.8263</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4065</v>
+        <v>0.4985</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0344</v>
+        <v>0.2072</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4894</v>
+        <v>1.8263</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8065</v>
+        <v>1.8009</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3171</v>
+        <v>0.0254</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8065</v>
+        <v>1.8009</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9582</v>
+        <v>1.8949</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3171</v>
+        <v>0.0254</v>
       </c>
       <c r="K18" t="n">
         <v>50</v>
@@ -1265,7 +1265,7 @@
         <v>181</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6411</v>
+        <v>1.9203</v>
       </c>
       <c r="N18" t="n">
         <v>231</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2795</v>
+        <v>1.3712</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3492</v>
+        <v>0.3743</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0604</v>
+        <v>-0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2795</v>
+        <v>1.3712</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2795</v>
+        <v>1.3712</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2795</v>
+        <v>1.3712</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2795</v>
+        <v>1.3712</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9754</v>
+        <v>1.05</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2662</v>
+        <v>0.2866</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1977</v>
+        <v>-0.1462</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9754</v>
+        <v>1.05</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3681</v>
+        <v>0.3143</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6073</v>
+        <v>0.7357</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3681</v>
+        <v>0.3143</v>
       </c>
       <c r="I20" t="n">
-        <v>0.399</v>
+        <v>0.3307</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6073</v>
+        <v>0.7357</v>
       </c>
       <c r="K20" t="n">
         <v>122</v>
@@ -1357,7 +1357,7 @@
         <v>98</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0063</v>
+        <v>1.0664</v>
       </c>
       <c r="N20" t="n">
         <v>220</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.821</v>
+        <v>0.8511</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2241</v>
+        <v>0.2323</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2674</v>
+        <v>-0.2368</v>
       </c>
       <c r="E21" t="n">
-        <v>0.821</v>
+        <v>0.8511</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1959</v>
+        <v>0.6375</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3749</v>
+        <v>0.2136</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1959</v>
+        <v>0.6375</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2963</v>
+        <v>0.6539</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3749</v>
+        <v>0.2136</v>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="L21" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9214</v>
+        <v>0.8675</v>
       </c>
       <c r="N21" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8021</v>
+        <v>0.7936</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2189</v>
+        <v>0.2166</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2759</v>
+        <v>-0.2629</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8021</v>
+        <v>0.7936</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6048</v>
+        <v>1.2058</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1973</v>
+        <v>-0.4122</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6048</v>
+        <v>1.2058</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6297</v>
+        <v>1.2687</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1973</v>
+        <v>-0.4122</v>
       </c>
       <c r="K22" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="L22" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.8564999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8015</v>
+        <v>0.7773</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2188</v>
+        <v>0.2122</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2762</v>
+        <v>-0.2704</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8015</v>
+        <v>0.7773</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1955</v>
+        <v>0.1005</v>
       </c>
       <c r="G23" t="n">
-        <v>0.606</v>
+        <v>0.6768</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1955</v>
+        <v>0.1005</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2119</v>
+        <v>0.1057</v>
       </c>
       <c r="J23" t="n">
-        <v>0.606</v>
+        <v>0.6768</v>
       </c>
       <c r="K23" t="n">
         <v>122</v>
@@ -1495,7 +1495,7 @@
         <v>98</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8179</v>
+        <v>0.7825</v>
       </c>
       <c r="N23" t="n">
         <v>220</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.7094</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1677</v>
+        <v>0.1936</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3606</v>
+        <v>-0.3013</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.7094</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0282</v>
+        <v>0.0399</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6695</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0282</v>
+        <v>0.0399</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0294</v>
+        <v>0.0409</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6695</v>
       </c>
       <c r="K24" t="n">
         <v>80</v>
@@ -1541,7 +1541,7 @@
         <v>73</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6156</v>
+        <v>0.7104</v>
       </c>
       <c r="N24" t="n">
         <v>153</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.494</v>
+        <v>0.5562</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1348</v>
+        <v>0.1518</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.415</v>
+        <v>-0.371</v>
       </c>
       <c r="E25" t="n">
-        <v>0.494</v>
+        <v>0.5562</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.494</v>
+        <v>0.5562</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.494</v>
+        <v>0.5562</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>0.494</v>
+        <v>0.5562</v>
       </c>
       <c r="N25" t="n">
         <v>162</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3935</v>
+        <v>0.5119</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1074</v>
+        <v>0.1397</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4604</v>
+        <v>-0.3912</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3935</v>
+        <v>0.5119</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1244</v>
+        <v>-0.1504</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5179</v>
+        <v>0.6623</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1244</v>
+        <v>-0.1504</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1244</v>
+        <v>-0.1504</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5179</v>
+        <v>0.6623</v>
       </c>
       <c r="K26" t="n">
         <v>113</v>
@@ -1633,7 +1633,7 @@
         <v>112</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3935</v>
+        <v>0.5119</v>
       </c>
       <c r="N26" t="n">
         <v>225</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2921</v>
+        <v>0.3567</v>
       </c>
       <c r="C27" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5061</v>
+        <v>-0.4618</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2921</v>
+        <v>0.3567</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0926</v>
+        <v>-0.1056</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3847</v>
+        <v>0.4623</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0926</v>
+        <v>-0.1056</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0964</v>
+        <v>-0.1083</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3847</v>
+        <v>0.4623</v>
       </c>
       <c r="K27" t="n">
         <v>80</v>
@@ -1679,7 +1679,7 @@
         <v>73</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2883</v>
+        <v>0.354</v>
       </c>
       <c r="N27" t="n">
         <v>153</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2349</v>
+        <v>0.1996</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0641</v>
+        <v>0.0545</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.532</v>
+        <v>-0.5333</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2349</v>
+        <v>0.1996</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6514</v>
+        <v>0.6405</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4165</v>
+        <v>-0.4409</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6514</v>
+        <v>0.6405</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6782</v>
+        <v>0.657</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4165</v>
+        <v>-0.4409</v>
       </c>
       <c r="K28" t="n">
         <v>80</v>
@@ -1725,7 +1725,7 @@
         <v>73</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2617</v>
+        <v>0.2161</v>
       </c>
       <c r="N28" t="n">
         <v>153</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1829</v>
+        <v>0.1663</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0499</v>
+        <v>0.0454</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5554</v>
+        <v>-0.5485</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1829</v>
+        <v>0.1663</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.283</v>
+        <v>-0.3292</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4659</v>
+        <v>0.4955</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.283</v>
+        <v>-0.3292</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3068</v>
+        <v>-0.3464</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4659</v>
+        <v>0.4955</v>
       </c>
       <c r="K29" t="n">
         <v>122</v>
@@ -1771,7 +1771,7 @@
         <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1591</v>
+        <v>0.1491</v>
       </c>
       <c r="N29" t="n">
         <v>220</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0606</v>
+        <v>0.0147</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0165</v>
+        <v>0.004</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6107</v>
+        <v>-0.6175</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0606</v>
+        <v>0.0147</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6595</v>
+        <v>-0.618</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5989</v>
+        <v>0.6327</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6595</v>
+        <v>-0.618</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6595</v>
+        <v>-0.618</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5989</v>
+        <v>0.6327</v>
       </c>
       <c r="K30" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.01470000000000005</v>
       </c>
       <c r="N30" t="n">
-        <v>98</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.148</v>
+        <v>-0.0314</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0404</v>
+        <v>-0.0086</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7048</v>
+        <v>-0.6385</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.148</v>
+        <v>-0.0314</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.6102</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4654</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.6102</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6133999999999999</v>
+        <v>0.6102</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4654</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="L31" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.148</v>
+        <v>-0.03139999999999998</v>
       </c>
       <c r="N31" t="n">
-        <v>225</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4773</v>
+        <v>-0.5023</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1303</v>
+        <v>-0.1371</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8535</v>
+        <v>-0.8529</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4773</v>
+        <v>-0.5023</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6158</v>
+        <v>0.6422</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.0931</v>
+        <v>-1.1445</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6158</v>
+        <v>0.6422</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6675</v>
+        <v>0.6757</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0931</v>
+        <v>-1.1445</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -1909,7 +1909,7 @@
         <v>96</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4256</v>
+        <v>-0.4688000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>155</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.539</v>
+        <v>-0.5851</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1471</v>
+        <v>-0.1597</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8813</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.539</v>
+        <v>-0.5851</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5964</v>
+        <v>-0.6231</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0574</v>
+        <v>0.038</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5964</v>
+        <v>-0.6231</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5964</v>
+        <v>-0.6231</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0574</v>
+        <v>0.038</v>
       </c>
       <c r="K33" t="n">
         <v>59</v>
@@ -1955,7 +1955,7 @@
         <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.539</v>
+        <v>-0.5851</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1964,81 +1964,81 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hutji</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7585</v>
+        <v>-0.7309</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.207</v>
+        <v>-0.1995</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9804</v>
+        <v>-0.9569</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7585</v>
+        <v>-0.7309</v>
       </c>
       <c r="F34" t="n">
-        <v>0.117</v>
+        <v>-0.5138</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.2171</v>
       </c>
       <c r="H34" t="n">
-        <v>0.117</v>
+        <v>-0.5138</v>
       </c>
       <c r="I34" t="n">
-        <v>0.117</v>
+        <v>-0.5406</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.2171</v>
       </c>
       <c r="K34" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="L34" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7585</v>
+        <v>-0.7576999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>98</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>hutji</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7677</v>
+        <v>-0.8023</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2095</v>
+        <v>-0.219</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9846</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7677</v>
+        <v>-0.8023</v>
       </c>
       <c r="F35" t="n">
-        <v>0.013</v>
+        <v>0.103</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.9053</v>
       </c>
       <c r="H35" t="n">
-        <v>0.013</v>
+        <v>0.103</v>
       </c>
       <c r="I35" t="n">
-        <v>0.013</v>
+        <v>0.103</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.9053</v>
       </c>
       <c r="K35" t="n">
         <v>59</v>
@@ -2047,7 +2047,7 @@
         <v>39</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7676999999999999</v>
+        <v>-0.8023</v>
       </c>
       <c r="N35" t="n">
         <v>98</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7684</v>
+        <v>-0.8141</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2097</v>
+        <v>-0.2222</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9849</v>
+        <v>-0.9948</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7684</v>
+        <v>-0.8141</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0926</v>
+        <v>0.0025</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.861</v>
+        <v>-0.8166</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0926</v>
+        <v>0.0025</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1004</v>
+        <v>0.0025</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.861</v>
+        <v>-0.8166</v>
       </c>
       <c r="K36" t="n">
         <v>59</v>
       </c>
       <c r="L36" t="n">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7605999999999999</v>
+        <v>-0.8141</v>
       </c>
       <c r="N36" t="n">
-        <v>155</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7692</v>
+        <v>-0.8156</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2099</v>
+        <v>-0.2226</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9853</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7692</v>
+        <v>-0.8156</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4516</v>
+        <v>0.1077</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.3176</v>
+        <v>-0.9233</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4516</v>
+        <v>0.1077</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4895</v>
+        <v>0.1133</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3176</v>
+        <v>-0.9233</v>
       </c>
       <c r="K37" t="n">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="L37" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8070999999999999</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>220</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7945</v>
+        <v>-0.8348</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2169</v>
+        <v>-0.2279</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9967</v>
+        <v>-1.0042</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7945</v>
+        <v>-0.8348</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0611</v>
+        <v>0.0523</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8556</v>
+        <v>-0.8871</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0611</v>
+        <v>0.0523</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0611</v>
+        <v>0.0523</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8556</v>
+        <v>-0.8871</v>
       </c>
       <c r="K38" t="n">
         <v>59</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7945</v>
+        <v>-0.8348</v>
       </c>
       <c r="N38" t="n">
         <v>98</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9216</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2515</v>
+        <v>-0.2547</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0541</v>
+        <v>-1.0489</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9216</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1404</v>
+        <v>-0.1151</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.7812</v>
+        <v>-0.8179</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1404</v>
+        <v>-0.1151</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1522</v>
+        <v>-0.1211</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7812</v>
+        <v>-0.8179</v>
       </c>
       <c r="K39" t="n">
         <v>59</v>
@@ -2231,7 +2231,7 @@
         <v>96</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9334</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>155</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3028</v>
+        <v>-1.2747</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3556</v>
+        <v>-0.3479</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2262</v>
+        <v>-1.2045</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3028</v>
+        <v>-1.2747</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3028</v>
+        <v>-1.2747</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.3028</v>
+        <v>-1.2747</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3028</v>
+        <v>-1.2747</v>
       </c>
       <c r="N40" t="n">
         <v>162</v>
@@ -2383,10 +2383,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1981</v>
+        <v>0.2117</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1981</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1841</v>
+        <v>0.1977</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1841</v>
+        <v>0.1977</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1259</v>
+        <v>0.1387</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1259</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0789</v>
+        <v>0.0898</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0789</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2125</v>
+        <v>-0.2252</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2125</v>
+        <v>-0.2252</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5394</v>
+        <v>0.5311</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5394</v>
+        <v>0.5311</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3809</v>
+        <v>0.3842</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3809</v>
+        <v>0.3842</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.081</v>
+        <v>0.0924</v>
       </c>
       <c r="J9" t="n">
-        <v>0.081</v>
+        <v>0.0924</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0051</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0051</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1316</v>
+        <v>-0.142</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1316</v>
+        <v>-0.142</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.33</v>
+        <v>0.3092</v>
       </c>
       <c r="J12" t="n">
-        <v>11.88</v>
+        <v>11.1312</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>0.87</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1349</v>
+        <v>-0.1556</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.8564</v>
+        <v>-5.6016</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3313</v>
+        <v>-0.349</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.9268</v>
+        <v>-12.564</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3876</v>
+        <v>-0.4029</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.9536</v>
+        <v>-14.5044</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4902</v>
+        <v>-0.4999</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.6472</v>
+        <v>-17.9964</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8018</v>
+        <v>0.7954</v>
       </c>
       <c r="J17" t="n">
-        <v>28.8648</v>
+        <v>28.6344</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>1.4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4911</v>
+        <v>0.5049</v>
       </c>
       <c r="J18" t="n">
-        <v>17.6796</v>
+        <v>18.1764</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4492</v>
+        <v>0.4647</v>
       </c>
       <c r="J19" t="n">
-        <v>16.1712</v>
+        <v>16.7292</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3379</v>
+        <v>0.3574</v>
       </c>
       <c r="J20" t="n">
-        <v>12.1644</v>
+        <v>12.8664</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1188</v>
+        <v>0.1413</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2768</v>
+        <v>5.0868</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5537</v>
+        <v>0.5447</v>
       </c>
       <c r="J22" t="n">
-        <v>13.2888</v>
+        <v>13.0728</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2294</v>
+        <v>0.2403</v>
       </c>
       <c r="J23" t="n">
-        <v>5.5056</v>
+        <v>5.7672</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0794</v>
+        <v>0.0912</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9056</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0794</v>
+        <v>0.0912</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9056</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0076</v>
+        <v>-0.0058</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1824</v>
+        <v>-0.1392</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.39</v>
+        <v>0.3991</v>
       </c>
       <c r="J27" t="n">
-        <v>9.359999999999999</v>
+        <v>9.5784</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1817</v>
+        <v>0.1959</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3608</v>
+        <v>4.7016</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0222</v>
+        <v>0.0288</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.6912</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0249</v>
+        <v>-0.0286</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5976</v>
+        <v>-0.6864</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1725</v>
+        <v>-0.1846</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.14</v>
+        <v>-4.4304</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>1.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1254</v>
+        <v>0.1342</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3858</v>
+        <v>3.6234</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1254</v>
+        <v>0.1342</v>
       </c>
       <c r="J33" t="n">
-        <v>3.3858</v>
+        <v>3.6234</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0456</v>
+        <v>-0.0549</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.2312</v>
+        <v>-1.4823</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1388</v>
+        <v>-0.1533</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.7476</v>
+        <v>-4.1391</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3007</v>
+        <v>-0.3144</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.1189</v>
+        <v>-8.488799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0912</v>
+        <v>1.0875</v>
       </c>
       <c r="J37" t="n">
-        <v>29.4624</v>
+        <v>29.3625</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4985</v>
+        <v>0.4981</v>
       </c>
       <c r="J38" t="n">
-        <v>13.4595</v>
+        <v>13.4487</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3115</v>
+        <v>0.3221</v>
       </c>
       <c r="J39" t="n">
-        <v>8.410500000000001</v>
+        <v>8.6967</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1306</v>
+        <v>-0.1384</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.5262</v>
+        <v>-3.7368</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1644</v>
+        <v>-0.1732</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.4388</v>
+        <v>-4.6764</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4507</v>
+        <v>0.4461</v>
       </c>
       <c r="J42" t="n">
-        <v>16.2252</v>
+        <v>16.0596</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1126</v>
+        <v>0.1222</v>
       </c>
       <c r="J43" t="n">
-        <v>4.0536</v>
+        <v>4.3992</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0356</v>
+        <v>0.0419</v>
       </c>
       <c r="J44" t="n">
-        <v>1.2816</v>
+        <v>1.5084</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1022</v>
+        <v>-0.1131</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.6792</v>
+        <v>-4.0716</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1252</v>
+        <v>-0.1371</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.5072</v>
+        <v>-4.9356</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6933</v>
+        <v>0.6567</v>
       </c>
       <c r="J47" t="n">
-        <v>24.9588</v>
+        <v>23.6412</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6183</v>
+        <v>0.5903</v>
       </c>
       <c r="J48" t="n">
-        <v>22.2588</v>
+        <v>21.2508</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1166</v>
+        <v>0.1264</v>
       </c>
       <c r="J49" t="n">
-        <v>4.1976</v>
+        <v>4.5504</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1108</v>
+        <v>-0.1113</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.9888</v>
+        <v>-4.0068</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3976</v>
+        <v>-0.3823</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.3136</v>
+        <v>-13.7628</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5313</v>
+        <v>0.5088</v>
       </c>
       <c r="J52" t="n">
-        <v>14.3451</v>
+        <v>13.7376</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1008</v>
+        <v>0.0985</v>
       </c>
       <c r="J53" t="n">
-        <v>2.7216</v>
+        <v>2.6595</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1529</v>
+        <v>-0.1695</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.1283</v>
+        <v>-4.5765</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3576</v>
+        <v>-0.3713</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.655200000000001</v>
+        <v>-10.0251</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4507</v>
+        <v>-0.4601</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.1689</v>
+        <v>-12.4227</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>1.58</v>
       </c>
       <c r="I57" t="n">
-        <v>1.2269</v>
+        <v>1.1986</v>
       </c>
       <c r="J57" t="n">
-        <v>33.1263</v>
+        <v>32.3622</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>1.51</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1396</v>
+        <v>1.1051</v>
       </c>
       <c r="J58" t="n">
-        <v>30.7692</v>
+        <v>29.8377</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4231</v>
+        <v>0.4239</v>
       </c>
       <c r="J59" t="n">
-        <v>11.4237</v>
+        <v>11.4453</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1368</v>
+        <v>0.1586</v>
       </c>
       <c r="J60" t="n">
-        <v>3.6936</v>
+        <v>4.2822</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>1.03</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0688</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>1.8576</v>
+        <v>2.5164</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1424</v>
+        <v>1.1051</v>
       </c>
       <c r="J62" t="n">
-        <v>28.56</v>
+        <v>27.6275</v>
       </c>
     </row>
     <row r="63">
@@ -4823,10 +4823,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8176</v>
+        <v>0.7739</v>
       </c>
       <c r="J63" t="n">
-        <v>20.44</v>
+        <v>19.3475</v>
       </c>
     </row>
     <row r="64">
@@ -4863,10 +4863,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6313</v>
+        <v>0.6091</v>
       </c>
       <c r="J64" t="n">
-        <v>15.7825</v>
+        <v>15.2275</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3587</v>
+        <v>0.3618</v>
       </c>
       <c r="J65" t="n">
-        <v>8.967499999999999</v>
+        <v>9.045</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6221</v>
+        <v>-0.5783</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.5525</v>
+        <v>-14.4575</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2715</v>
+        <v>0.2708</v>
       </c>
       <c r="J67" t="n">
-        <v>6.7875</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.081</v>
+        <v>-0.0936</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.025</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>0.91</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1147</v>
+        <v>-0.129</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.8675</v>
+        <v>-3.225</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1255</v>
+        <v>-0.1402</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.1375</v>
+        <v>-3.505</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2975</v>
+        <v>-0.3119</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.4375</v>
+        <v>-7.7975</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.82</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4395</v>
+        <v>1.4372</v>
       </c>
       <c r="J72" t="n">
-        <v>24.4715</v>
+        <v>24.4324</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.77</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3846</v>
+        <v>1.3788</v>
       </c>
       <c r="J73" t="n">
-        <v>23.5382</v>
+        <v>23.4396</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.72</v>
       </c>
       <c r="I74" t="n">
-        <v>1.3295</v>
+        <v>1.32</v>
       </c>
       <c r="J74" t="n">
-        <v>22.6015</v>
+        <v>22.44</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.152</v>
+        <v>1.1285</v>
       </c>
       <c r="J75" t="n">
-        <v>19.584</v>
+        <v>19.1845</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>1.34</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7988</v>
+        <v>0.7736</v>
       </c>
       <c r="J76" t="n">
-        <v>13.5796</v>
+        <v>13.1512</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>0.64</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3143</v>
+        <v>-0.3412</v>
       </c>
       <c r="J77" t="n">
-        <v>-5.3431</v>
+        <v>-5.8004</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.62</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3352</v>
+        <v>-0.3608</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.6984</v>
+        <v>-6.1336</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.53</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4229</v>
+        <v>-0.4431</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.1893</v>
+        <v>-7.5327</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5139</v>
+        <v>-0.5281</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.7363</v>
+        <v>-8.9777</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.582</v>
+        <v>-0.5908</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.894</v>
+        <v>-10.0436</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4333</v>
+        <v>0.4225</v>
       </c>
       <c r="J82" t="n">
-        <v>10.8325</v>
+        <v>10.5625</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2516</v>
+        <v>0.2515</v>
       </c>
       <c r="J83" t="n">
-        <v>6.29</v>
+        <v>6.2875</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.162</v>
+        <v>0.1644</v>
       </c>
       <c r="J84" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.75</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2776</v>
+        <v>-0.2926</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.94</v>
+        <v>-7.315</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.49</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5246</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.9925</v>
+        <v>-13.115</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2365</v>
+        <v>1.2048</v>
       </c>
       <c r="J87" t="n">
-        <v>30.9125</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6828</v>
+        <v>0.654</v>
       </c>
       <c r="J88" t="n">
-        <v>17.07</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5634</v>
+        <v>0.5474</v>
       </c>
       <c r="J89" t="n">
-        <v>14.085</v>
+        <v>13.685</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J90" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5646</v>
+        <v>-0.5276</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.115</v>
+        <v>-13.19</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5833</v>
       </c>
       <c r="J92" t="n">
-        <v>15.26</v>
+        <v>14.5825</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3213</v>
+        <v>0.3163</v>
       </c>
       <c r="J93" t="n">
-        <v>8.032500000000001</v>
+        <v>7.9075</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1654</v>
+        <v>-0.1816</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.135</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.285</v>
+        <v>-0.3002</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.125</v>
+        <v>-7.505</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5269</v>
+        <v>-0.5316</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.1725</v>
+        <v>-13.29</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1006</v>
+        <v>1.0602</v>
       </c>
       <c r="J97" t="n">
-        <v>27.515</v>
+        <v>26.505</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7217</v>
+        <v>0.6901</v>
       </c>
       <c r="J98" t="n">
-        <v>18.0425</v>
+        <v>17.2525</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.652</v>
+        <v>0.6282</v>
       </c>
       <c r="J99" t="n">
-        <v>16.3</v>
+        <v>15.705</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3825</v>
+        <v>0.3843</v>
       </c>
       <c r="J100" t="n">
-        <v>9.5625</v>
+        <v>9.6075</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2852</v>
+        <v>-0.2695</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.13</v>
+        <v>-6.7375</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3402</v>
+        <v>0.3393</v>
       </c>
       <c r="J102" t="n">
-        <v>8.505000000000001</v>
+        <v>8.4825</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2408</v>
+        <v>0.2386</v>
       </c>
       <c r="J103" t="n">
-        <v>6.02</v>
+        <v>5.965</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2147</v>
+        <v>-0.2313</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.3675</v>
+        <v>-5.7825</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.75</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2737</v>
+        <v>-0.2895</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.8425</v>
+        <v>-7.2375</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3785</v>
+        <v>-0.391</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.4625</v>
+        <v>-9.775</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6176</v>
+        <v>0.6854</v>
       </c>
       <c r="J107" t="n">
-        <v>15.44</v>
+        <v>17.135</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.29</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5905</v>
+        <v>0.6555</v>
       </c>
       <c r="J108" t="n">
-        <v>14.7625</v>
+        <v>16.3875</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4242</v>
+        <v>0.4684</v>
       </c>
       <c r="J109" t="n">
-        <v>10.605</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3634</v>
+        <v>0.3852</v>
       </c>
       <c r="J110" t="n">
-        <v>9.085000000000001</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3471</v>
+        <v>0.3605</v>
       </c>
       <c r="J111" t="n">
-        <v>8.6775</v>
+        <v>9.012499999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>0.99</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0055</v>
+        <v>-0.0137</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.1485</v>
+        <v>-0.3699</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0217</v>
+        <v>-0.0318</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.5859</v>
+        <v>-0.8586</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0631</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.7037</v>
+        <v>-2.0601</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1219</v>
+        <v>-0.1375</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.2913</v>
+        <v>-3.7125</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4698</v>
+        <v>-0.4781</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.6846</v>
+        <v>-12.9087</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2602</v>
+        <v>1.3752</v>
       </c>
       <c r="J117" t="n">
-        <v>34.0254</v>
+        <v>37.1304</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>1.27</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5574</v>
+        <v>0.6203</v>
       </c>
       <c r="J118" t="n">
-        <v>15.0498</v>
+        <v>16.7481</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4622</v>
+        <v>0.5131</v>
       </c>
       <c r="J119" t="n">
-        <v>12.4794</v>
+        <v>13.8537</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>1.08</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2324</v>
+        <v>0.248</v>
       </c>
       <c r="J120" t="n">
-        <v>6.2748</v>
+        <v>6.696</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.473</v>
+        <v>-0.4411</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.771</v>
+        <v>-11.9097</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8783</v>
+        <v>0.9566</v>
       </c>
       <c r="J122" t="n">
-        <v>26.349</v>
+        <v>28.698</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5342</v>
+        <v>0.583</v>
       </c>
       <c r="J123" t="n">
-        <v>16.026</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1295</v>
+        <v>-0.1351</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.885</v>
+        <v>-4.053</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.8237</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="J125" t="n">
-        <v>-24.711</v>
+        <v>-22.968</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-1.0672</v>
+        <v>-0.9762</v>
       </c>
       <c r="J126" t="n">
-        <v>-32.016</v>
+        <v>-29.286</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6146</v>
+        <v>0.6897</v>
       </c>
       <c r="J127" t="n">
-        <v>18.438</v>
+        <v>20.691</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3577</v>
+        <v>0.3793</v>
       </c>
       <c r="J128" t="n">
-        <v>10.731</v>
+        <v>11.379</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0309</v>
+        <v>-0.0332</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.927</v>
+        <v>-0.996</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>0.97</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.061</v>
+        <v>-0.0667</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.83</v>
+        <v>-2.001</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.061</v>
+        <v>-0.0667</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.83</v>
+        <v>-2.001</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6905</v>
+        <v>0.767</v>
       </c>
       <c r="J132" t="n">
-        <v>17.2625</v>
+        <v>19.175</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>1.37</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6905</v>
+        <v>0.767</v>
       </c>
       <c r="J133" t="n">
-        <v>17.2625</v>
+        <v>19.175</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>1.29</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5849</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>14.6225</v>
+        <v>16.2675</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4194</v>
+        <v>0.4642</v>
       </c>
       <c r="J135" t="n">
-        <v>10.485</v>
+        <v>11.605</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0365</v>
+        <v>0.0601</v>
       </c>
       <c r="J136" t="n">
-        <v>0.9125</v>
+        <v>1.5025</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.184</v>
+        <v>0.1863</v>
       </c>
       <c r="J137" t="n">
-        <v>4.6</v>
+        <v>4.6575</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.01</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0555</v>
+        <v>0.0561</v>
       </c>
       <c r="J138" t="n">
-        <v>1.3875</v>
+        <v>1.4025</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1468</v>
+        <v>-0.1621</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.67</v>
+        <v>-4.0525</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1781</v>
+        <v>-0.1939</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.4525</v>
+        <v>-4.8475</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2487</v>
+        <v>-0.2641</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.2175</v>
+        <v>-6.6025</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1521</v>
+        <v>0.1507</v>
       </c>
       <c r="J142" t="n">
-        <v>4.1067</v>
+        <v>4.0689</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0994</v>
+        <v>0.0975</v>
       </c>
       <c r="J143" t="n">
-        <v>2.6838</v>
+        <v>2.6325</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1832</v>
+        <v>-0.2002</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.9464</v>
+        <v>-5.4054</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2818</v>
+        <v>-0.2978</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.6086</v>
+        <v>-8.0406</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.71</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3107</v>
+        <v>-0.3259</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.3889</v>
+        <v>-8.799300000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>1.043</v>
+        <v>0.9936</v>
       </c>
       <c r="J147" t="n">
-        <v>28.161</v>
+        <v>26.8272</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8973</v>
+        <v>0.8458</v>
       </c>
       <c r="J148" t="n">
-        <v>24.2271</v>
+        <v>22.8366</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J149" t="n">
-        <v>16.2675</v>
+        <v>15.7815</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.377</v>
+        <v>0.3805</v>
       </c>
       <c r="J150" t="n">
-        <v>10.179</v>
+        <v>10.2735</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.1109</v>
+        <v>0.132</v>
       </c>
       <c r="J151" t="n">
-        <v>2.9943</v>
+        <v>3.564</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.67</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7773</v>
+        <v>0.7718</v>
       </c>
       <c r="J152" t="n">
-        <v>17.8779</v>
+        <v>17.7514</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.33</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4193</v>
+        <v>0.4354</v>
       </c>
       <c r="J153" t="n">
-        <v>9.6439</v>
+        <v>10.0142</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.3977</v>
+        <v>0.4146</v>
       </c>
       <c r="J154" t="n">
-        <v>9.1471</v>
+        <v>9.5358</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2814</v>
+        <v>0.3017</v>
       </c>
       <c r="J155" t="n">
-        <v>6.4722</v>
+        <v>6.9391</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>1.13</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1786</v>
+        <v>0.2004</v>
       </c>
       <c r="J156" t="n">
-        <v>4.1078</v>
+        <v>4.6092</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2772</v>
+        <v>0.2714</v>
       </c>
       <c r="J157" t="n">
-        <v>6.3756</v>
+        <v>6.2422</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1236</v>
+        <v>-0.1417</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.8428</v>
+        <v>-3.2591</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>0.76</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2541</v>
+        <v>-0.2724</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.8443</v>
+        <v>-6.2652</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2637</v>
+        <v>-0.2818</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.0651</v>
+        <v>-6.4814</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.51</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.489</v>
+        <v>-0.4975</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.247</v>
+        <v>-11.4425</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7075</v>
+        <v>0.6812</v>
       </c>
       <c r="J162" t="n">
-        <v>21.225</v>
+        <v>20.436</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.04</v>
       </c>
       <c r="I163" t="n">
-        <v>0.111</v>
+        <v>0.121</v>
       </c>
       <c r="J163" t="n">
-        <v>3.33</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.034</v>
+        <v>0.0407</v>
       </c>
       <c r="J164" t="n">
-        <v>1.02</v>
+        <v>1.221</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1151</v>
+        <v>-0.1263</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.453</v>
+        <v>-3.789</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2123</v>
+        <v>-0.2251</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.369</v>
+        <v>-6.753</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>1.045</v>
+        <v>0.9861</v>
       </c>
       <c r="J167" t="n">
-        <v>31.35</v>
+        <v>29.583</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3012</v>
+        <v>0.3024</v>
       </c>
       <c r="J168" t="n">
-        <v>9.036</v>
+        <v>9.071999999999999</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>1.03</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1175</v>
+        <v>0.127</v>
       </c>
       <c r="J169" t="n">
-        <v>3.525</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1817</v>
+        <v>-0.1807</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.451</v>
+        <v>-5.421</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.85</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5077</v>
+        <v>-0.4824</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.231</v>
+        <v>-14.472</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>1.1367</v>
+        <v>1.0976</v>
       </c>
       <c r="J172" t="n">
-        <v>32.9643</v>
+        <v>31.8304</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4433</v>
+        <v>0.4378</v>
       </c>
       <c r="J173" t="n">
-        <v>12.8557</v>
+        <v>12.6962</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.09</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2815</v>
+        <v>0.289</v>
       </c>
       <c r="J174" t="n">
-        <v>8.163500000000001</v>
+        <v>8.381</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.192</v>
+        <v>0.2051</v>
       </c>
       <c r="J175" t="n">
-        <v>5.568</v>
+        <v>5.9479</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1602</v>
+        <v>0.175</v>
       </c>
       <c r="J176" t="n">
-        <v>4.6458</v>
+        <v>5.075</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>1.38</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7658</v>
+        <v>0.7297</v>
       </c>
       <c r="J177" t="n">
-        <v>22.2082</v>
+        <v>21.1613</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2114</v>
+        <v>0.2171</v>
       </c>
       <c r="J178" t="n">
-        <v>6.1306</v>
+        <v>6.2959</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1849</v>
+        <v>-0.1991</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.3621</v>
+        <v>-5.7739</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2056</v>
+        <v>-0.2198</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.9624</v>
+        <v>-6.3742</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.73</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3046</v>
+        <v>-0.3175</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.833399999999999</v>
+        <v>-9.2075</v>
       </c>
     </row>
     <row r="182">
@@ -9583,10 +9583,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1685</v>
+        <v>1.133</v>
       </c>
       <c r="J182" t="n">
-        <v>35.055</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="183">
@@ -9623,10 +9623,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1043</v>
+        <v>1.0636</v>
       </c>
       <c r="J183" t="n">
-        <v>33.129</v>
+        <v>31.908</v>
       </c>
     </row>
     <row r="184">
@@ -9663,10 +9663,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.386</v>
+        <v>0.3867</v>
       </c>
       <c r="J184" t="n">
-        <v>11.58</v>
+        <v>11.601</v>
       </c>
     </row>
     <row r="185">
@@ -9703,10 +9703,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.3124</v>
+        <v>-0.2961</v>
       </c>
       <c r="J185" t="n">
-        <v>-9.372</v>
+        <v>-8.882999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9743,10 +9743,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3429</v>
+        <v>-0.3245</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.287</v>
+        <v>-9.734999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9783,10 +9783,10 @@
         <v>1.12</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3019</v>
+        <v>0.3021</v>
       </c>
       <c r="J187" t="n">
-        <v>9.057</v>
+        <v>9.063000000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9823,10 +9823,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2186</v>
+        <v>0.2223</v>
       </c>
       <c r="J188" t="n">
-        <v>6.558</v>
+        <v>6.669</v>
       </c>
     </row>
     <row r="189">
@@ -9863,10 +9863,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1063</v>
+        <v>-0.1195</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.189</v>
+        <v>-3.585</v>
       </c>
     </row>
     <row r="190">
@@ -9903,10 +9903,10 @@
         <v>0.88</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1503</v>
+        <v>-0.1648</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.509</v>
+        <v>-4.944</v>
       </c>
     </row>
     <row r="191">
@@ -9943,10 +9943,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2918</v>
+        <v>-0.3056</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.754</v>
+        <v>-9.167999999999999</v>
       </c>
     </row>
     <row r="192">
@@ -9983,10 +9983,10 @@
         <v>0.84</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1586</v>
+        <v>-0.1812</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.172</v>
+        <v>-3.624</v>
       </c>
     </row>
     <row r="193">
@@ -10023,10 +10023,10 @@
         <v>0.73</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.271</v>
+        <v>-0.2914</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.42</v>
+        <v>-5.828</v>
       </c>
     </row>
     <row r="194">
@@ -10063,10 +10063,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2979</v>
+        <v>-0.3179</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.958</v>
+        <v>-6.358</v>
       </c>
     </row>
     <row r="195">
@@ -10103,10 +10103,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3069</v>
+        <v>-0.3266</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.138</v>
+        <v>-6.532</v>
       </c>
     </row>
     <row r="196">
@@ -10143,10 +10143,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4183</v>
+        <v>-0.4332</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.366</v>
+        <v>-8.664</v>
       </c>
     </row>
     <row r="197">
@@ -10183,10 +10183,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9346</v>
+        <v>1.0374</v>
       </c>
       <c r="J197" t="n">
-        <v>18.692</v>
+        <v>20.748</v>
       </c>
     </row>
     <row r="198">
@@ -10223,10 +10223,10 @@
         <v>1.57</v>
       </c>
       <c r="I198" t="n">
-        <v>0.9109</v>
+        <v>1.0118</v>
       </c>
       <c r="J198" t="n">
-        <v>18.218</v>
+        <v>20.236</v>
       </c>
     </row>
     <row r="199">
@@ -10263,10 +10263,10 @@
         <v>1.46</v>
       </c>
       <c r="I199" t="n">
-        <v>0.7793</v>
+        <v>0.8694</v>
       </c>
       <c r="J199" t="n">
-        <v>15.586</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="200">
@@ -10303,10 +10303,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.7199</v>
+        <v>0.8041</v>
       </c>
       <c r="J200" t="n">
-        <v>14.398</v>
+        <v>16.082</v>
       </c>
     </row>
     <row r="201">
@@ -10343,10 +10343,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2229</v>
+        <v>0.2481</v>
       </c>
       <c r="J201" t="n">
-        <v>4.458</v>
+        <v>4.962</v>
       </c>
     </row>
     <row r="202">
@@ -10383,10 +10383,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4291</v>
+        <v>0.4734</v>
       </c>
       <c r="J202" t="n">
-        <v>11.5857</v>
+        <v>12.7818</v>
       </c>
     </row>
     <row r="203">
@@ -10423,10 +10423,10 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>0.364</v>
+        <v>0.3831</v>
       </c>
       <c r="J203" t="n">
-        <v>9.827999999999999</v>
+        <v>10.3437</v>
       </c>
     </row>
     <row r="204">
@@ -10463,10 +10463,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.0721</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.6929</v>
+        <v>-1.9467</v>
       </c>
     </row>
     <row r="205">
@@ -10503,10 +10503,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.111</v>
+        <v>-0.1231</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.997</v>
+        <v>-3.3237</v>
       </c>
     </row>
     <row r="206">
@@ -10543,10 +10543,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.345</v>
+        <v>-0.3563</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.315</v>
+        <v>-9.620100000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10583,10 +10583,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7968</v>
+        <v>0.8793</v>
       </c>
       <c r="J207" t="n">
-        <v>21.5136</v>
+        <v>23.7411</v>
       </c>
     </row>
     <row r="208">
@@ -10623,10 +10623,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4982</v>
+        <v>0.5516</v>
       </c>
       <c r="J208" t="n">
-        <v>13.4514</v>
+        <v>14.8932</v>
       </c>
     </row>
     <row r="209">
@@ -10663,10 +10663,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.4841</v>
+        <v>0.5356</v>
       </c>
       <c r="J209" t="n">
-        <v>13.0707</v>
+        <v>14.4612</v>
       </c>
     </row>
     <row r="210">
@@ -10703,10 +10703,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4698</v>
+        <v>0.5196</v>
       </c>
       <c r="J210" t="n">
-        <v>12.6846</v>
+        <v>14.0292</v>
       </c>
     </row>
     <row r="211">
@@ -10743,10 +10743,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.6434</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.7407</v>
+        <v>-17.3718</v>
       </c>
     </row>
     <row r="212">
@@ -10783,10 +10783,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4959</v>
+        <v>0.5458</v>
       </c>
       <c r="J212" t="n">
-        <v>14.3811</v>
+        <v>15.8282</v>
       </c>
     </row>
     <row r="213">
@@ -10823,10 +10823,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4663</v>
+        <v>0.5127</v>
       </c>
       <c r="J213" t="n">
-        <v>13.5227</v>
+        <v>14.8683</v>
       </c>
     </row>
     <row r="214">
@@ -10863,10 +10863,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.3905</v>
+        <v>0.4215</v>
       </c>
       <c r="J214" t="n">
-        <v>11.3245</v>
+        <v>12.2235</v>
       </c>
     </row>
     <row r="215">
@@ -10903,10 +10903,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2084</v>
+        <v>0.2165</v>
       </c>
       <c r="J215" t="n">
-        <v>6.0436</v>
+        <v>6.2785</v>
       </c>
     </row>
     <row r="216">
@@ -10943,10 +10943,10 @@
         <v>0.89</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4055</v>
+        <v>-0.3877</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.7595</v>
+        <v>-11.2433</v>
       </c>
     </row>
     <row r="217">
@@ -10983,10 +10983,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7378</v>
+        <v>0.8218</v>
       </c>
       <c r="J217" t="n">
-        <v>21.3962</v>
+        <v>23.8322</v>
       </c>
     </row>
     <row r="218">
@@ -11023,10 +11023,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1228</v>
+        <v>-0.1353</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.5612</v>
+        <v>-3.9237</v>
       </c>
     </row>
     <row r="219">
@@ -11063,10 +11063,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1559</v>
+        <v>-0.1691</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.5211</v>
+        <v>-4.9039</v>
       </c>
     </row>
     <row r="220">
@@ -11103,10 +11103,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1772</v>
+        <v>-0.1907</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.1388</v>
+        <v>-5.5303</v>
       </c>
     </row>
     <row r="221">
@@ -11143,10 +11143,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2388</v>
+        <v>-0.2522</v>
       </c>
       <c r="J221" t="n">
-        <v>-6.9252</v>
+        <v>-7.3138</v>
       </c>
     </row>
     <row r="222">
@@ -11183,10 +11183,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8723</v>
+        <v>0.9586</v>
       </c>
       <c r="J222" t="n">
-        <v>36.6366</v>
+        <v>40.2612</v>
       </c>
     </row>
     <row r="223">
@@ -11223,10 +11223,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.672</v>
+        <v>0.7421</v>
       </c>
       <c r="J223" t="n">
-        <v>28.224</v>
+        <v>31.1682</v>
       </c>
     </row>
     <row r="224">
@@ -11263,10 +11263,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3561</v>
+        <v>0.3705</v>
       </c>
       <c r="J224" t="n">
-        <v>14.9562</v>
+        <v>15.561</v>
       </c>
     </row>
     <row r="225">
@@ -11303,10 +11303,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2333</v>
+        <v>-0.2253</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.7986</v>
+        <v>-9.4626</v>
       </c>
     </row>
     <row r="226">
@@ -11343,10 +11343,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7356</v>
+        <v>-0.6819</v>
       </c>
       <c r="J226" t="n">
-        <v>-30.8952</v>
+        <v>-28.6398</v>
       </c>
     </row>
     <row r="227">
@@ -11383,10 +11383,10 @@
         <v>1.17</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3726</v>
+        <v>0.3938</v>
       </c>
       <c r="J227" t="n">
-        <v>15.6492</v>
+        <v>16.5396</v>
       </c>
     </row>
     <row r="228">
@@ -11423,10 +11423,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0594</v>
+        <v>-0.0697</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.4948</v>
+        <v>-2.9274</v>
       </c>
     </row>
     <row r="229">
@@ -11463,10 +11463,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1177</v>
+        <v>-0.1313</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.9434</v>
+        <v>-5.5146</v>
       </c>
     </row>
     <row r="230">
@@ -11503,10 +11503,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1717</v>
+        <v>-0.1864</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2114</v>
+        <v>-7.8288</v>
       </c>
     </row>
     <row r="231">
@@ -11543,10 +11543,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1821</v>
+        <v>-0.1969</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.6482</v>
+        <v>-8.2698</v>
       </c>
     </row>
     <row r="232">
@@ -11583,10 +11583,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2751</v>
+        <v>1.4036</v>
       </c>
       <c r="J232" t="n">
-        <v>25.502</v>
+        <v>28.072</v>
       </c>
     </row>
     <row r="233">
@@ -11623,10 +11623,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>0.9734</v>
+        <v>1.0829</v>
       </c>
       <c r="J233" t="n">
-        <v>19.468</v>
+        <v>21.658</v>
       </c>
     </row>
     <row r="234">
@@ -11663,10 +11663,10 @@
         <v>1.55</v>
       </c>
       <c r="I234" t="n">
-        <v>0.8726</v>
+        <v>0.9738</v>
       </c>
       <c r="J234" t="n">
-        <v>17.452</v>
+        <v>19.476</v>
       </c>
     </row>
     <row r="235">
@@ -11703,10 +11703,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6796</v>
+        <v>0.7635</v>
       </c>
       <c r="J235" t="n">
-        <v>13.592</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="236">
@@ -11743,10 +11743,10 @@
         <v>1.38</v>
       </c>
       <c r="I236" t="n">
-        <v>0.6669</v>
+        <v>0.7496</v>
       </c>
       <c r="J236" t="n">
-        <v>13.338</v>
+        <v>14.992</v>
       </c>
     </row>
     <row r="237">
@@ -11783,10 +11783,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.1664</v>
+        <v>-0.2</v>
       </c>
       <c r="J237" t="n">
-        <v>-3.328</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="238">
@@ -11823,10 +11823,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2237</v>
+        <v>-0.2545</v>
       </c>
       <c r="J238" t="n">
-        <v>-4.474</v>
+        <v>-5.09</v>
       </c>
     </row>
     <row r="239">
@@ -11863,10 +11863,10 @@
         <v>0.58</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.3803</v>
+        <v>-0.4023</v>
       </c>
       <c r="J239" t="n">
-        <v>-7.606</v>
+        <v>-8.045999999999999</v>
       </c>
     </row>
     <row r="240">
@@ -11903,10 +11903,10 @@
         <v>0.33</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6153</v>
+        <v>-0.6207</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.306</v>
+        <v>-12.414</v>
       </c>
     </row>
     <row r="241">
@@ -11943,10 +11943,10 @@
         <v>0.25</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6947</v>
+        <v>-0.6929</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.894</v>
+        <v>-13.858</v>
       </c>
     </row>
     <row r="242">
@@ -11983,10 +11983,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.0119</v>
+        <v>1.1078</v>
       </c>
       <c r="J242" t="n">
-        <v>26.3094</v>
+        <v>28.8028</v>
       </c>
     </row>
     <row r="243">
@@ -12023,10 +12023,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5312</v>
+        <v>0.5873</v>
       </c>
       <c r="J243" t="n">
-        <v>13.8112</v>
+        <v>15.2698</v>
       </c>
     </row>
     <row r="244">
@@ -12063,10 +12063,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4447</v>
+        <v>0.4901</v>
       </c>
       <c r="J244" t="n">
-        <v>11.5622</v>
+        <v>12.7426</v>
       </c>
     </row>
     <row r="245">
@@ -12103,10 +12103,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2288</v>
+        <v>0.2383</v>
       </c>
       <c r="J245" t="n">
-        <v>5.9488</v>
+        <v>6.1958</v>
       </c>
     </row>
     <row r="246">
@@ -12143,10 +12143,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-1.1026</v>
+        <v>-1.0013</v>
       </c>
       <c r="J246" t="n">
-        <v>-28.6676</v>
+        <v>-26.0338</v>
       </c>
     </row>
     <row r="247">
@@ -12183,10 +12183,10 @@
         <v>1.36</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5577</v>
+        <v>0.6214</v>
       </c>
       <c r="J247" t="n">
-        <v>14.5002</v>
+        <v>16.1564</v>
       </c>
     </row>
     <row r="248">
@@ -12223,10 +12223,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1802</v>
+        <v>0.1892</v>
       </c>
       <c r="J248" t="n">
-        <v>4.6852</v>
+        <v>4.9192</v>
       </c>
     </row>
     <row r="249">
@@ -12263,10 +12263,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1363</v>
+        <v>0.1457</v>
       </c>
       <c r="J249" t="n">
-        <v>3.5438</v>
+        <v>3.7882</v>
       </c>
     </row>
     <row r="250">
@@ -12303,10 +12303,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.136</v>
+        <v>-0.1483</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.536</v>
+        <v>-3.8558</v>
       </c>
     </row>
     <row r="251">
@@ -12343,10 +12343,10 @@
         <v>0.7</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.338</v>
+        <v>-0.3491</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.788</v>
+        <v>-9.076599999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12383,10 +12383,10 @@
         <v>1.85</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.7917</v>
       </c>
       <c r="J252" t="n">
-        <v>13.015</v>
+        <v>15.0423</v>
       </c>
     </row>
     <row r="253">
@@ -12423,10 +12423,10 @@
         <v>1.67</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5814</v>
+        <v>0.6718</v>
       </c>
       <c r="J253" t="n">
-        <v>11.0466</v>
+        <v>12.7642</v>
       </c>
     </row>
     <row r="254">
@@ -12463,10 +12463,10 @@
         <v>1.62</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5522</v>
+        <v>0.6378</v>
       </c>
       <c r="J254" t="n">
-        <v>10.4918</v>
+        <v>12.1182</v>
       </c>
     </row>
     <row r="255">
@@ -12503,10 +12503,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.3137</v>
+        <v>0.337</v>
       </c>
       <c r="J255" t="n">
-        <v>5.9603</v>
+        <v>6.403</v>
       </c>
     </row>
     <row r="256">
@@ -12543,10 +12543,10 @@
         <v>0.99</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0635</v>
+        <v>-0.0587</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.2065</v>
+        <v>-1.1153</v>
       </c>
     </row>
     <row r="257">
@@ -12583,10 +12583,10 @@
         <v>0.82</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1477</v>
+        <v>-0.1771</v>
       </c>
       <c r="J257" t="n">
-        <v>-2.8063</v>
+        <v>-3.3649</v>
       </c>
     </row>
     <row r="258">
@@ -12623,10 +12623,10 @@
         <v>0.76</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.215</v>
+        <v>-0.2421</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.085</v>
+        <v>-4.5999</v>
       </c>
     </row>
     <row r="259">
@@ -12663,10 +12663,10 @@
         <v>0.6</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3736</v>
+        <v>-0.3938</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.0984</v>
+        <v>-7.4822</v>
       </c>
     </row>
     <row r="260">
@@ -12703,10 +12703,10 @@
         <v>0.43</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5309</v>
+        <v>-0.5415</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.0871</v>
+        <v>-10.2885</v>
       </c>
     </row>
     <row r="261">
@@ -12743,10 +12743,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5788</v>
+        <v>-0.5857</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.9972</v>
+        <v>-11.1283</v>
       </c>
     </row>
     <row r="262">
@@ -12783,10 +12783,10 @@
         <v>0.91</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1095</v>
+        <v>-0.1251</v>
       </c>
       <c r="J262" t="n">
-        <v>-2.628</v>
+        <v>-3.0024</v>
       </c>
     </row>
     <row r="263">
@@ -12823,10 +12823,10 @@
         <v>0.89</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1316</v>
+        <v>-0.1478</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.1584</v>
+        <v>-3.5472</v>
       </c>
     </row>
     <row r="264">
@@ -12863,10 +12863,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1526</v>
+        <v>-0.1693</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.6624</v>
+        <v>-4.0632</v>
       </c>
     </row>
     <row r="265">
@@ -12903,10 +12903,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1526</v>
+        <v>-0.1693</v>
       </c>
       <c r="J265" t="n">
-        <v>-3.6624</v>
+        <v>-4.0632</v>
       </c>
     </row>
     <row r="266">
@@ -12943,10 +12943,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2516</v>
+        <v>-0.2684</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.0384</v>
+        <v>-6.4416</v>
       </c>
     </row>
     <row r="267">
@@ -12983,10 +12983,10 @@
         <v>1.64</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0245</v>
+        <v>1.1277</v>
       </c>
       <c r="J267" t="n">
-        <v>24.588</v>
+        <v>27.0648</v>
       </c>
     </row>
     <row r="268">
@@ -13023,10 +13023,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.8881</v>
       </c>
       <c r="J268" t="n">
-        <v>19.2216</v>
+        <v>21.3144</v>
       </c>
     </row>
     <row r="269">
@@ -13063,10 +13063,10 @@
         <v>1.31</v>
       </c>
       <c r="I269" t="n">
-        <v>0.6078</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="J269" t="n">
-        <v>14.5872</v>
+        <v>16.2456</v>
       </c>
     </row>
     <row r="270">
@@ -13103,10 +13103,10 @@
         <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0667</v>
+        <v>-0.0462</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.6008</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="271">
@@ -13143,10 +13143,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2351</v>
+        <v>-0.218</v>
       </c>
       <c r="J271" t="n">
-        <v>-5.6424</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="272">
@@ -13183,10 +13183,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4858</v>
+        <v>0.5399</v>
       </c>
       <c r="J272" t="n">
-        <v>14.574</v>
+        <v>16.197</v>
       </c>
     </row>
     <row r="273">
@@ -13223,10 +13223,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.1574</v>
+        <v>0.167</v>
       </c>
       <c r="J273" t="n">
-        <v>4.722</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="274">
@@ -13263,10 +13263,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1352</v>
+        <v>0.145</v>
       </c>
       <c r="J274" t="n">
-        <v>4.056</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="275">
@@ -13303,10 +13303,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1477</v>
+        <v>-0.1601</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.431</v>
+        <v>-4.803</v>
       </c>
     </row>
     <row r="276">
@@ -13343,10 +13343,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2214</v>
+        <v>-0.2344</v>
       </c>
       <c r="J276" t="n">
-        <v>-6.642</v>
+        <v>-7.032</v>
       </c>
     </row>
     <row r="277">
@@ -13383,10 +13383,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6395</v>
+        <v>0.7045</v>
       </c>
       <c r="J277" t="n">
-        <v>19.185</v>
+        <v>21.135</v>
       </c>
     </row>
     <row r="278">
@@ -13423,10 +13423,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.4963</v>
+        <v>0.5462</v>
       </c>
       <c r="J278" t="n">
-        <v>14.889</v>
+        <v>16.386</v>
       </c>
     </row>
     <row r="279">
@@ -13463,10 +13463,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2089</v>
+        <v>0.2168</v>
       </c>
       <c r="J279" t="n">
-        <v>6.267</v>
+        <v>6.504</v>
       </c>
     </row>
     <row r="280">
@@ -13503,10 +13503,10 @@
         <v>1.05</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1775</v>
+        <v>0.1869</v>
       </c>
       <c r="J280" t="n">
-        <v>5.325</v>
+        <v>5.607</v>
       </c>
     </row>
     <row r="281">
@@ -13543,10 +13543,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5161</v>
+        <v>-0.4882</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.483</v>
+        <v>-14.646</v>
       </c>
     </row>
     <row r="282">
@@ -13583,10 +13583,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0881</v>
+        <v>1.201</v>
       </c>
       <c r="J282" t="n">
-        <v>22.8501</v>
+        <v>25.221</v>
       </c>
     </row>
     <row r="283">
@@ -13623,10 +13623,10 @@
         <v>1.67</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0297</v>
+        <v>1.1388</v>
       </c>
       <c r="J283" t="n">
-        <v>21.6237</v>
+        <v>23.9148</v>
       </c>
     </row>
     <row r="284">
@@ -13663,10 +13663,10 @@
         <v>1.47</v>
       </c>
       <c r="I284" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8828</v>
       </c>
       <c r="J284" t="n">
-        <v>16.6278</v>
+        <v>18.5388</v>
       </c>
     </row>
     <row r="285">
@@ -13703,10 +13703,10 @@
         <v>1.15</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3662</v>
+        <v>0.3998</v>
       </c>
       <c r="J285" t="n">
-        <v>7.6902</v>
+        <v>8.395799999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13743,10 +13743,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2237</v>
+        <v>0.2487</v>
       </c>
       <c r="J286" t="n">
-        <v>4.6977</v>
+        <v>5.2227</v>
       </c>
     </row>
     <row r="287">
@@ -13783,10 +13783,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3902</v>
+        <v>0.3919</v>
       </c>
       <c r="J287" t="n">
-        <v>8.1942</v>
+        <v>8.229900000000001</v>
       </c>
     </row>
     <row r="288">
@@ -13823,10 +13823,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2661</v>
+        <v>-0.2877</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.5881</v>
+        <v>-6.0417</v>
       </c>
     </row>
     <row r="289">
@@ -13863,10 +13863,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4039</v>
+        <v>-0.4204</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.4819</v>
+        <v>-8.8284</v>
       </c>
     </row>
     <row r="290">
@@ -13903,10 +13903,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4788</v>
+        <v>-0.4909</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.0548</v>
+        <v>-10.3089</v>
       </c>
     </row>
     <row r="291">
@@ -13943,10 +13943,10 @@
         <v>0.46</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5163</v>
+        <v>-0.526</v>
       </c>
       <c r="J291" t="n">
-        <v>-10.8423</v>
+        <v>-11.046</v>
       </c>
     </row>
     <row r="292">
@@ -13983,10 +13983,10 @@
         <v>2.23</v>
       </c>
       <c r="I292" t="n">
-        <v>1.6345</v>
+        <v>1.777</v>
       </c>
       <c r="J292" t="n">
-        <v>29.421</v>
+        <v>31.986</v>
       </c>
     </row>
     <row r="293">
@@ -14023,10 +14023,10 @@
         <v>2.23</v>
       </c>
       <c r="I293" t="n">
-        <v>1.6345</v>
+        <v>1.777</v>
       </c>
       <c r="J293" t="n">
-        <v>29.421</v>
+        <v>31.986</v>
       </c>
     </row>
     <row r="294">
@@ -14063,10 +14063,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3356</v>
+        <v>0.3607</v>
       </c>
       <c r="J294" t="n">
-        <v>6.0408</v>
+        <v>6.4926</v>
       </c>
     </row>
     <row r="295">
@@ -14103,10 +14103,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3131</v>
+        <v>0.3363</v>
       </c>
       <c r="J295" t="n">
-        <v>5.6358</v>
+        <v>6.0534</v>
       </c>
     </row>
     <row r="296">
@@ -14143,10 +14143,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4718</v>
+        <v>-0.4283</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.4924</v>
+        <v>-7.7094</v>
       </c>
     </row>
     <row r="297">
@@ -14183,10 +14183,10 @@
         <v>0.65</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.3328</v>
+        <v>-0.3539</v>
       </c>
       <c r="J297" t="n">
-        <v>-5.9904</v>
+        <v>-6.3702</v>
       </c>
     </row>
     <row r="298">
@@ -14223,10 +14223,10 @@
         <v>0.65</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3328</v>
+        <v>-0.3539</v>
       </c>
       <c r="J298" t="n">
-        <v>-5.9904</v>
+        <v>-6.3702</v>
       </c>
     </row>
     <row r="299">
@@ -14263,10 +14263,10 @@
         <v>0.62</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3592</v>
+        <v>-0.3793</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.4656</v>
+        <v>-6.8274</v>
       </c>
     </row>
     <row r="300">
@@ -14303,10 +14303,10 @@
         <v>0.6</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3768</v>
+        <v>-0.3962</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.7824</v>
+        <v>-7.1316</v>
       </c>
     </row>
     <row r="301">
@@ -14343,10 +14343,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3768</v>
+        <v>-0.3962</v>
       </c>
       <c r="J301" t="n">
-        <v>-6.7824</v>
+        <v>-7.1316</v>
       </c>
     </row>
     <row r="302">
@@ -14383,10 +14383,10 @@
         <v>1.82</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1943</v>
+        <v>1.315</v>
       </c>
       <c r="J302" t="n">
-        <v>23.886</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="303">
@@ -14423,10 +14423,10 @@
         <v>1.73</v>
       </c>
       <c r="I303" t="n">
-        <v>1.0913</v>
+        <v>1.2059</v>
       </c>
       <c r="J303" t="n">
-        <v>21.826</v>
+        <v>24.118</v>
       </c>
     </row>
     <row r="304">
@@ -14463,10 +14463,10 @@
         <v>1.5</v>
       </c>
       <c r="I304" t="n">
-        <v>0.8228</v>
+        <v>0.9177</v>
       </c>
       <c r="J304" t="n">
-        <v>16.456</v>
+        <v>18.354</v>
       </c>
     </row>
     <row r="305">
@@ -14503,10 +14503,10 @@
         <v>1.14</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3442</v>
+        <v>0.3691</v>
       </c>
       <c r="J305" t="n">
-        <v>6.884</v>
+        <v>7.382</v>
       </c>
     </row>
     <row r="306">
@@ -14543,10 +14543,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3442</v>
+        <v>0.3691</v>
       </c>
       <c r="J306" t="n">
-        <v>6.884</v>
+        <v>7.382</v>
       </c>
     </row>
     <row r="307">
@@ -14583,10 +14583,10 @@
         <v>0.85</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1275</v>
+        <v>-0.1545</v>
       </c>
       <c r="J307" t="n">
-        <v>-2.55</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="308">
@@ -14623,10 +14623,10 @@
         <v>0.72</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.268</v>
+        <v>-0.2911</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.36</v>
+        <v>-5.822</v>
       </c>
     </row>
     <row r="309">
@@ -14663,10 +14663,10 @@
         <v>0.66</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3259</v>
+        <v>-0.3467</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.518</v>
+        <v>-6.934</v>
       </c>
     </row>
     <row r="310">
@@ -14703,10 +14703,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3974</v>
+        <v>-0.4153</v>
       </c>
       <c r="J310" t="n">
-        <v>-7.948</v>
+        <v>-8.305999999999999</v>
       </c>
     </row>
     <row r="311">
@@ -14743,10 +14743,10 @@
         <v>0.38</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5856</v>
+        <v>-0.591</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.712</v>
+        <v>-11.82</v>
       </c>
     </row>
     <row r="312">
@@ -14783,10 +14783,10 @@
         <v>1.99</v>
       </c>
       <c r="I312" t="n">
-        <v>1.3899</v>
+        <v>1.5197</v>
       </c>
       <c r="J312" t="n">
-        <v>29.1879</v>
+        <v>31.9137</v>
       </c>
     </row>
     <row r="313">
@@ -14823,10 +14823,10 @@
         <v>1.51</v>
       </c>
       <c r="I313" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.9319</v>
       </c>
       <c r="J313" t="n">
-        <v>17.5602</v>
+        <v>19.5699</v>
       </c>
     </row>
     <row r="314">
@@ -14863,10 +14863,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8125</v>
+        <v>0.9062</v>
       </c>
       <c r="J314" t="n">
-        <v>17.0625</v>
+        <v>19.0302</v>
       </c>
     </row>
     <row r="315">
@@ -14903,10 +14903,10 @@
         <v>1.22</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4663</v>
+        <v>0.524</v>
       </c>
       <c r="J315" t="n">
-        <v>9.792299999999999</v>
+        <v>11.004</v>
       </c>
     </row>
     <row r="316">
@@ -14943,10 +14943,10 @@
         <v>1.04</v>
       </c>
       <c r="I316" t="n">
-        <v>0.0624</v>
+        <v>0.098</v>
       </c>
       <c r="J316" t="n">
-        <v>1.3104</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="317">
@@ -14983,10 +14983,10 @@
         <v>0.79</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.1978</v>
+        <v>-0.2227</v>
       </c>
       <c r="J317" t="n">
-        <v>-4.1538</v>
+        <v>-4.6767</v>
       </c>
     </row>
     <row r="318">
@@ -15023,10 +15023,10 @@
         <v>0.67</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3182</v>
+        <v>-0.3391</v>
       </c>
       <c r="J318" t="n">
-        <v>-6.6822</v>
+        <v>-7.1211</v>
       </c>
     </row>
     <row r="319">
@@ -15063,10 +15063,10 @@
         <v>0.66</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3273</v>
+        <v>-0.3478</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.8733</v>
+        <v>-7.3038</v>
       </c>
     </row>
     <row r="320">
@@ -15103,10 +15103,10 @@
         <v>0.57</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4084</v>
+        <v>-0.4255</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.5764</v>
+        <v>-8.935499999999999</v>
       </c>
     </row>
     <row r="321">
@@ -15143,10 +15143,10 @@
         <v>0.55</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J321" t="n">
-        <v>-8.967000000000001</v>
+        <v>-9.305099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3454/event_3454_evp_summary.xlsx
+++ b/database/event/3454/event_3454_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9847</v>
+        <v>6.7454</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9064</v>
+        <v>1.8411</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5554</v>
+        <v>2.4671</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9847</v>
+        <v>6.7454</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4402</v>
+        <v>2.438</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5445</v>
+        <v>4.3074</v>
       </c>
       <c r="H2" t="n">
-        <v>2.616</v>
+        <v>2.637</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8962</v>
+        <v>2.9304</v>
       </c>
       <c r="J2" t="n">
-        <v>4.5445</v>
+        <v>4.3074</v>
       </c>
       <c r="K2" t="n">
         <v>105</v>
@@ -529,7 +529,7 @@
         <v>263</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4407</v>
+        <v>7.2378</v>
       </c>
       <c r="N2" t="n">
         <v>368</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2511</v>
+        <v>5.02</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4332</v>
+        <v>1.3702</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7662</v>
+        <v>1.6811</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2511</v>
+        <v>5.02</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9868</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2643</v>
+        <v>4.0981</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9868</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0383</v>
+        <v>0.9718</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2643</v>
+        <v>4.0981</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -575,7 +575,7 @@
         <v>181</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3026</v>
+        <v>5.0699</v>
       </c>
       <c r="N3" t="n">
         <v>231</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.953</v>
+        <v>4.7045</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3519</v>
+        <v>1.2841</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6305</v>
+        <v>1.5373</v>
       </c>
       <c r="E4" t="n">
-        <v>4.953</v>
+        <v>4.7045</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5521</v>
+        <v>2.5234</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4009</v>
+        <v>2.1812</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8609</v>
+        <v>2.8327</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1674</v>
+        <v>3.1478</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4009</v>
+        <v>2.1812</v>
       </c>
       <c r="K4" t="n">
         <v>105</v>
@@ -621,7 +621,7 @@
         <v>263</v>
       </c>
       <c r="M4" t="n">
-        <v>5.568300000000001</v>
+        <v>5.329000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>368</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8718</v>
+        <v>3.6888</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0568</v>
+        <v>1.0068</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1383</v>
+        <v>1.0746</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8718</v>
+        <v>3.6888</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1173</v>
+        <v>1.0515</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7545</v>
+        <v>2.6373</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1173</v>
+        <v>1.0515</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1756</v>
+        <v>1.1084</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7545</v>
+        <v>2.6373</v>
       </c>
       <c r="K5" t="n">
         <v>50</v>
@@ -667,7 +667,7 @@
         <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9301</v>
+        <v>3.7457</v>
       </c>
       <c r="N5" t="n">
         <v>231</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8564</v>
+        <v>3.6856</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0526</v>
+        <v>1.006</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1313</v>
+        <v>1.0732</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8564</v>
+        <v>3.6856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7466</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1098</v>
+        <v>3.6856</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7466</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7466</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1098</v>
+        <v>3.6856</v>
       </c>
       <c r="K6" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8564</v>
+        <v>3.6856</v>
       </c>
       <c r="N6" t="n">
-        <v>225</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7468</v>
+        <v>3.6368</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0227</v>
+        <v>0.9926</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0814</v>
+        <v>1.0509</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7468</v>
+        <v>3.6368</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.5745</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7468</v>
+        <v>3.0623</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.5745</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5745</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7468</v>
+        <v>3.0623</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="L7" t="n">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7468</v>
+        <v>3.6368</v>
       </c>
       <c r="N7" t="n">
-        <v>162</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5493</v>
+        <v>3.5132</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9688</v>
+        <v>0.9589</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9915</v>
+        <v>0.9946</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5493</v>
+        <v>3.5132</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1102</v>
+        <v>1.0952</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4391</v>
+        <v>2.418</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1102</v>
+        <v>1.0952</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1682</v>
+        <v>1.1545</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4391</v>
+        <v>2.418</v>
       </c>
       <c r="K8" t="n">
         <v>50</v>
@@ -805,7 +805,7 @@
         <v>181</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6073</v>
+        <v>3.5725</v>
       </c>
       <c r="N8" t="n">
         <v>231</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5368</v>
+        <v>3.374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9653</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9858</v>
+        <v>0.9312</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5368</v>
+        <v>3.374</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2564</v>
+        <v>2.2878</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2804</v>
+        <v>1.0861</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2564</v>
+        <v>2.2929</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4981</v>
+        <v>2.548</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2804</v>
+        <v>1.0861</v>
       </c>
       <c r="K9" t="n">
         <v>105</v>
@@ -851,7 +851,7 @@
         <v>263</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7785</v>
+        <v>3.6341</v>
       </c>
       <c r="N9" t="n">
         <v>368</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2757</v>
+        <v>3.3025</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8941</v>
+        <v>0.9014</v>
       </c>
       <c r="D10" t="n">
-        <v>0.867</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2757</v>
+        <v>3.3025</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6018</v>
+        <v>-0.5594</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8775</v>
+        <v>3.8619</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6018</v>
+        <v>-0.5594</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6018</v>
+        <v>-0.5594</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8775</v>
+        <v>3.8619</v>
       </c>
       <c r="K10" t="n">
         <v>113</v>
@@ -897,7 +897,7 @@
         <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2757</v>
+        <v>3.3025</v>
       </c>
       <c r="N10" t="n">
         <v>225</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8142</v>
+        <v>2.734</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7681</v>
+        <v>0.7462</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6569</v>
+        <v>0.6397</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8142</v>
+        <v>2.734</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4259</v>
+        <v>2.3857</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3883</v>
+        <v>0.3483</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5847</v>
+        <v>2.5173</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8616</v>
+        <v>2.7973</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3883</v>
+        <v>0.3483</v>
       </c>
       <c r="K11" t="n">
         <v>105</v>
@@ -943,7 +943,7 @@
         <v>263</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2499</v>
+        <v>3.1456</v>
       </c>
       <c r="N11" t="n">
         <v>368</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6882</v>
+        <v>2.5252</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7337</v>
+        <v>0.6892</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5995</v>
+        <v>0.5446</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6882</v>
+        <v>2.5252</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4974</v>
+        <v>0.4142</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1908</v>
+        <v>2.111</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4974</v>
+        <v>0.4142</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4974</v>
+        <v>0.4142</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1908</v>
+        <v>2.111</v>
       </c>
       <c r="K12" t="n">
         <v>113</v>
@@ -989,7 +989,7 @@
         <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6882</v>
+        <v>2.5252</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.076</v>
+        <v>1.9965</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5666</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3208</v>
+        <v>0.3037</v>
       </c>
       <c r="E13" t="n">
-        <v>2.076</v>
+        <v>1.9965</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4123</v>
+        <v>2.3932</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3363</v>
+        <v>-0.3967</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5548</v>
+        <v>2.5342</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9762</v>
+        <v>2.9687</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3363</v>
+        <v>-0.3967</v>
       </c>
       <c r="K13" t="n">
         <v>164</v>
@@ -1035,7 +1035,7 @@
         <v>359</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6399</v>
+        <v>2.572</v>
       </c>
       <c r="N13" t="n">
         <v>523</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0323</v>
+        <v>1.9679</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5547</v>
+        <v>0.5371</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3009</v>
+        <v>0.2907</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0323</v>
+        <v>1.9679</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5222</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5101</v>
+        <v>1.4663</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5222</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5495</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5101</v>
+        <v>1.4663</v>
       </c>
       <c r="K14" t="n">
         <v>122</v>
@@ -1081,7 +1081,7 @@
         <v>98</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0596</v>
+        <v>1.995</v>
       </c>
       <c r="N14" t="n">
         <v>220</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9777</v>
+        <v>1.9339</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5278</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2761</v>
+        <v>0.2752</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9777</v>
+        <v>1.9339</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.6831</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7353</v>
+        <v>2.617</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.6831</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7971</v>
+        <v>-0.7201</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7353</v>
+        <v>2.617</v>
       </c>
       <c r="K15" t="n">
         <v>50</v>
@@ -1127,7 +1127,7 @@
         <v>181</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9382</v>
+        <v>1.8969</v>
       </c>
       <c r="N15" t="n">
         <v>231</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9043</v>
+        <v>1.9164</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5198</v>
+        <v>0.5231</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2427</v>
+        <v>0.2672</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9043</v>
+        <v>1.9164</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9043</v>
+        <v>1.9164</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9043</v>
+        <v>1.9164</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>162</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9043</v>
+        <v>1.9164</v>
       </c>
       <c r="N16" t="n">
         <v>162</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8288</v>
+        <v>1.785</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4992</v>
+        <v>0.4872</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2083</v>
+        <v>0.2074</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8288</v>
+        <v>1.785</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7762</v>
+        <v>1.7842</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0526</v>
+        <v>0.0008</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7762</v>
+        <v>1.7842</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7962</v>
+        <v>1.8808</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0526</v>
+        <v>0.0008</v>
       </c>
       <c r="K17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L17" t="n">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8488</v>
+        <v>1.8816</v>
       </c>
       <c r="N17" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8263</v>
+        <v>1.6802</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4985</v>
+        <v>0.4586</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2072</v>
+        <v>0.1596</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8263</v>
+        <v>1.6802</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8009</v>
+        <v>0.6859</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0254</v>
+        <v>0.9943</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8009</v>
+        <v>0.6859</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8949</v>
+        <v>0.7042</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0254</v>
+        <v>0.9943</v>
       </c>
       <c r="K18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L18" t="n">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="M18" t="n">
-        <v>1.9203</v>
+        <v>1.6985</v>
       </c>
       <c r="N18" t="n">
-        <v>231</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3712</v>
+        <v>1.3349</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3743</v>
+        <v>0.3643</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>0.0023</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3712</v>
+        <v>1.3349</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3712</v>
+        <v>1.3349</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3712</v>
+        <v>1.3349</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>162</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3712</v>
+        <v>1.3349</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.05</v>
+        <v>0.918</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2866</v>
+        <v>0.2506</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1462</v>
+        <v>-0.1876</v>
       </c>
       <c r="E20" t="n">
-        <v>1.05</v>
+        <v>0.918</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3143</v>
+        <v>0.2054</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7357</v>
+        <v>0.7126</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3143</v>
+        <v>0.2054</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3307</v>
+        <v>0.2165</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7357</v>
+        <v>0.7126</v>
       </c>
       <c r="K20" t="n">
         <v>122</v>
@@ -1357,7 +1357,7 @@
         <v>98</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0664</v>
+        <v>0.9291</v>
       </c>
       <c r="N20" t="n">
         <v>220</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8511</v>
+        <v>0.7722</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2323</v>
+        <v>0.2108</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2368</v>
+        <v>-0.254</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8511</v>
+        <v>0.7722</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6375</v>
+        <v>0.1677</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2136</v>
+        <v>0.6045</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6375</v>
+        <v>0.1677</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6539</v>
+        <v>0.1768</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2136</v>
+        <v>0.6045</v>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="L21" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8675</v>
+        <v>0.7813000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>153</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7936</v>
+        <v>0.7614</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2166</v>
+        <v>0.2078</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2629</v>
+        <v>-0.2589</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7936</v>
+        <v>0.7614</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2058</v>
+        <v>1.1833</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4122</v>
+        <v>-0.4219</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2058</v>
+        <v>1.1833</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2687</v>
+        <v>1.2474</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4122</v>
+        <v>-0.4219</v>
       </c>
       <c r="K22" t="n">
         <v>59</v>
@@ -1449,7 +1449,7 @@
         <v>96</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8564999999999999</v>
+        <v>0.8255000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>155</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7773</v>
+        <v>0.667</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2122</v>
+        <v>0.1821</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2704</v>
+        <v>-0.3019</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7773</v>
+        <v>0.667</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1005</v>
+        <v>0.5206</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6768</v>
+        <v>0.1465</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1005</v>
+        <v>0.5206</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1057</v>
+        <v>0.5345</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6768</v>
+        <v>0.1465</v>
       </c>
       <c r="K23" t="n">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="L23" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7825</v>
+        <v>0.6809999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>220</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24">
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7094</v>
+        <v>0.6122</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1936</v>
+        <v>0.1671</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3013</v>
+        <v>-0.3269</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7094</v>
+        <v>0.6122</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0399</v>
+        <v>0.0075</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6695</v>
+        <v>0.6047</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0399</v>
+        <v>0.0075</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0409</v>
+        <v>0.0077</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6695</v>
+        <v>0.6047</v>
       </c>
       <c r="K24" t="n">
         <v>80</v>
@@ -1541,7 +1541,7 @@
         <v>73</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7104</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>153</v>
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5562</v>
+        <v>0.5787</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1518</v>
+        <v>0.158</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.371</v>
+        <v>-0.3422</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5562</v>
+        <v>0.5787</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5562</v>
+        <v>0.5787</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5562</v>
+        <v>0.5787</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>162</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5562</v>
+        <v>0.5787</v>
       </c>
       <c r="N25" t="n">
         <v>162</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5119</v>
+        <v>0.5231</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1397</v>
+        <v>0.1428</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3912</v>
+        <v>-0.3675</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5119</v>
+        <v>0.5231</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1504</v>
+        <v>-0.177</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6623</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1504</v>
+        <v>-0.177</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1504</v>
+        <v>-0.177</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6623</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>113</v>
@@ -1633,7 +1633,7 @@
         <v>112</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5119</v>
+        <v>0.5230999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>225</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3567</v>
+        <v>0.3195</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0974</v>
+        <v>0.0872</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4618</v>
+        <v>-0.4602</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3567</v>
+        <v>0.3195</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1056</v>
+        <v>-0.1262</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4623</v>
+        <v>0.4457</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1056</v>
+        <v>-0.1262</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1083</v>
+        <v>-0.1296</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4623</v>
+        <v>0.4457</v>
       </c>
       <c r="K27" t="n">
         <v>80</v>
@@ -1679,7 +1679,7 @@
         <v>73</v>
       </c>
       <c r="M27" t="n">
-        <v>0.354</v>
+        <v>0.3161</v>
       </c>
       <c r="N27" t="n">
         <v>153</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1996</v>
+        <v>0.1507</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0545</v>
+        <v>0.0411</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5333</v>
+        <v>-0.5371</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1996</v>
+        <v>0.1507</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6405</v>
+        <v>0.5472</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4409</v>
+        <v>-0.3965</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6405</v>
+        <v>0.5472</v>
       </c>
       <c r="I28" t="n">
-        <v>0.657</v>
+        <v>0.5618</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4409</v>
+        <v>-0.3965</v>
       </c>
       <c r="K28" t="n">
         <v>80</v>
@@ -1725,7 +1725,7 @@
         <v>73</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2161</v>
+        <v>0.1652999999999999</v>
       </c>
       <c r="N28" t="n">
         <v>153</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1663</v>
+        <v>0.1413</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0454</v>
+        <v>0.0386</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5485</v>
+        <v>-0.5414</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1663</v>
+        <v>0.1413</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3292</v>
+        <v>-0.3473</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4955</v>
+        <v>0.4886</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3292</v>
+        <v>-0.3473</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3464</v>
+        <v>-0.3661</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4955</v>
+        <v>0.4886</v>
       </c>
       <c r="K29" t="n">
         <v>122</v>
@@ -1771,7 +1771,7 @@
         <v>98</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1491</v>
+        <v>0.1225</v>
       </c>
       <c r="N29" t="n">
         <v>220</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0147</v>
+        <v>-0.0487</v>
       </c>
       <c r="C30" t="n">
-        <v>0.004</v>
+        <v>-0.0133</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6175</v>
+        <v>-0.628</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0147</v>
+        <v>-0.0487</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.618</v>
+        <v>0.5697</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6327</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.618</v>
+        <v>0.5697</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.618</v>
+        <v>0.5697</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6327</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="L30" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="M30" t="n">
-        <v>0.01470000000000005</v>
+        <v>-0.04869999999999997</v>
       </c>
       <c r="N30" t="n">
-        <v>225</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0314</v>
+        <v>-0.1029</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0086</v>
+        <v>-0.0281</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6385</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0314</v>
+        <v>-0.1029</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6102</v>
+        <v>-0.6935</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.5906</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6102</v>
+        <v>-0.6935</v>
       </c>
       <c r="I31" t="n">
-        <v>0.6102</v>
+        <v>-0.6935</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.5906</v>
       </c>
       <c r="K31" t="n">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.03139999999999998</v>
+        <v>-0.1029</v>
       </c>
       <c r="N31" t="n">
-        <v>98</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5023</v>
+        <v>-0.5292</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1371</v>
+        <v>-0.1444</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8529</v>
+        <v>-0.8469</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5023</v>
+        <v>-0.5292</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6422</v>
+        <v>0.5772</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.1445</v>
+        <v>-1.1064</v>
       </c>
       <c r="H32" t="n">
-        <v>0.6422</v>
+        <v>0.5772</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6757</v>
+        <v>0.6085</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.1445</v>
+        <v>-1.1064</v>
       </c>
       <c r="K32" t="n">
         <v>59</v>
@@ -1909,7 +1909,7 @@
         <v>96</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4688000000000001</v>
+        <v>-0.4979</v>
       </c>
       <c r="N32" t="n">
         <v>155</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5851</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1597</v>
+        <v>-0.1553</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.865</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5851</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6231</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.038</v>
+        <v>0.0191</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6231</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6231</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>0.038</v>
+        <v>0.0191</v>
       </c>
       <c r="K33" t="n">
         <v>59</v>
@@ -1955,7 +1955,7 @@
         <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5851</v>
+        <v>-0.5690999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>98</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7309</v>
+        <v>-0.7076</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1995</v>
+        <v>-0.1931</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9569</v>
+        <v>-0.9281</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7309</v>
+        <v>-0.7076</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5138</v>
+        <v>-0.4644</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2171</v>
+        <v>-0.2432</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5138</v>
+        <v>-0.4644</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5406</v>
+        <v>-0.4895</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2171</v>
+        <v>-0.2432</v>
       </c>
       <c r="K34" t="n">
         <v>122</v>
@@ -2001,7 +2001,7 @@
         <v>98</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7576999999999999</v>
+        <v>-0.7327</v>
       </c>
       <c r="N34" t="n">
         <v>220</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hutji</t>
+          <t>Pollo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8023</v>
+        <v>-0.7569</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.219</v>
+        <v>-0.2066</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.9506</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8023</v>
+        <v>-0.7569</v>
       </c>
       <c r="F35" t="n">
-        <v>0.103</v>
+        <v>0.1115</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.9053</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.103</v>
+        <v>0.1115</v>
       </c>
       <c r="I35" t="n">
-        <v>0.103</v>
+        <v>0.1175</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9053</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="K35" t="n">
         <v>59</v>
       </c>
       <c r="L35" t="n">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8023</v>
+        <v>-0.7508999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>98</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8141</v>
+        <v>-0.8193</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2222</v>
+        <v>-0.2236</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9948</v>
+        <v>-0.979</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8141</v>
+        <v>-0.8193</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0025</v>
+        <v>-0.0209</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8166</v>
+        <v>-0.7984</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0025</v>
+        <v>-0.0209</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0025</v>
+        <v>-0.0209</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8166</v>
+        <v>-0.7984</v>
       </c>
       <c r="K36" t="n">
         <v>59</v>
@@ -2093,7 +2093,7 @@
         <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8141</v>
+        <v>-0.8193</v>
       </c>
       <c r="N36" t="n">
         <v>98</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pollo</t>
+          <t>hutji</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8156</v>
+        <v>-0.825</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2226</v>
+        <v>-0.2252</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.9816</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8156</v>
+        <v>-0.825</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1077</v>
+        <v>0.0722</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9233</v>
+        <v>-0.8972</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1077</v>
+        <v>0.0722</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1133</v>
+        <v>0.0722</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9233</v>
+        <v>-0.8972</v>
       </c>
       <c r="K37" t="n">
         <v>59</v>
       </c>
       <c r="L37" t="n">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.825</v>
       </c>
       <c r="N37" t="n">
-        <v>155</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8348</v>
+        <v>-0.8467</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2279</v>
+        <v>-0.2311</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0042</v>
+        <v>-0.9915</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8348</v>
+        <v>-0.8467</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0523</v>
+        <v>0.0285</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.8871</v>
+        <v>-0.8752</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0523</v>
+        <v>0.0285</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0523</v>
+        <v>0.0285</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.8871</v>
+        <v>-0.8752</v>
       </c>
       <c r="K38" t="n">
         <v>59</v>
@@ -2185,7 +2185,7 @@
         <v>39</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8348</v>
+        <v>-0.8467</v>
       </c>
       <c r="N38" t="n">
         <v>98</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9123</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2547</v>
+        <v>-0.249</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0489</v>
+        <v>-1.0214</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9330000000000001</v>
+        <v>-0.9123</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.1151</v>
+        <v>-0.1026</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.8179</v>
+        <v>-0.8097</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.1151</v>
+        <v>-0.1026</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1211</v>
+        <v>-0.1082</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8179</v>
+        <v>-0.8097</v>
       </c>
       <c r="K39" t="n">
         <v>59</v>
@@ -2231,7 +2231,7 @@
         <v>96</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.9178999999999999</v>
       </c>
       <c r="N39" t="n">
         <v>155</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2747</v>
+        <v>-1.2198</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3479</v>
+        <v>-0.3329</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2045</v>
+        <v>-1.1615</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2747</v>
+        <v>-1.2198</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.2747</v>
+        <v>-1.2198</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.2747</v>
+        <v>-1.2198</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>162</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2747</v>
+        <v>-1.2198</v>
       </c>
       <c r="N40" t="n">
         <v>162</v>
@@ -2383,10 +2383,10 @@
         <v>1.12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2117</v>
+        <v>0.166</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2117</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="3">
@@ -2423,10 +2423,10 @@
         <v>1.11</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1977</v>
+        <v>0.1539</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1977</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="4">
@@ -2463,10 +2463,10 @@
         <v>1.07</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1387</v>
+        <v>0.1043</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1387</v>
+        <v>0.1043</v>
       </c>
     </row>
     <row r="5">
@@ -2503,10 +2503,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0898</v>
+        <v>0.0648</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0898</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="6">
@@ -2543,10 +2543,10 @@
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2252</v>
+        <v>-0.2048</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2252</v>
+        <v>-0.2048</v>
       </c>
     </row>
     <row r="7">
@@ -2583,10 +2583,10 @@
         <v>1.27</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5311</v>
+        <v>0.4715</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5311</v>
+        <v>0.4715</v>
       </c>
     </row>
     <row r="8">
@@ -2623,10 +2623,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3842</v>
+        <v>0.3295</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3842</v>
+        <v>0.3295</v>
       </c>
     </row>
     <row r="9">
@@ -2663,10 +2663,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0924</v>
+        <v>0.0699</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0924</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="10">
@@ -2703,10 +2703,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0033</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0051</v>
+        <v>-0.0033</v>
       </c>
     </row>
     <row r="11">
@@ -2743,10 +2743,10 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.142</v>
+        <v>-0.1224</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.142</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3092</v>
+        <v>0.2699</v>
       </c>
       <c r="J12" t="n">
-        <v>11.1312</v>
+        <v>9.7164</v>
       </c>
     </row>
     <row r="13">
@@ -2823,10 +2823,10 @@
         <v>0.87</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1556</v>
+        <v>-0.1401</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.6016</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="14">
@@ -2863,10 +2863,10 @@
         <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.349</v>
+        <v>-0.3347</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.564</v>
+        <v>-12.0492</v>
       </c>
     </row>
     <row r="15">
@@ -2903,10 +2903,10 @@
         <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4029</v>
+        <v>-0.3917</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.5044</v>
+        <v>-14.1012</v>
       </c>
     </row>
     <row r="16">
@@ -2943,10 +2943,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4999</v>
+        <v>-0.4984</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.9964</v>
+        <v>-17.9424</v>
       </c>
     </row>
     <row r="17">
@@ -2983,10 +2983,10 @@
         <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7954</v>
+        <v>0.7238</v>
       </c>
       <c r="J17" t="n">
-        <v>28.6344</v>
+        <v>26.0568</v>
       </c>
     </row>
     <row r="18">
@@ -3023,10 +3023,10 @@
         <v>1.4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5049</v>
+        <v>0.4398</v>
       </c>
       <c r="J18" t="n">
-        <v>18.1764</v>
+        <v>15.8328</v>
       </c>
     </row>
     <row r="19">
@@ -3063,10 +3063,10 @@
         <v>1.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4647</v>
+        <v>0.4021</v>
       </c>
       <c r="J19" t="n">
-        <v>16.7292</v>
+        <v>14.4756</v>
       </c>
     </row>
     <row r="20">
@@ -3103,10 +3103,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3574</v>
+        <v>0.3028</v>
       </c>
       <c r="J20" t="n">
-        <v>12.8664</v>
+        <v>10.9008</v>
       </c>
     </row>
     <row r="21">
@@ -3143,10 +3143,10 @@
         <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1413</v>
+        <v>0.1092</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0868</v>
+        <v>3.9312</v>
       </c>
     </row>
     <row r="22">
@@ -3183,10 +3183,10 @@
         <v>1.28</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5447</v>
+        <v>0.485</v>
       </c>
       <c r="J22" t="n">
-        <v>13.0728</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="23">
@@ -3223,10 +3223,10 @@
         <v>1.1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2403</v>
+        <v>0.1974</v>
       </c>
       <c r="J23" t="n">
-        <v>5.7672</v>
+        <v>4.7376</v>
       </c>
     </row>
     <row r="24">
@@ -3263,10 +3263,10 @@
         <v>1.03</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0912</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1888</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="25">
@@ -3303,10 +3303,10 @@
         <v>1.03</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0912</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>2.1888</v>
+        <v>1.656</v>
       </c>
     </row>
     <row r="26">
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0058</v>
+        <v>-0.0039</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1392</v>
+        <v>-0.0936</v>
       </c>
     </row>
     <row r="27">
@@ -3383,10 +3383,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3991</v>
+        <v>0.3357</v>
       </c>
       <c r="J27" t="n">
-        <v>9.5784</v>
+        <v>8.056800000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3423,10 +3423,10 @@
         <v>1.11</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1959</v>
+        <v>0.1527</v>
       </c>
       <c r="J28" t="n">
-        <v>4.7016</v>
+        <v>3.6648</v>
       </c>
     </row>
     <row r="29">
@@ -3463,10 +3463,10 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0288</v>
+        <v>0.019</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6912</v>
+        <v>0.456</v>
       </c>
     </row>
     <row r="30">
@@ -3503,10 +3503,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0286</v>
+        <v>-0.0203</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6864</v>
+        <v>-0.4872</v>
       </c>
     </row>
     <row r="31">
@@ -3543,10 +3543,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1846</v>
+        <v>-0.164</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.4304</v>
+        <v>-3.936</v>
       </c>
     </row>
     <row r="32">
@@ -3583,10 +3583,10 @@
         <v>1.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1342</v>
+        <v>0.0994</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6234</v>
+        <v>2.6838</v>
       </c>
     </row>
     <row r="33">
@@ -3623,10 +3623,10 @@
         <v>1.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1342</v>
+        <v>0.0994</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6234</v>
+        <v>2.6838</v>
       </c>
     </row>
     <row r="34">
@@ -3663,10 +3663,10 @@
         <v>0.97</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0549</v>
+        <v>-0.0439</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.4823</v>
+        <v>-1.1853</v>
       </c>
     </row>
     <row r="35">
@@ -3703,10 +3703,10 @@
         <v>0.89</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1533</v>
+        <v>-0.1341</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.1391</v>
+        <v>-3.6207</v>
       </c>
     </row>
     <row r="36">
@@ -3743,10 +3743,10 @@
         <v>0.73</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3144</v>
+        <v>-0.2971</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.488799999999999</v>
+        <v>-8.021699999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3783,10 +3783,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0875</v>
+        <v>1.0501</v>
       </c>
       <c r="J37" t="n">
-        <v>29.3625</v>
+        <v>28.3527</v>
       </c>
     </row>
     <row r="38">
@@ -3823,10 +3823,10 @@
         <v>1.26</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4981</v>
+        <v>0.4412</v>
       </c>
       <c r="J38" t="n">
-        <v>13.4487</v>
+        <v>11.9124</v>
       </c>
     </row>
     <row r="39">
@@ -3863,10 +3863,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3221</v>
+        <v>0.2751</v>
       </c>
       <c r="J39" t="n">
-        <v>8.6967</v>
+        <v>7.4277</v>
       </c>
     </row>
     <row r="40">
@@ -3903,10 +3903,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1384</v>
+        <v>-0.1194</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.7368</v>
+        <v>-3.2238</v>
       </c>
     </row>
     <row r="41">
@@ -3943,10 +3943,10 @@
         <v>0.89</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1732</v>
+        <v>-0.1534</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.6764</v>
+        <v>-4.1418</v>
       </c>
     </row>
     <row r="42">
@@ -3983,10 +3983,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4461</v>
+        <v>0.3881</v>
       </c>
       <c r="J42" t="n">
-        <v>16.0596</v>
+        <v>13.9716</v>
       </c>
     </row>
     <row r="43">
@@ -4023,10 +4023,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1222</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>4.3992</v>
+        <v>3.3408</v>
       </c>
     </row>
     <row r="44">
@@ -4063,10 +4063,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0419</v>
+        <v>0.0288</v>
       </c>
       <c r="J44" t="n">
-        <v>1.5084</v>
+        <v>1.0368</v>
       </c>
     </row>
     <row r="45">
@@ -4103,10 +4103,10 @@
         <v>0.93</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1131</v>
+        <v>-0.0951</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.0716</v>
+        <v>-3.4236</v>
       </c>
     </row>
     <row r="46">
@@ -4143,10 +4143,10 @@
         <v>0.91</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1371</v>
+        <v>-0.1178</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.9356</v>
+        <v>-4.2408</v>
       </c>
     </row>
     <row r="47">
@@ -4183,10 +4183,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6567</v>
+        <v>0.6208</v>
       </c>
       <c r="J47" t="n">
-        <v>23.6412</v>
+        <v>22.3488</v>
       </c>
     </row>
     <row r="48">
@@ -4223,10 +4223,10 @@
         <v>1.21</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5903</v>
+        <v>0.5516</v>
       </c>
       <c r="J48" t="n">
-        <v>21.2508</v>
+        <v>19.8576</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1264</v>
+        <v>0.1027</v>
       </c>
       <c r="J49" t="n">
-        <v>4.5504</v>
+        <v>3.6972</v>
       </c>
     </row>
     <row r="50">
@@ -4303,10 +4303,10 @@
         <v>0.98</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1113</v>
+        <v>-0.0852</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.0068</v>
+        <v>-3.0672</v>
       </c>
     </row>
     <row r="51">
@@ -4343,10 +4343,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3823</v>
+        <v>-0.3393</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.7628</v>
+        <v>-12.2148</v>
       </c>
     </row>
     <row r="52">
@@ -4383,10 +4383,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5088</v>
+        <v>0.4551</v>
       </c>
       <c r="J52" t="n">
-        <v>13.7376</v>
+        <v>12.2877</v>
       </c>
     </row>
     <row r="53">
@@ -4423,10 +4423,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0985</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>2.6595</v>
+        <v>1.9683</v>
       </c>
     </row>
     <row r="54">
@@ -4463,10 +4463,10 @@
         <v>0.87</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1695</v>
+        <v>-0.1515</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.5765</v>
+        <v>-4.0905</v>
       </c>
     </row>
     <row r="55">
@@ -4503,10 +4503,10 @@
         <v>0.66</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3713</v>
+        <v>-0.3576</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.0251</v>
+        <v>-9.655200000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4543,10 +4543,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4601</v>
+        <v>-0.455</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.4227</v>
+        <v>-12.285</v>
       </c>
     </row>
     <row r="57">
@@ -4583,10 +4583,10 @@
         <v>1.58</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1986</v>
+        <v>1.2133</v>
       </c>
       <c r="J57" t="n">
-        <v>32.3622</v>
+        <v>32.7591</v>
       </c>
     </row>
     <row r="58">
@@ -4623,10 +4623,10 @@
         <v>1.51</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1051</v>
+        <v>1.1168</v>
       </c>
       <c r="J58" t="n">
-        <v>29.8377</v>
+        <v>30.1536</v>
       </c>
     </row>
     <row r="59">
@@ -4663,10 +4663,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4239</v>
+        <v>0.3914</v>
       </c>
       <c r="J59" t="n">
-        <v>11.4453</v>
+        <v>10.5678</v>
       </c>
     </row>
     <row r="60">
@@ -4703,10 +4703,10 @@
         <v>1.05</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1586</v>
+        <v>0.1327</v>
       </c>
       <c r="J60" t="n">
-        <v>4.2822</v>
+        <v>3.5829</v>
       </c>
     </row>
     <row r="61">
@@ -4743,10 +4743,10 @@
         <v>1.03</v>
       </c>
       <c r="I61" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J61" t="n">
-        <v>2.5164</v>
+        <v>1.9629</v>
       </c>
     </row>
     <row r="62">
@@ -4783,10 +4783,10 @@
         <v>1.5</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1051</v>
+        <v>1.1166</v>
       </c>
       <c r="J62" t="n">
-        <v>27.6275</v>
+        <v>27.915</v>
       </c>
     </row>
     <row r="63">
@@ -4823,10 +4823,10 @@
         <v>1.31</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7739</v>
+        <v>0.7478</v>
       </c>
       <c r="J63" t="n">
-        <v>19.3475</v>
+        <v>18.695</v>
       </c>
     </row>
     <row r="64">
@@ -4863,10 +4863,10 @@
         <v>1.23</v>
       </c>
       <c r="I64" t="n">
-        <v>0.6091</v>
+        <v>0.576</v>
       </c>
       <c r="J64" t="n">
-        <v>15.2275</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="65">
@@ -4903,10 +4903,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3618</v>
+        <v>0.3278</v>
       </c>
       <c r="J65" t="n">
-        <v>9.045</v>
+        <v>8.195</v>
       </c>
     </row>
     <row r="66">
@@ -4943,10 +4943,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5783</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.4575</v>
+        <v>-13.545</v>
       </c>
     </row>
     <row r="67">
@@ -4983,10 +4983,10 @@
         <v>1.1</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2708</v>
+        <v>0.2227</v>
       </c>
       <c r="J67" t="n">
-        <v>6.77</v>
+        <v>5.5675</v>
       </c>
     </row>
     <row r="68">
@@ -5023,10 +5023,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0936</v>
+        <v>-0.079</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.34</v>
+        <v>-1.975</v>
       </c>
     </row>
     <row r="69">
@@ -5063,10 +5063,10 @@
         <v>0.91</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.129</v>
+        <v>-0.1117</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.225</v>
+        <v>-2.7925</v>
       </c>
     </row>
     <row r="70">
@@ -5103,10 +5103,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1402</v>
+        <v>-0.1222</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.505</v>
+        <v>-3.055</v>
       </c>
     </row>
     <row r="71">
@@ -5143,10 +5143,10 @@
         <v>0.73</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3119</v>
+        <v>-0.2944</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.7975</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="72">
@@ -5183,10 +5183,10 @@
         <v>1.82</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4372</v>
+        <v>1.4678</v>
       </c>
       <c r="J72" t="n">
-        <v>24.4324</v>
+        <v>24.9526</v>
       </c>
     </row>
     <row r="73">
@@ -5223,10 +5223,10 @@
         <v>1.77</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3788</v>
+        <v>1.4069</v>
       </c>
       <c r="J73" t="n">
-        <v>23.4396</v>
+        <v>23.9173</v>
       </c>
     </row>
     <row r="74">
@@ -5263,10 +5263,10 @@
         <v>1.72</v>
       </c>
       <c r="I74" t="n">
-        <v>1.32</v>
+        <v>1.3462</v>
       </c>
       <c r="J74" t="n">
-        <v>22.44</v>
+        <v>22.8854</v>
       </c>
     </row>
     <row r="75">
@@ -5303,10 +5303,10 @@
         <v>1.56</v>
       </c>
       <c r="I75" t="n">
-        <v>1.1285</v>
+        <v>1.151</v>
       </c>
       <c r="J75" t="n">
-        <v>19.1845</v>
+        <v>19.567</v>
       </c>
     </row>
     <row r="76">
@@ -5343,10 +5343,10 @@
         <v>1.34</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7736</v>
+        <v>0.7621</v>
       </c>
       <c r="J76" t="n">
-        <v>13.1512</v>
+        <v>12.9557</v>
       </c>
     </row>
     <row r="77">
@@ -5383,10 +5383,10 @@
         <v>0.64</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.3412</v>
+        <v>-0.3328</v>
       </c>
       <c r="J77" t="n">
-        <v>-5.8004</v>
+        <v>-5.6576</v>
       </c>
     </row>
     <row r="78">
@@ -5423,10 +5423,10 @@
         <v>0.62</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.3608</v>
+        <v>-0.3539</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.1336</v>
+        <v>-6.0163</v>
       </c>
     </row>
     <row r="79">
@@ -5463,10 +5463,10 @@
         <v>0.53</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4431</v>
+        <v>-0.4406</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.5327</v>
+        <v>-7.4902</v>
       </c>
     </row>
     <row r="80">
@@ -5503,10 +5503,10 @@
         <v>0.43</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5281</v>
+        <v>-0.53</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.9777</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="81">
@@ -5543,10 +5543,10 @@
         <v>0.36</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5908</v>
+        <v>-0.5999</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.0436</v>
+        <v>-10.1983</v>
       </c>
     </row>
     <row r="82">
@@ -5583,10 +5583,10 @@
         <v>1.18</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4225</v>
+        <v>0.3669</v>
       </c>
       <c r="J82" t="n">
-        <v>10.5625</v>
+        <v>9.172499999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5623,10 +5623,10 @@
         <v>1.09</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2515</v>
+        <v>0.205</v>
       </c>
       <c r="J83" t="n">
-        <v>6.2875</v>
+        <v>5.125</v>
       </c>
     </row>
     <row r="84">
@@ -5663,10 +5663,10 @@
         <v>1.05</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1644</v>
+        <v>0.1274</v>
       </c>
       <c r="J84" t="n">
-        <v>4.11</v>
+        <v>3.185</v>
       </c>
     </row>
     <row r="85">
@@ -5703,10 +5703,10 @@
         <v>0.75</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2926</v>
+        <v>-0.2742</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.315</v>
+        <v>-6.855</v>
       </c>
     </row>
     <row r="86">
@@ -5743,10 +5743,10 @@
         <v>0.49</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5246</v>
+        <v>-0.5285</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.115</v>
+        <v>-13.2125</v>
       </c>
     </row>
     <row r="87">
@@ -5783,10 +5783,10 @@
         <v>1.57</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2048</v>
+        <v>1.2204</v>
       </c>
       <c r="J87" t="n">
-        <v>30.12</v>
+        <v>30.51</v>
       </c>
     </row>
     <row r="88">
@@ -5823,10 +5823,10 @@
         <v>1.25</v>
       </c>
       <c r="I88" t="n">
-        <v>0.654</v>
+        <v>0.6214</v>
       </c>
       <c r="J88" t="n">
-        <v>16.35</v>
+        <v>15.535</v>
       </c>
     </row>
     <row r="89">
@@ -5863,10 +5863,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5474</v>
+        <v>0.5121</v>
       </c>
       <c r="J89" t="n">
-        <v>13.685</v>
+        <v>12.8025</v>
       </c>
     </row>
     <row r="90">
@@ -5903,10 +5903,10 @@
         <v>1.03</v>
       </c>
       <c r="I90" t="n">
-        <v>0.108</v>
+        <v>0.0873</v>
       </c>
       <c r="J90" t="n">
-        <v>2.7</v>
+        <v>2.1825</v>
       </c>
     </row>
     <row r="91">
@@ -5943,10 +5943,10 @@
         <v>0.84</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5276</v>
+        <v>-0.4886</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.19</v>
+        <v>-12.215</v>
       </c>
     </row>
     <row r="92">
@@ -5983,10 +5983,10 @@
         <v>1.27</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5833</v>
+        <v>0.5289</v>
       </c>
       <c r="J92" t="n">
-        <v>14.5825</v>
+        <v>13.2225</v>
       </c>
     </row>
     <row r="93">
@@ -6023,10 +6023,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3163</v>
+        <v>0.2656</v>
       </c>
       <c r="J93" t="n">
-        <v>7.9075</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="94">
@@ -6063,10 +6063,10 @@
         <v>0.86</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1816</v>
+        <v>-0.1625</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.54</v>
+        <v>-4.0625</v>
       </c>
     </row>
     <row r="95">
@@ -6103,10 +6103,10 @@
         <v>0.74</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3002</v>
+        <v>-0.2822</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.505</v>
+        <v>-7.055</v>
       </c>
     </row>
     <row r="96">
@@ -6143,10 +6143,10 @@
         <v>0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5316</v>
+        <v>-0.5363</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.29</v>
+        <v>-13.4075</v>
       </c>
     </row>
     <row r="97">
@@ -6183,10 +6183,10 @@
         <v>1.47</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0602</v>
+        <v>1.0672</v>
       </c>
       <c r="J97" t="n">
-        <v>26.505</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="98">
@@ -6223,10 +6223,10 @@
         <v>1.27</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6901</v>
+        <v>0.6604</v>
       </c>
       <c r="J98" t="n">
-        <v>17.2525</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="99">
@@ -6263,10 +6263,10 @@
         <v>1.24</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6282</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>15.705</v>
+        <v>14.9075</v>
       </c>
     </row>
     <row r="100">
@@ -6303,10 +6303,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3843</v>
+        <v>0.3504</v>
       </c>
       <c r="J100" t="n">
-        <v>9.6075</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="101">
@@ -6343,10 +6343,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2695</v>
+        <v>-0.2315</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.7375</v>
+        <v>-5.7875</v>
       </c>
     </row>
     <row r="102">
@@ -6383,10 +6383,10 @@
         <v>1.13</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3393</v>
+        <v>0.2878</v>
       </c>
       <c r="J102" t="n">
-        <v>8.4825</v>
+        <v>7.195</v>
       </c>
     </row>
     <row r="103">
@@ -6423,10 +6423,10 @@
         <v>1.08</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2386</v>
+        <v>0.194</v>
       </c>
       <c r="J103" t="n">
-        <v>5.965</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="104">
@@ -6463,10 +6463,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2313</v>
+        <v>-0.2118</v>
       </c>
       <c r="J104" t="n">
-        <v>-5.7825</v>
+        <v>-5.295</v>
       </c>
     </row>
     <row r="105">
@@ -6503,10 +6503,10 @@
         <v>0.75</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2895</v>
+        <v>-0.2712</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.2375</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="106">
@@ -6543,10 +6543,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.391</v>
+        <v>-0.3789</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.775</v>
+        <v>-9.4725</v>
       </c>
     </row>
     <row r="107">
@@ -6583,10 +6583,10 @@
         <v>1.31</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6854</v>
+        <v>0.672</v>
       </c>
       <c r="J107" t="n">
-        <v>17.135</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="108">
@@ -6623,10 +6623,10 @@
         <v>1.29</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6555</v>
+        <v>0.6432</v>
       </c>
       <c r="J108" t="n">
-        <v>16.3875</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="109">
@@ -6663,10 +6663,10 @@
         <v>1.17</v>
       </c>
       <c r="I109" t="n">
-        <v>0.4684</v>
+        <v>0.4446</v>
       </c>
       <c r="J109" t="n">
-        <v>11.71</v>
+        <v>11.115</v>
       </c>
     </row>
     <row r="110">
@@ -6703,10 +6703,10 @@
         <v>1.13</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3852</v>
+        <v>0.3511</v>
       </c>
       <c r="J110" t="n">
-        <v>9.630000000000001</v>
+        <v>8.7775</v>
       </c>
     </row>
     <row r="111">
@@ -6743,10 +6743,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3605</v>
+        <v>0.3268</v>
       </c>
       <c r="J111" t="n">
-        <v>9.012499999999999</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="112">
@@ -6783,10 +6783,10 @@
         <v>0.99</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.0137</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.3699</v>
+        <v>-0.2511</v>
       </c>
     </row>
     <row r="113">
@@ -6823,10 +6823,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0318</v>
+        <v>-0.0244</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.8586</v>
+        <v>-0.6588000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6863,10 +6863,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0639</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.0601</v>
+        <v>-1.7253</v>
       </c>
     </row>
     <row r="115">
@@ -6903,10 +6903,10 @@
         <v>0.9</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1375</v>
+        <v>-0.1209</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.7125</v>
+        <v>-3.2643</v>
       </c>
     </row>
     <row r="116">
@@ -6943,10 +6943,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4781</v>
+        <v>-0.4753</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.9087</v>
+        <v>-12.8331</v>
       </c>
     </row>
     <row r="117">
@@ -6983,10 +6983,10 @@
         <v>1.83</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3752</v>
+        <v>1.3858</v>
       </c>
       <c r="J117" t="n">
-        <v>37.1304</v>
+        <v>37.4166</v>
       </c>
     </row>
     <row r="118">
@@ -7023,10 +7023,10 @@
         <v>1.27</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6203</v>
+        <v>0.6113</v>
       </c>
       <c r="J118" t="n">
-        <v>16.7481</v>
+        <v>16.5051</v>
       </c>
     </row>
     <row r="119">
@@ -7063,10 +7063,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5131</v>
+        <v>0.5048</v>
       </c>
       <c r="J119" t="n">
-        <v>13.8537</v>
+        <v>13.6296</v>
       </c>
     </row>
     <row r="120">
@@ -7103,10 +7103,10 @@
         <v>1.08</v>
       </c>
       <c r="I120" t="n">
-        <v>0.248</v>
+        <v>0.2177</v>
       </c>
       <c r="J120" t="n">
-        <v>6.696</v>
+        <v>5.8779</v>
       </c>
     </row>
     <row r="121">
@@ -7143,10 +7143,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4411</v>
+        <v>-0.4017</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.9097</v>
+        <v>-10.8459</v>
       </c>
     </row>
     <row r="122">
@@ -7183,10 +7183,10 @@
         <v>1.46</v>
       </c>
       <c r="I122" t="n">
-        <v>0.9566</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>28.698</v>
+        <v>28.443</v>
       </c>
     </row>
     <row r="123">
@@ -7223,10 +7223,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.583</v>
+        <v>0.5707</v>
       </c>
       <c r="J123" t="n">
-        <v>17.49</v>
+        <v>17.121</v>
       </c>
     </row>
     <row r="124">
@@ -7263,10 +7263,10 @@
         <v>0.97</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1351</v>
+        <v>-0.1074</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.053</v>
+        <v>-3.222</v>
       </c>
     </row>
     <row r="125">
@@ -7303,10 +7303,10 @@
         <v>0.72</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7373</v>
       </c>
       <c r="J125" t="n">
-        <v>-22.968</v>
+        <v>-22.119</v>
       </c>
     </row>
     <row r="126">
@@ -7343,10 +7343,10 @@
         <v>0.62</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9762</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-29.286</v>
+        <v>-29.079</v>
       </c>
     </row>
     <row r="127">
@@ -7383,10 +7383,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6897</v>
+        <v>0.6556</v>
       </c>
       <c r="J127" t="n">
-        <v>20.691</v>
+        <v>19.668</v>
       </c>
     </row>
     <row r="128">
@@ -7423,10 +7423,10 @@
         <v>1.18</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3793</v>
+        <v>0.3258</v>
       </c>
       <c r="J128" t="n">
-        <v>11.379</v>
+        <v>9.773999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -7463,10 +7463,10 @@
         <v>0.99</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0332</v>
+        <v>-0.0241</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.996</v>
+        <v>-0.723</v>
       </c>
     </row>
     <row r="130">
@@ -7503,10 +7503,10 @@
         <v>0.97</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0667</v>
+        <v>-0.0525</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.001</v>
+        <v>-1.575</v>
       </c>
     </row>
     <row r="131">
@@ -7543,10 +7543,10 @@
         <v>0.97</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0667</v>
+        <v>-0.0525</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.001</v>
+        <v>-1.575</v>
       </c>
     </row>
     <row r="132">
@@ -7583,10 +7583,10 @@
         <v>1.37</v>
       </c>
       <c r="I132" t="n">
-        <v>0.767</v>
+        <v>0.7527</v>
       </c>
       <c r="J132" t="n">
-        <v>19.175</v>
+        <v>18.8175</v>
       </c>
     </row>
     <row r="133">
@@ -7623,10 +7623,10 @@
         <v>1.37</v>
       </c>
       <c r="I133" t="n">
-        <v>0.767</v>
+        <v>0.7527</v>
       </c>
       <c r="J133" t="n">
-        <v>19.175</v>
+        <v>18.8175</v>
       </c>
     </row>
     <row r="134">
@@ -7663,10 +7663,10 @@
         <v>1.29</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6399</v>
       </c>
       <c r="J134" t="n">
-        <v>16.2675</v>
+        <v>15.9975</v>
       </c>
     </row>
     <row r="135">
@@ -7703,10 +7703,10 @@
         <v>1.17</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4642</v>
+        <v>0.4407</v>
       </c>
       <c r="J135" t="n">
-        <v>11.605</v>
+        <v>11.0175</v>
       </c>
     </row>
     <row r="136">
@@ -7743,10 +7743,10 @@
         <v>1.02</v>
       </c>
       <c r="I136" t="n">
-        <v>0.0601</v>
+        <v>0.0438</v>
       </c>
       <c r="J136" t="n">
-        <v>1.5025</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="137">
@@ -7783,10 +7783,10 @@
         <v>1.06</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1863</v>
+        <v>0.1465</v>
       </c>
       <c r="J137" t="n">
-        <v>4.6575</v>
+        <v>3.6625</v>
       </c>
     </row>
     <row r="138">
@@ -7823,10 +7823,10 @@
         <v>1.01</v>
       </c>
       <c r="I138" t="n">
-        <v>0.0561</v>
+        <v>0.0382</v>
       </c>
       <c r="J138" t="n">
-        <v>1.4025</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="139">
@@ -7863,10 +7863,10 @@
         <v>0.88</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1621</v>
+        <v>-0.1431</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.0525</v>
+        <v>-3.5775</v>
       </c>
     </row>
     <row r="140">
@@ -7903,10 +7903,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1939</v>
+        <v>-0.174</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.8475</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="141">
@@ -7943,10 +7943,10 @@
         <v>0.78</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.6025</v>
+        <v>-6.1175</v>
       </c>
     </row>
     <row r="142">
@@ -7983,10 +7983,10 @@
         <v>1.04</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1507</v>
+        <v>0.1165</v>
       </c>
       <c r="J142" t="n">
-        <v>4.0689</v>
+        <v>3.1455</v>
       </c>
     </row>
     <row r="143">
@@ -8023,10 +8023,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0975</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>2.6325</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="144">
@@ -8063,10 +8063,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2002</v>
+        <v>-0.1812</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.4054</v>
+        <v>-4.8924</v>
       </c>
     </row>
     <row r="145">
@@ -8103,10 +8103,10 @@
         <v>0.74</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2978</v>
+        <v>-0.2798</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.0406</v>
+        <v>-7.5546</v>
       </c>
     </row>
     <row r="146">
@@ -8143,10 +8143,10 @@
         <v>0.71</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3259</v>
+        <v>-0.3092</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.799300000000001</v>
+        <v>-8.3484</v>
       </c>
     </row>
     <row r="147">
@@ -8183,10 +8183,10 @@
         <v>1.43</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9936</v>
+        <v>0.9901</v>
       </c>
       <c r="J147" t="n">
-        <v>26.8272</v>
+        <v>26.7327</v>
       </c>
     </row>
     <row r="148">
@@ -8223,10 +8223,10 @@
         <v>1.35</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8458</v>
+        <v>0.8257</v>
       </c>
       <c r="J148" t="n">
-        <v>22.8366</v>
+        <v>22.2939</v>
       </c>
     </row>
     <row r="149">
@@ -8263,10 +8263,10 @@
         <v>1.22</v>
       </c>
       <c r="I149" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J149" t="n">
-        <v>15.7815</v>
+        <v>14.9256</v>
       </c>
     </row>
     <row r="150">
@@ -8303,10 +8303,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3805</v>
+        <v>0.3473</v>
       </c>
       <c r="J150" t="n">
-        <v>10.2735</v>
+        <v>9.3771</v>
       </c>
     </row>
     <row r="151">
@@ -8343,10 +8343,10 @@
         <v>1.04</v>
       </c>
       <c r="I151" t="n">
-        <v>0.132</v>
+        <v>0.1084</v>
       </c>
       <c r="J151" t="n">
-        <v>3.564</v>
+        <v>2.9268</v>
       </c>
     </row>
     <row r="152">
@@ -8383,10 +8383,10 @@
         <v>1.67</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7718</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
-        <v>17.7514</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="153">
@@ -8423,10 +8423,10 @@
         <v>1.33</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4354</v>
+        <v>0.3741</v>
       </c>
       <c r="J153" t="n">
-        <v>10.0142</v>
+        <v>8.6043</v>
       </c>
     </row>
     <row r="154">
@@ -8463,10 +8463,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4146</v>
+        <v>0.3548</v>
       </c>
       <c r="J154" t="n">
-        <v>9.5358</v>
+        <v>8.160399999999999</v>
       </c>
     </row>
     <row r="155">
@@ -8503,10 +8503,10 @@
         <v>1.21</v>
       </c>
       <c r="I155" t="n">
-        <v>0.3017</v>
+        <v>0.2516</v>
       </c>
       <c r="J155" t="n">
-        <v>6.9391</v>
+        <v>5.7868</v>
       </c>
     </row>
     <row r="156">
@@ -8543,10 +8543,10 @@
         <v>1.13</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2004</v>
+        <v>0.1608</v>
       </c>
       <c r="J156" t="n">
-        <v>4.6092</v>
+        <v>3.6984</v>
       </c>
     </row>
     <row r="157">
@@ -8583,10 +8583,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2714</v>
+        <v>0.2632</v>
       </c>
       <c r="J157" t="n">
-        <v>6.2422</v>
+        <v>6.0536</v>
       </c>
     </row>
     <row r="158">
@@ -8623,10 +8623,10 @@
         <v>0.89</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1417</v>
+        <v>-0.1261</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.2591</v>
+        <v>-2.9003</v>
       </c>
     </row>
     <row r="159">
@@ -8663,10 +8663,10 @@
         <v>0.76</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.2724</v>
+        <v>-0.2547</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.2652</v>
+        <v>-5.8581</v>
       </c>
     </row>
     <row r="160">
@@ -8703,10 +8703,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2818</v>
+        <v>-0.2642</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.4814</v>
+        <v>-6.0766</v>
       </c>
     </row>
     <row r="161">
@@ -8743,10 +8743,10 @@
         <v>0.51</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4975</v>
+        <v>-0.4964</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.4425</v>
+        <v>-11.4172</v>
       </c>
     </row>
     <row r="162">
@@ -8783,10 +8783,10 @@
         <v>1.36</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6812</v>
+        <v>0.6233</v>
       </c>
       <c r="J162" t="n">
-        <v>20.436</v>
+        <v>18.699</v>
       </c>
     </row>
     <row r="163">
@@ -8823,10 +8823,10 @@
         <v>1.04</v>
       </c>
       <c r="I163" t="n">
-        <v>0.121</v>
+        <v>0.0922</v>
       </c>
       <c r="J163" t="n">
-        <v>3.63</v>
+        <v>2.766</v>
       </c>
     </row>
     <row r="164">
@@ -8863,10 +8863,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0407</v>
+        <v>0.0282</v>
       </c>
       <c r="J164" t="n">
-        <v>1.221</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="165">
@@ -8903,10 +8903,10 @@
         <v>0.92</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1263</v>
+        <v>-0.1074</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.789</v>
+        <v>-3.222</v>
       </c>
     </row>
     <row r="166">
@@ -8943,10 +8943,10 @@
         <v>0.83</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2251</v>
+        <v>-0.2046</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.753</v>
+        <v>-6.138</v>
       </c>
     </row>
     <row r="167">
@@ -8983,10 +8983,10 @@
         <v>1.4</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9861</v>
+        <v>0.9815</v>
       </c>
       <c r="J167" t="n">
-        <v>29.583</v>
+        <v>29.445</v>
       </c>
     </row>
     <row r="168">
@@ -9023,10 +9023,10 @@
         <v>1.09</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3024</v>
+        <v>0.2644</v>
       </c>
       <c r="J168" t="n">
-        <v>9.071999999999999</v>
+        <v>7.932</v>
       </c>
     </row>
     <row r="169">
@@ -9063,10 +9063,10 @@
         <v>1.03</v>
       </c>
       <c r="I169" t="n">
-        <v>0.127</v>
+        <v>0.1031</v>
       </c>
       <c r="J169" t="n">
-        <v>3.81</v>
+        <v>3.093</v>
       </c>
     </row>
     <row r="170">
@@ -9103,10 +9103,10 @@
         <v>0.96</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1807</v>
+        <v>-0.1468</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.421</v>
+        <v>-4.404</v>
       </c>
     </row>
     <row r="171">
@@ -9143,10 +9143,10 @@
         <v>0.85</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4824</v>
+        <v>-0.4401</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.472</v>
+        <v>-13.203</v>
       </c>
     </row>
     <row r="172">
@@ -9183,10 +9183,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0976</v>
+        <v>1.1087</v>
       </c>
       <c r="J172" t="n">
-        <v>31.8304</v>
+        <v>32.1523</v>
       </c>
     </row>
     <row r="173">
@@ -9223,10 +9223,10 @@
         <v>1.15</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4378</v>
+        <v>0.4016</v>
       </c>
       <c r="J173" t="n">
-        <v>12.6962</v>
+        <v>11.6464</v>
       </c>
     </row>
     <row r="174">
@@ -9263,10 +9263,10 @@
         <v>1.09</v>
       </c>
       <c r="I174" t="n">
-        <v>0.289</v>
+        <v>0.2562</v>
       </c>
       <c r="J174" t="n">
-        <v>8.381</v>
+        <v>7.4298</v>
       </c>
     </row>
     <row r="175">
@@ -9303,10 +9303,10 @@
         <v>1.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2051</v>
+        <v>0.1764</v>
       </c>
       <c r="J175" t="n">
-        <v>5.9479</v>
+        <v>5.1156</v>
       </c>
     </row>
     <row r="176">
@@ -9343,10 +9343,10 @@
         <v>1.05</v>
       </c>
       <c r="I176" t="n">
-        <v>0.175</v>
+        <v>0.1483</v>
       </c>
       <c r="J176" t="n">
-        <v>5.075</v>
+        <v>4.3007</v>
       </c>
     </row>
     <row r="177">
@@ -9383,10 +9383,10 @@
         <v>1.38</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7297</v>
+        <v>0.6758</v>
       </c>
       <c r="J177" t="n">
-        <v>21.1613</v>
+        <v>19.5982</v>
       </c>
     </row>
     <row r="178">
@@ -9423,10 +9423,10 @@
         <v>1.08</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2171</v>
+        <v>0.1738</v>
       </c>
       <c r="J178" t="n">
-        <v>6.2959</v>
+        <v>5.0402</v>
       </c>
     </row>
     <row r="179">
@@ -9463,10 +9463,10 @@
         <v>0.85</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1991</v>
+        <v>-0.1786</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.7739</v>
+        <v>-5.1794</v>
       </c>
     </row>
     <row r="180">
@@ -9503,10 +9503,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2198</v>
+        <v>-0.1993</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.3742</v>
+        <v>-5.7797</v>
       </c>
     </row>
     <row r="181">
@@ -9543,10 +9543,10 @@
         <v>0.73</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3175</v>
+        <v>-0.3004</v>
       </c>
       <c r="J181" t="n">
-        <v>-9.2075</v>
+        <v>-8.711600000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9583,10 +9583,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.133</v>
+        <v>1.1456</v>
       </c>
       <c r="J182" t="n">
-        <v>33.99</v>
+        <v>34.368</v>
       </c>
     </row>
     <row r="183">
@@ -9623,10 +9623,10 @@
         <v>1.47</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0636</v>
+        <v>1.071</v>
       </c>
       <c r="J183" t="n">
-        <v>31.908</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="184">
@@ -9663,10 +9663,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3867</v>
+        <v>0.3523</v>
       </c>
       <c r="J184" t="n">
-        <v>11.601</v>
+        <v>10.569</v>
       </c>
     </row>
     <row r="185">
@@ -9703,10 +9703,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2961</v>
+        <v>-0.2565</v>
       </c>
       <c r="J185" t="n">
-        <v>-8.882999999999999</v>
+        <v>-7.695</v>
       </c>
     </row>
     <row r="186">
@@ -9743,10 +9743,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3245</v>
+        <v>-0.2841</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.734999999999999</v>
+        <v>-8.523</v>
       </c>
     </row>
     <row r="187">
@@ -9783,10 +9783,10 @@
         <v>1.12</v>
       </c>
       <c r="I187" t="n">
-        <v>0.3021</v>
+        <v>0.2513</v>
       </c>
       <c r="J187" t="n">
-        <v>9.063000000000001</v>
+        <v>7.539</v>
       </c>
     </row>
     <row r="188">
@@ -9823,10 +9823,10 @@
         <v>1.08</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2223</v>
+        <v>0.1784</v>
       </c>
       <c r="J188" t="n">
-        <v>6.669</v>
+        <v>5.352</v>
       </c>
     </row>
     <row r="189">
@@ -9863,10 +9863,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1195</v>
+        <v>-0.1021</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.585</v>
+        <v>-3.063</v>
       </c>
     </row>
     <row r="190">
@@ -9903,10 +9903,10 @@
         <v>0.88</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1648</v>
+        <v>-0.1451</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.944</v>
+        <v>-4.353</v>
       </c>
     </row>
     <row r="191">
@@ -9943,10 +9943,10 @@
         <v>0.74</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3056</v>
+        <v>-0.2878</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.167999999999999</v>
+        <v>-8.634</v>
       </c>
     </row>
     <row r="192">
@@ -9983,10 +9983,10 @@
         <v>0.84</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.1812</v>
+        <v>-0.1657</v>
       </c>
       <c r="J192" t="n">
-        <v>-3.624</v>
+        <v>-3.314</v>
       </c>
     </row>
     <row r="193">
@@ -10023,10 +10023,10 @@
         <v>0.73</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.2914</v>
+        <v>-0.2773</v>
       </c>
       <c r="J193" t="n">
-        <v>-5.828</v>
+        <v>-5.546</v>
       </c>
     </row>
     <row r="194">
@@ -10063,10 +10063,10 @@
         <v>0.7</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.3179</v>
+        <v>-0.3039</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.358</v>
+        <v>-6.078</v>
       </c>
     </row>
     <row r="195">
@@ -10103,10 +10103,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3266</v>
+        <v>-0.3128</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.532</v>
+        <v>-6.256</v>
       </c>
     </row>
     <row r="196">
@@ -10143,10 +10143,10 @@
         <v>0.57</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4332</v>
+        <v>-0.4246</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.664</v>
+        <v>-8.492000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -10183,10 +10183,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0374</v>
+        <v>1.0283</v>
       </c>
       <c r="J197" t="n">
-        <v>20.748</v>
+        <v>20.566</v>
       </c>
     </row>
     <row r="198">
@@ -10223,10 +10223,10 @@
         <v>1.57</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0118</v>
+        <v>1.0023</v>
       </c>
       <c r="J198" t="n">
-        <v>20.236</v>
+        <v>20.046</v>
       </c>
     </row>
     <row r="199">
@@ -10263,10 +10263,10 @@
         <v>1.46</v>
       </c>
       <c r="I199" t="n">
-        <v>0.8694</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>17.388</v>
+        <v>17.188</v>
       </c>
     </row>
     <row r="200">
@@ -10303,10 +10303,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.8041</v>
+        <v>0.795</v>
       </c>
       <c r="J200" t="n">
-        <v>16.082</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="201">
@@ -10343,10 +10343,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2481</v>
+        <v>0.216</v>
       </c>
       <c r="J201" t="n">
-        <v>4.962</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="202">
@@ -10383,10 +10383,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4734</v>
+        <v>0.427</v>
       </c>
       <c r="J202" t="n">
-        <v>12.7818</v>
+        <v>11.529</v>
       </c>
     </row>
     <row r="203">
@@ -10423,10 +10423,10 @@
         <v>1.17</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3831</v>
+        <v>0.3275</v>
       </c>
       <c r="J203" t="n">
-        <v>10.3437</v>
+        <v>8.842499999999999</v>
       </c>
     </row>
     <row r="204">
@@ -10463,10 +10463,10 @@
         <v>0.96</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.0721</v>
+        <v>-0.0579</v>
       </c>
       <c r="J204" t="n">
-        <v>-1.9467</v>
+        <v>-1.5633</v>
       </c>
     </row>
     <row r="205">
@@ -10503,10 +10503,10 @@
         <v>0.92</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1231</v>
+        <v>-0.1047</v>
       </c>
       <c r="J205" t="n">
-        <v>-3.3237</v>
+        <v>-2.8269</v>
       </c>
     </row>
     <row r="206">
@@ -10543,10 +10543,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3563</v>
+        <v>-0.3421</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.620100000000001</v>
+        <v>-9.236700000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10583,10 +10583,10 @@
         <v>1.44</v>
       </c>
       <c r="I207" t="n">
-        <v>0.8793</v>
+        <v>0.8639</v>
       </c>
       <c r="J207" t="n">
-        <v>23.7411</v>
+        <v>23.3253</v>
       </c>
     </row>
     <row r="208">
@@ -10623,10 +10623,10 @@
         <v>1.22</v>
       </c>
       <c r="I208" t="n">
-        <v>0.5516</v>
+        <v>0.5432</v>
       </c>
       <c r="J208" t="n">
-        <v>14.8932</v>
+        <v>14.6664</v>
       </c>
     </row>
     <row r="209">
@@ -10663,10 +10663,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5356</v>
+        <v>0.5269</v>
       </c>
       <c r="J209" t="n">
-        <v>14.4612</v>
+        <v>14.2263</v>
       </c>
     </row>
     <row r="210">
@@ -10703,10 +10703,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5196</v>
+        <v>0.509</v>
       </c>
       <c r="J210" t="n">
-        <v>14.0292</v>
+        <v>13.743</v>
       </c>
     </row>
     <row r="211">
@@ -10743,10 +10743,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6434</v>
+        <v>-0.61</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.3718</v>
+        <v>-16.47</v>
       </c>
     </row>
     <row r="212">
@@ -10783,10 +10783,10 @@
         <v>1.21</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5458</v>
+        <v>0.5352</v>
       </c>
       <c r="J212" t="n">
-        <v>15.8282</v>
+        <v>15.5208</v>
       </c>
     </row>
     <row r="213">
@@ -10823,10 +10823,10 @@
         <v>1.19</v>
       </c>
       <c r="I213" t="n">
-        <v>0.5127</v>
+        <v>0.4977</v>
       </c>
       <c r="J213" t="n">
-        <v>14.8683</v>
+        <v>14.4333</v>
       </c>
     </row>
     <row r="214">
@@ -10863,10 +10863,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4215</v>
+        <v>0.3829</v>
       </c>
       <c r="J214" t="n">
-        <v>12.2235</v>
+        <v>11.1041</v>
       </c>
     </row>
     <row r="215">
@@ -10903,10 +10903,10 @@
         <v>1.06</v>
       </c>
       <c r="I215" t="n">
-        <v>0.2165</v>
+        <v>0.1853</v>
       </c>
       <c r="J215" t="n">
-        <v>6.2785</v>
+        <v>5.3737</v>
       </c>
     </row>
     <row r="216">
@@ -10943,10 +10943,10 @@
         <v>0.89</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3877</v>
+        <v>-0.3449</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.2433</v>
+        <v>-10.0021</v>
       </c>
     </row>
     <row r="217">
@@ -10983,10 +10983,10 @@
         <v>1.54</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8218</v>
+        <v>0.7877</v>
       </c>
       <c r="J217" t="n">
-        <v>23.8322</v>
+        <v>22.8433</v>
       </c>
     </row>
     <row r="218">
@@ -11023,10 +11023,10 @@
         <v>0.91</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1353</v>
+        <v>-0.1161</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.9237</v>
+        <v>-3.3669</v>
       </c>
     </row>
     <row r="219">
@@ -11063,10 +11063,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1691</v>
+        <v>-0.1488</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.9039</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="220">
@@ -11103,10 +11103,10 @@
         <v>0.86</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1907</v>
+        <v>-0.1701</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.5303</v>
+        <v>-4.9329</v>
       </c>
     </row>
     <row r="221">
@@ -11143,10 +11143,10 @@
         <v>0.8</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2522</v>
+        <v>-0.2323</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.3138</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="222">
@@ -11183,10 +11183,10 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9586</v>
+        <v>0.9453</v>
       </c>
       <c r="J222" t="n">
-        <v>40.2612</v>
+        <v>39.7026</v>
       </c>
     </row>
     <row r="223">
@@ -11223,10 +11223,10 @@
         <v>1.34</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7421</v>
+        <v>0.7262</v>
       </c>
       <c r="J223" t="n">
-        <v>31.1682</v>
+        <v>30.5004</v>
       </c>
     </row>
     <row r="224">
@@ -11263,10 +11263,10 @@
         <v>1.12</v>
       </c>
       <c r="I224" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J224" t="n">
-        <v>15.561</v>
+        <v>14.0154</v>
       </c>
     </row>
     <row r="225">
@@ -11303,10 +11303,10 @@
         <v>0.95</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2253</v>
+        <v>-0.1883</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.4626</v>
+        <v>-7.9086</v>
       </c>
     </row>
     <row r="226">
@@ -11343,10 +11343,10 @@
         <v>0.77</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6819</v>
+        <v>-0.65</v>
       </c>
       <c r="J226" t="n">
-        <v>-28.6398</v>
+        <v>-27.3</v>
       </c>
     </row>
     <row r="227">
@@ -11383,10 +11383,10 @@
         <v>1.17</v>
       </c>
       <c r="I227" t="n">
-        <v>0.3938</v>
+        <v>0.3382</v>
       </c>
       <c r="J227" t="n">
-        <v>16.5396</v>
+        <v>14.2044</v>
       </c>
     </row>
     <row r="228">
@@ -11423,10 +11423,10 @@
         <v>0.96</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0697</v>
+        <v>-0.0567</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.9274</v>
+        <v>-2.3814</v>
       </c>
     </row>
     <row r="229">
@@ -11463,10 +11463,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1313</v>
+        <v>-0.1131</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.5146</v>
+        <v>-4.7502</v>
       </c>
     </row>
     <row r="230">
@@ -11503,10 +11503,10 @@
         <v>0.86</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1864</v>
+        <v>-0.1662</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.8288</v>
+        <v>-6.9804</v>
       </c>
     </row>
     <row r="231">
@@ -11543,10 +11543,10 @@
         <v>0.85</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1969</v>
+        <v>-0.1766</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.2698</v>
+        <v>-7.4172</v>
       </c>
     </row>
     <row r="232">
@@ -11583,10 +11583,10 @@
         <v>1.91</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4036</v>
+        <v>1.4139</v>
       </c>
       <c r="J232" t="n">
-        <v>28.072</v>
+        <v>28.278</v>
       </c>
     </row>
     <row r="233">
@@ -11623,10 +11623,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>1.0829</v>
+        <v>1.0792</v>
       </c>
       <c r="J233" t="n">
-        <v>21.658</v>
+        <v>21.584</v>
       </c>
     </row>
     <row r="234">
@@ -11663,10 +11663,10 @@
         <v>1.55</v>
       </c>
       <c r="I234" t="n">
-        <v>0.9738</v>
+        <v>0.9686</v>
       </c>
       <c r="J234" t="n">
-        <v>19.476</v>
+        <v>19.372</v>
       </c>
     </row>
     <row r="235">
@@ -11703,10 +11703,10 @@
         <v>1.39</v>
       </c>
       <c r="I235" t="n">
-        <v>0.7635</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>15.27</v>
+        <v>15.172</v>
       </c>
     </row>
     <row r="236">
@@ -11743,10 +11743,10 @@
         <v>1.38</v>
       </c>
       <c r="I236" t="n">
-        <v>0.7496</v>
+        <v>0.7448</v>
       </c>
       <c r="J236" t="n">
-        <v>14.992</v>
+        <v>14.896</v>
       </c>
     </row>
     <row r="237">
@@ -11783,10 +11783,10 @@
         <v>0.78</v>
       </c>
       <c r="I237" t="n">
-        <v>-0.2</v>
+        <v>-0.1789</v>
       </c>
       <c r="J237" t="n">
-        <v>-4</v>
+        <v>-3.578</v>
       </c>
     </row>
     <row r="238">
@@ -11823,10 +11823,10 @@
         <v>0.73</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.2545</v>
+        <v>-0.2388</v>
       </c>
       <c r="J238" t="n">
-        <v>-5.09</v>
+        <v>-4.776</v>
       </c>
     </row>
     <row r="239">
@@ -11863,10 +11863,10 @@
         <v>0.58</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.4023</v>
+        <v>-0.3976</v>
       </c>
       <c r="J239" t="n">
-        <v>-8.045999999999999</v>
+        <v>-7.952</v>
       </c>
     </row>
     <row r="240">
@@ -11903,10 +11903,10 @@
         <v>0.33</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6207</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-12.414</v>
+        <v>-12.692</v>
       </c>
     </row>
     <row r="241">
@@ -11943,10 +11943,10 @@
         <v>0.25</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6929</v>
+        <v>-0.7204</v>
       </c>
       <c r="J241" t="n">
-        <v>-13.858</v>
+        <v>-14.408</v>
       </c>
     </row>
     <row r="242">
@@ -11983,10 +11983,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1078</v>
+        <v>1.1014</v>
       </c>
       <c r="J242" t="n">
-        <v>28.8028</v>
+        <v>28.6364</v>
       </c>
     </row>
     <row r="243">
@@ -12023,10 +12023,10 @@
         <v>1.24</v>
       </c>
       <c r="I243" t="n">
-        <v>0.5873</v>
+        <v>0.5763</v>
       </c>
       <c r="J243" t="n">
-        <v>15.2698</v>
+        <v>14.9838</v>
       </c>
     </row>
     <row r="244">
@@ -12063,10 +12063,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4901</v>
+        <v>0.4705</v>
       </c>
       <c r="J244" t="n">
-        <v>12.7426</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="245">
@@ -12103,10 +12103,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.2383</v>
+        <v>0.2071</v>
       </c>
       <c r="J245" t="n">
-        <v>6.1958</v>
+        <v>5.3846</v>
       </c>
     </row>
     <row r="246">
@@ -12143,10 +12143,10 @@
         <v>0.62</v>
       </c>
       <c r="I246" t="n">
-        <v>-1.0013</v>
+        <v>-1.0017</v>
       </c>
       <c r="J246" t="n">
-        <v>-26.0338</v>
+        <v>-26.0442</v>
       </c>
     </row>
     <row r="247">
@@ -12183,10 +12183,10 @@
         <v>1.36</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6214</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J247" t="n">
-        <v>16.1564</v>
+        <v>15.3972</v>
       </c>
     </row>
     <row r="248">
@@ -12223,10 +12223,10 @@
         <v>1.07</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1892</v>
+        <v>0.1499</v>
       </c>
       <c r="J248" t="n">
-        <v>4.9192</v>
+        <v>3.8974</v>
       </c>
     </row>
     <row r="249">
@@ -12263,10 +12263,10 @@
         <v>1.05</v>
       </c>
       <c r="I249" t="n">
-        <v>0.1457</v>
+        <v>0.1124</v>
       </c>
       <c r="J249" t="n">
-        <v>3.7882</v>
+        <v>2.9224</v>
       </c>
     </row>
     <row r="250">
@@ -12303,10 +12303,10 @@
         <v>0.9</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1483</v>
+        <v>-0.1285</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.8558</v>
+        <v>-3.341</v>
       </c>
     </row>
     <row r="251">
@@ -12343,10 +12343,10 @@
         <v>0.7</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3491</v>
+        <v>-0.3345</v>
       </c>
       <c r="J251" t="n">
-        <v>-9.076599999999999</v>
+        <v>-8.696999999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12383,10 +12383,10 @@
         <v>1.85</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7917</v>
+        <v>0.7402</v>
       </c>
       <c r="J252" t="n">
-        <v>15.0423</v>
+        <v>14.0638</v>
       </c>
     </row>
     <row r="253">
@@ -12423,10 +12423,10 @@
         <v>1.67</v>
       </c>
       <c r="I253" t="n">
-        <v>0.6718</v>
+        <v>0.6294</v>
       </c>
       <c r="J253" t="n">
-        <v>12.7642</v>
+        <v>11.9586</v>
       </c>
     </row>
     <row r="254">
@@ -12463,10 +12463,10 @@
         <v>1.62</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6378</v>
+        <v>0.5986</v>
       </c>
       <c r="J254" t="n">
-        <v>12.1182</v>
+        <v>11.3734</v>
       </c>
     </row>
     <row r="255">
@@ -12503,10 +12503,10 @@
         <v>1.25</v>
       </c>
       <c r="I255" t="n">
-        <v>0.337</v>
+        <v>0.2851</v>
       </c>
       <c r="J255" t="n">
-        <v>6.403</v>
+        <v>5.4169</v>
       </c>
     </row>
     <row r="256">
@@ -12543,10 +12543,10 @@
         <v>0.99</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.0587</v>
+        <v>-0.0515</v>
       </c>
       <c r="J256" t="n">
-        <v>-1.1153</v>
+        <v>-0.9785</v>
       </c>
     </row>
     <row r="257">
@@ -12583,10 +12583,10 @@
         <v>0.82</v>
       </c>
       <c r="I257" t="n">
-        <v>-0.1771</v>
+        <v>-0.1585</v>
       </c>
       <c r="J257" t="n">
-        <v>-3.3649</v>
+        <v>-3.0115</v>
       </c>
     </row>
     <row r="258">
@@ -12623,10 +12623,10 @@
         <v>0.76</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.2421</v>
+        <v>-0.2275</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.5999</v>
+        <v>-4.3225</v>
       </c>
     </row>
     <row r="259">
@@ -12663,10 +12663,10 @@
         <v>0.6</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.3938</v>
+        <v>-0.3859</v>
       </c>
       <c r="J259" t="n">
-        <v>-7.4822</v>
+        <v>-7.3321</v>
       </c>
     </row>
     <row r="260">
@@ -12703,10 +12703,10 @@
         <v>0.43</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.5415</v>
+        <v>-0.5444</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.2885</v>
+        <v>-10.3436</v>
       </c>
     </row>
     <row r="261">
@@ -12743,10 +12743,10 @@
         <v>0.38</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5857</v>
+        <v>-0.5947</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.1283</v>
+        <v>-11.2993</v>
       </c>
     </row>
     <row r="262">
@@ -12783,10 +12783,10 @@
         <v>0.91</v>
       </c>
       <c r="I262" t="n">
-        <v>-0.1251</v>
+        <v>-0.1094</v>
       </c>
       <c r="J262" t="n">
-        <v>-3.0024</v>
+        <v>-2.6256</v>
       </c>
     </row>
     <row r="263">
@@ -12823,10 +12823,10 @@
         <v>0.89</v>
       </c>
       <c r="I263" t="n">
-        <v>-0.1478</v>
+        <v>-0.1309</v>
       </c>
       <c r="J263" t="n">
-        <v>-3.5472</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="264">
@@ -12863,10 +12863,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1693</v>
+        <v>-0.1514</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.0632</v>
+        <v>-3.6336</v>
       </c>
     </row>
     <row r="265">
@@ -12903,10 +12903,10 @@
         <v>0.87</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1693</v>
+        <v>-0.1514</v>
       </c>
       <c r="J265" t="n">
-        <v>-4.0632</v>
+        <v>-3.6336</v>
       </c>
     </row>
     <row r="266">
@@ -12943,10 +12943,10 @@
         <v>0.77</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2684</v>
+        <v>-0.2496</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.4416</v>
+        <v>-5.9904</v>
       </c>
     </row>
     <row r="267">
@@ -12983,10 +12983,10 @@
         <v>1.64</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1277</v>
+        <v>1.1203</v>
       </c>
       <c r="J267" t="n">
-        <v>27.0648</v>
+        <v>26.8872</v>
       </c>
     </row>
     <row r="268">
@@ -13023,10 +13023,10 @@
         <v>1.46</v>
       </c>
       <c r="I268" t="n">
-        <v>0.8881</v>
+        <v>0.8738</v>
       </c>
       <c r="J268" t="n">
-        <v>21.3144</v>
+        <v>20.9712</v>
       </c>
     </row>
     <row r="269">
@@ -13063,10 +13063,10 @@
         <v>1.31</v>
       </c>
       <c r="I269" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6661</v>
       </c>
       <c r="J269" t="n">
-        <v>16.2456</v>
+        <v>15.9864</v>
       </c>
     </row>
     <row r="270">
@@ -13103,10 +13103,10 @@
         <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.0462</v>
+        <v>-0.0413</v>
       </c>
       <c r="J270" t="n">
-        <v>-1.1088</v>
+        <v>-0.9912</v>
       </c>
     </row>
     <row r="271">
@@ -13143,10 +13143,10 @@
         <v>0.96</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.218</v>
+        <v>-0.1848</v>
       </c>
       <c r="J271" t="n">
-        <v>-5.232</v>
+        <v>-4.4352</v>
       </c>
     </row>
     <row r="272">
@@ -13183,10 +13183,10 @@
         <v>1.29</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5399</v>
+        <v>0.512</v>
       </c>
       <c r="J272" t="n">
-        <v>16.197</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="273">
@@ -13223,10 +13223,10 @@
         <v>1.06</v>
       </c>
       <c r="I273" t="n">
-        <v>0.167</v>
+        <v>0.1309</v>
       </c>
       <c r="J273" t="n">
-        <v>5.01</v>
+        <v>3.927</v>
       </c>
     </row>
     <row r="274">
@@ -13263,10 +13263,10 @@
         <v>1.05</v>
       </c>
       <c r="I274" t="n">
-        <v>0.145</v>
+        <v>0.112</v>
       </c>
       <c r="J274" t="n">
-        <v>4.35</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="275">
@@ -13303,10 +13303,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1601</v>
+        <v>-0.14</v>
       </c>
       <c r="J275" t="n">
-        <v>-4.803</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="276">
@@ -13343,10 +13343,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.2344</v>
+        <v>-0.2141</v>
       </c>
       <c r="J276" t="n">
-        <v>-7.032</v>
+        <v>-6.423</v>
       </c>
     </row>
     <row r="277">
@@ -13383,10 +13383,10 @@
         <v>1.31</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7045</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="J277" t="n">
-        <v>21.135</v>
+        <v>20.67</v>
       </c>
     </row>
     <row r="278">
@@ -13423,10 +13423,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5462</v>
+        <v>0.5355</v>
       </c>
       <c r="J278" t="n">
-        <v>16.386</v>
+        <v>16.065</v>
       </c>
     </row>
     <row r="279">
@@ -13463,10 +13463,10 @@
         <v>1.06</v>
       </c>
       <c r="I279" t="n">
-        <v>0.2168</v>
+        <v>0.1854</v>
       </c>
       <c r="J279" t="n">
-        <v>6.504</v>
+        <v>5.562</v>
       </c>
     </row>
     <row r="280">
@@ -13503,10 +13503,10 @@
         <v>1.05</v>
       </c>
       <c r="I280" t="n">
-        <v>0.1869</v>
+        <v>0.158</v>
       </c>
       <c r="J280" t="n">
-        <v>5.607</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="281">
@@ -13543,10 +13543,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4882</v>
+        <v>-0.4464</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.646</v>
+        <v>-13.392</v>
       </c>
     </row>
     <row r="282">
@@ -13583,10 +13583,10 @@
         <v>1.72</v>
       </c>
       <c r="I282" t="n">
-        <v>1.201</v>
+        <v>1.1977</v>
       </c>
       <c r="J282" t="n">
-        <v>25.221</v>
+        <v>25.1517</v>
       </c>
     </row>
     <row r="283">
@@ -13623,10 +13623,10 @@
         <v>1.67</v>
       </c>
       <c r="I283" t="n">
-        <v>1.1388</v>
+        <v>1.1328</v>
       </c>
       <c r="J283" t="n">
-        <v>23.9148</v>
+        <v>23.7888</v>
       </c>
     </row>
     <row r="284">
@@ -13663,10 +13663,10 @@
         <v>1.47</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8828</v>
+        <v>0.8726</v>
       </c>
       <c r="J284" t="n">
-        <v>18.5388</v>
+        <v>18.3246</v>
       </c>
     </row>
     <row r="285">
@@ -13703,10 +13703,10 @@
         <v>1.15</v>
       </c>
       <c r="I285" t="n">
-        <v>0.3998</v>
+        <v>0.3682</v>
       </c>
       <c r="J285" t="n">
-        <v>8.395799999999999</v>
+        <v>7.7322</v>
       </c>
     </row>
     <row r="286">
@@ -13743,10 +13743,10 @@
         <v>1.09</v>
       </c>
       <c r="I286" t="n">
-        <v>0.2487</v>
+        <v>0.2167</v>
       </c>
       <c r="J286" t="n">
-        <v>5.2227</v>
+        <v>4.5507</v>
       </c>
     </row>
     <row r="287">
@@ -13783,10 +13783,10 @@
         <v>1.11</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3919</v>
+        <v>0.3631</v>
       </c>
       <c r="J287" t="n">
-        <v>8.229900000000001</v>
+        <v>7.6251</v>
       </c>
     </row>
     <row r="288">
@@ -13823,10 +13823,10 @@
         <v>0.73</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2877</v>
+        <v>-0.2745</v>
       </c>
       <c r="J288" t="n">
-        <v>-6.0417</v>
+        <v>-5.7645</v>
       </c>
     </row>
     <row r="289">
@@ -13863,10 +13863,10 @@
         <v>0.58</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4204</v>
+        <v>-0.4112</v>
       </c>
       <c r="J289" t="n">
-        <v>-8.8284</v>
+        <v>-8.635199999999999</v>
       </c>
     </row>
     <row r="290">
@@ -13903,10 +13903,10 @@
         <v>0.5</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4909</v>
+        <v>-0.488</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.3089</v>
+        <v>-10.248</v>
       </c>
     </row>
     <row r="291">
@@ -13943,10 +13943,10 @@
         <v>0.46</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.526</v>
+        <v>-0.5273</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.046</v>
+        <v>-11.0733</v>
       </c>
     </row>
     <row r="292">
@@ -13983,10 +13983,10 @@
         <v>2.23</v>
       </c>
       <c r="I292" t="n">
-        <v>1.777</v>
+        <v>1.8228</v>
       </c>
       <c r="J292" t="n">
-        <v>31.986</v>
+        <v>32.8104</v>
       </c>
     </row>
     <row r="293">
@@ -14023,10 +14023,10 @@
         <v>2.23</v>
       </c>
       <c r="I293" t="n">
-        <v>1.777</v>
+        <v>1.8228</v>
       </c>
       <c r="J293" t="n">
-        <v>31.986</v>
+        <v>32.8104</v>
       </c>
     </row>
     <row r="294">
@@ -14063,10 +14063,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3607</v>
+        <v>0.3271</v>
       </c>
       <c r="J294" t="n">
-        <v>6.4926</v>
+        <v>5.8878</v>
       </c>
     </row>
     <row r="295">
@@ -14103,10 +14103,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3363</v>
+        <v>0.3023</v>
       </c>
       <c r="J295" t="n">
-        <v>6.0534</v>
+        <v>5.4414</v>
       </c>
     </row>
     <row r="296">
@@ -14143,10 +14143,10 @@
         <v>0.9</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4283</v>
+        <v>-0.3975</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.7094</v>
+        <v>-7.155</v>
       </c>
     </row>
     <row r="297">
@@ -14183,10 +14183,10 @@
         <v>0.65</v>
       </c>
       <c r="I297" t="n">
-        <v>-0.3539</v>
+        <v>-0.3439</v>
       </c>
       <c r="J297" t="n">
-        <v>-6.3702</v>
+        <v>-6.1902</v>
       </c>
     </row>
     <row r="298">
@@ -14223,10 +14223,10 @@
         <v>0.65</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.3539</v>
+        <v>-0.3439</v>
       </c>
       <c r="J298" t="n">
-        <v>-6.3702</v>
+        <v>-6.1902</v>
       </c>
     </row>
     <row r="299">
@@ -14263,10 +14263,10 @@
         <v>0.62</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.3793</v>
+        <v>-0.3699</v>
       </c>
       <c r="J299" t="n">
-        <v>-6.8274</v>
+        <v>-6.6582</v>
       </c>
     </row>
     <row r="300">
@@ -14303,10 +14303,10 @@
         <v>0.6</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3962</v>
+        <v>-0.3872</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.1316</v>
+        <v>-6.9696</v>
       </c>
     </row>
     <row r="301">
@@ -14343,10 +14343,10 @@
         <v>0.6</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3962</v>
+        <v>-0.3872</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.1316</v>
+        <v>-6.9696</v>
       </c>
     </row>
     <row r="302">
@@ -14383,10 +14383,10 @@
         <v>1.82</v>
       </c>
       <c r="I302" t="n">
-        <v>1.315</v>
+        <v>1.3184</v>
       </c>
       <c r="J302" t="n">
-        <v>26.3</v>
+        <v>26.368</v>
       </c>
     </row>
     <row r="303">
@@ -14423,10 +14423,10 @@
         <v>1.73</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2059</v>
+        <v>1.2034</v>
       </c>
       <c r="J303" t="n">
-        <v>24.118</v>
+        <v>24.068</v>
       </c>
     </row>
     <row r="304">
@@ -14463,10 +14463,10 @@
         <v>1.5</v>
       </c>
       <c r="I304" t="n">
-        <v>0.9177</v>
+        <v>0.9089</v>
       </c>
       <c r="J304" t="n">
-        <v>18.354</v>
+        <v>18.178</v>
       </c>
     </row>
     <row r="305">
@@ -14503,10 +14503,10 @@
         <v>1.14</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3691</v>
+        <v>0.3365</v>
       </c>
       <c r="J305" t="n">
-        <v>7.382</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="306">
@@ -14543,10 +14543,10 @@
         <v>1.14</v>
       </c>
       <c r="I306" t="n">
-        <v>0.3691</v>
+        <v>0.3365</v>
       </c>
       <c r="J306" t="n">
-        <v>7.382</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="307">
@@ -14583,10 +14583,10 @@
         <v>0.85</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.1545</v>
+        <v>-0.1368</v>
       </c>
       <c r="J307" t="n">
-        <v>-3.09</v>
+        <v>-2.736</v>
       </c>
     </row>
     <row r="308">
@@ -14623,10 +14623,10 @@
         <v>0.72</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.2911</v>
+        <v>-0.2789</v>
       </c>
       <c r="J308" t="n">
-        <v>-5.822</v>
+        <v>-5.578</v>
       </c>
     </row>
     <row r="309">
@@ -14663,10 +14663,10 @@
         <v>0.66</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.3467</v>
+        <v>-0.3361</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.934</v>
+        <v>-6.722</v>
       </c>
     </row>
     <row r="310">
@@ -14703,10 +14703,10 @@
         <v>0.58</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4153</v>
+        <v>-0.4066</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.305999999999999</v>
+        <v>-8.132</v>
       </c>
     </row>
     <row r="311">
@@ -14743,10 +14743,10 @@
         <v>0.38</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.591</v>
+        <v>-0.6014</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.82</v>
+        <v>-12.028</v>
       </c>
     </row>
     <row r="312">
@@ -14783,10 +14783,10 @@
         <v>1.99</v>
       </c>
       <c r="I312" t="n">
-        <v>1.5197</v>
+        <v>1.5392</v>
       </c>
       <c r="J312" t="n">
-        <v>31.9137</v>
+        <v>32.3232</v>
       </c>
     </row>
     <row r="313">
@@ -14823,10 +14823,10 @@
         <v>1.51</v>
       </c>
       <c r="I313" t="n">
-        <v>0.9319</v>
+        <v>0.9225</v>
       </c>
       <c r="J313" t="n">
-        <v>19.5699</v>
+        <v>19.3725</v>
       </c>
     </row>
     <row r="314">
@@ -14863,10 +14863,10 @@
         <v>1.49</v>
       </c>
       <c r="I314" t="n">
-        <v>0.9062</v>
+        <v>0.8968</v>
       </c>
       <c r="J314" t="n">
-        <v>19.0302</v>
+        <v>18.8328</v>
       </c>
     </row>
     <row r="315">
@@ -14903,10 +14903,10 @@
         <v>1.22</v>
       </c>
       <c r="I315" t="n">
-        <v>0.524</v>
+        <v>0.5212</v>
       </c>
       <c r="J315" t="n">
-        <v>11.004</v>
+        <v>10.9452</v>
       </c>
     </row>
     <row r="316">
@@ -14943,10 +14943,10 @@
         <v>1.04</v>
       </c>
       <c r="I316" t="n">
-        <v>0.098</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J316" t="n">
-        <v>2.058</v>
+        <v>1.5015</v>
       </c>
     </row>
     <row r="317">
@@ -14983,10 +14983,10 @@
         <v>0.79</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.2227</v>
+        <v>-0.2078</v>
       </c>
       <c r="J317" t="n">
-        <v>-4.6767</v>
+        <v>-4.3638</v>
       </c>
     </row>
     <row r="318">
@@ -15023,10 +15023,10 @@
         <v>0.67</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3391</v>
+        <v>-0.3278</v>
       </c>
       <c r="J318" t="n">
-        <v>-7.1211</v>
+        <v>-6.8838</v>
       </c>
     </row>
     <row r="319">
@@ -15063,10 +15063,10 @@
         <v>0.66</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3478</v>
+        <v>-0.3367</v>
       </c>
       <c r="J319" t="n">
-        <v>-7.3038</v>
+        <v>-7.0707</v>
       </c>
     </row>
     <row r="320">
@@ -15103,10 +15103,10 @@
         <v>0.57</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4255</v>
+        <v>-0.4171</v>
       </c>
       <c r="J320" t="n">
-        <v>-8.935499999999999</v>
+        <v>-8.7591</v>
       </c>
     </row>
     <row r="321">
@@ -15143,10 +15143,10 @@
         <v>0.55</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.305099999999999</v>
+        <v>-9.1539</v>
       </c>
     </row>
   </sheetData>
